--- a/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
+++ b/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R26864e1de1f64ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R527531db09124037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="R2d479092a2e84ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="Rd8900ffb774a44c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="R89192fcf0d124a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="Rea3e060b6b4b4ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="R91cd392e3dc84716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="R1677607bd1bb44d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R486aaf9d6802480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R207e763e04b54d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="R9ba909f268a64f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="R52ba5c3e90e44bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="R5f7cdf00ff05440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="R6a6ffc223e394926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="R208af04e414f44b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="R05137d543b7d4c53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +27,7 @@
     <x:numFmt numFmtId="203" formatCode="0"/>
     <x:numFmt numFmtId="204" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -114,8 +114,13 @@
       <x:color rgb="FF7A4E00"/>
       <x:name val="NanumGothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF9FB4C5"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -182,6 +187,11 @@
         <x:fgColor rgb="FFF4C145"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF9FB4C5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -217,7 +227,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="76">
+  <x:cellXfs count="78">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -380,6 +390,8 @@
     <x:xf numFmtId="202" fontId="14" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -845,7 +857,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7ef3706f53ba47e3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc327255a297e49e9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -875,7 +887,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R35d9acd2c25145c0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56a1f92c97ea4fe0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -885,8 +897,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FDSWBS" displayName="FDSWBS" ref="A3:S54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:S54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FDSWBS" displayName="FDSWBS" ref="A3:S55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:S55"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="WBS ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -898,7 +910,7 @@
     <x:tableColumn id="8" name="Plan Start"/>
     <x:tableColumn id="9" name="Plan End"/>
     <x:tableColumn id="10" name="Calendar Days"/>
-    <x:tableColumn id="11" name="Working Days"/>
+    <x:tableColumn id="11" name="Lead Workdays"/>
     <x:tableColumn id="12" name="Lead"/>
     <x:tableColumn id="13" name="Support"/>
     <x:tableColumn id="14" name="Dependencies / Decisions"/>
@@ -1250,7 +1262,7 @@
         <x:v>Planning records</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
         <x:v>G2 Target</x:v>
@@ -1264,7 +1276,7 @@
         <x:v>Tasks + ICR</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
         <x:v>G3 Target</x:v>
@@ -1287,6 +1299,14 @@
         <x:v>In Progress / End TBD</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="D9" s="67" t="str">
+        <x:v>CR-P1-ANS-01-01</x:v>
+      </x:c>
+      <x:c r="E9" s="67" t="str">
+        <x:v>Done / 2026-09-07</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11">
       <x:c r="A11" s="9" t="str">
         <x:v>Status</x:v>
@@ -1306,15 +1326,15 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B12" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$54,A12)</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIF(WBS!$G$4:$G$55,A12)</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="E12" s="13" t="n">
-        <x:f>COUNTIF(WBS!$L$4:$L$54,D12)</x:f>
-        <x:v>28</x:v>
+        <x:f>COUNTIF(WBS!$L$4:$L$55,D12)</x:f>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1322,14 +1342,14 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$54,A13)</x:f>
+        <x:f>COUNTIF(WBS!$G$4:$G$55,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="E13" s="13" t="n">
-        <x:f>COUNTIF(WBS!$L$4:$L$54,D13)</x:f>
+        <x:f>COUNTIF(WBS!$L$4:$L$55,D13)</x:f>
         <x:v>13</x:v>
       </x:c>
     </x:row>
@@ -1338,14 +1358,14 @@
         <x:v>In Review</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$54,A14)</x:f>
+        <x:f>COUNTIF(WBS!$G$4:$G$55,A14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="13" t="str">
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="E14" s="13" t="n">
-        <x:f>COUNTIF(WBS!$L$4:$L$54,D14)</x:f>
+        <x:f>COUNTIF(WBS!$L$4:$L$55,D14)</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -1354,7 +1374,7 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="B15" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$54,A15)</x:f>
+        <x:f>COUNTIF(WBS!$G$4:$G$55,A15)</x:f>
         <x:v>42</x:v>
       </x:c>
     </x:row>
@@ -1502,7 +1522,7 @@
     <x:mergeCell ref="A18:V18"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f71d7548f5247b8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80ddee034ef24f8a"/>
 </x:worksheet>
 </file>
 
@@ -2170,80 +2190,77 @@
         <x:v>TBD</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="44" customHeight="1">
+    <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" s="13" t="str">
-        <x:v>P1-APP-01</x:v>
+        <x:v>CR-P1-ANS-01-01</x:v>
       </x:c>
       <x:c r="B12" s="13" t="str">
-        <x:v>transaction-api / fds-engine</x:v>
+        <x:v>Kubernetes Node DNS Resolver Automation</x:v>
       </x:c>
       <x:c r="C12" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
-        <x:v>Application / MSA</x:v>
+        <x:v>Automation / DNS Client</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Change Request</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G12" s="13" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="H12" s="19" t="n">
-        <x:v>46266</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="I12" s="19" t="n">
-        <x:v>46275</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="J12" s="61" t="n">
-        <x:f>IF(OR(H12="",I12=""),"",I12-H12+1)</x:f>
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K12" s="61" t="n">
-        <x:f>IF(OR(H12="",I12=""),"",NETWORKDAYS(H12,I12,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L12,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H12,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I12,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L12" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="M12" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N12" s="13" t="str">
-        <x:v>Service 80→8000, readiness /readyz, liveness /livez가 배포·호출·복구 시험에서 PASS하고 증적이 승인된다.</x:v>
+        <x:v>D08; D09; D34; D35; P1-DNS-01; P1-LB-01 Stage A</x:v>
       </x:c>
       <x:c r="O12" s="13" t="str">
-        <x:v>RISK-07; RISK-09</x:v>
+        <x:v>RISK-02; RISK-04; RISK-07</x:v>
       </x:c>
       <x:c r="P12" s="13" t="str">
-        <x:v>transaction-api Service 80→8000과 /readyz·/livez Probe를 구현하고 P1-LB-01·P1-SEC-01의 Entry/Policy 검증 입력으로 제공한다.</x:v>
+        <x:v>6개 Kubernetes 노드의 Resolver를 dns01(.52)→dns02(.53) 순서로 자동화하고 fds.internal FQDN·short name, 외부 DNS, 직접 질의, 서비스 회귀, 멱등성, Rollback, 증적 및 Support Review를 모두 검증한다.</x:v>
       </x:c>
       <x:c r="Q12" s="13" t="str">
-        <x:v>이재환 09-04 개인 휴가를 owner-specific 비가용일로 반영해 종료를 09-10으로 조정한다. 이하영이 기술 지원하며 G2 09-11 목표는 유지한다. 이하영 2026-09-08 면접 휴가로 당일 지원 가용성이 없다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>2026-09-07 구현·검토·수동 병합 완료. GitHub Actions는 NOT RUN. 다음 정본에 동기화하되 후속 Gate 완료를 자동 승인하지 않는다.</x:v>
       </x:c>
       <x:c r="R12" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; 321Team/infra-ansible PR #1; approved HEAD 507d8882a04f53640b07251bcc234b7d6ee81c09; merge 4f9bdb7c08704eebb3d1b294751e51b0721b6af4</x:v>
       </x:c>
       <x:c r="S12" s="13" t="str">
-        <x:f>IF(G12="Done","Complete",IF(OR(H12="",I12=""),"TBD",IF(I12&lt;'Executive Summary'!$B$4,"Past Due",IF(H12&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Active Window</x:v>
+        <x:v>Complete</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="13" t="str">
-        <x:v>P1-CICD-01</x:v>
+        <x:v>P1-APP-01</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>GitHub Actions / Self-hosted Runner Delivery</x:v>
+        <x:v>transaction-api / fds-engine</x:v>
       </x:c>
       <x:c r="C13" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
-        <x:v>CI/CD / Supply Chain</x:v>
+        <x:v>Application / MSA</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
         <x:v>Task</x:v>
@@ -2252,42 +2269,42 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G13" s="13" t="str">
-        <x:v>To Do</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="H13" s="19" t="n">
         <x:v>46266</x:v>
       </x:c>
       <x:c r="I13" s="19" t="n">
-        <x:v>46274</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="J13" s="61" t="n">
         <x:f>IF(OR(H13="",I13=""),"",I13-H13+1)</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K13" s="61" t="n">
         <x:f>IF(OR(H13="",I13=""),"",NETWORKDAYS(H13,I13,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L13,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H13,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I13,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="L13" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="M13" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N13" s="13" t="str">
-        <x:v>D03; D04; D19</x:v>
+        <x:v>Service 80→8000, readiness /readyz, liveness /livez가 배포·호출·복구 시험에서 PASS하고 증적이 승인된다.</x:v>
       </x:c>
       <x:c r="O13" s="13" t="str">
-        <x:v>RISK-06; RISK-08</x:v>
+        <x:v>RISK-07; RISK-09</x:v>
       </x:c>
       <x:c r="P13" s="13" t="str">
-        <x:v>GitHub→Runner→Test→Build→Trivy→Harbor→Kubernetes Deploy→Health/E2E 흐름과 실패 시 Deploy 차단 Evidence 확보</x:v>
+        <x:v>transaction-api Service 80→8000과 /readyz·/livez Probe를 구현하고 P1-LB-01·P1-SEC-01의 Entry/Policy 검증 입력으로 제공한다.</x:v>
       </x:c>
       <x:c r="Q13" s="13" t="str">
-        <x:v>G1에는 Runner 연결·Harbor Push/Pull까지만 중간검증하고, 전체 Delivery Gate는 G2 전 09-09 완료한다. 이하영 2026-09-08 면접 휴가로 당일 지원 가용성이 없다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>이재환 09-04 개인 휴가를 owner-specific 비가용일로 반영해 종료를 09-10으로 조정한다. 이하영이 기술 지원하며 G2 09-11 목표는 유지한다. 이하영 2026-09-08 면접 휴가로 당일 지원 가용성이 없다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
       </x:c>
       <x:c r="R13" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
       </x:c>
       <x:c r="S13" s="13" t="str">
         <x:f>IF(G13="Done","Complete",IF(OR(H13="",I13=""),"TBD",IF(I13&lt;'Executive Summary'!$B$4,"Past Due",IF(H13&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -2296,16 +2313,16 @@
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="13" t="str">
-        <x:v>P1-MON-01</x:v>
+        <x:v>P1-CICD-01</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
-        <x:v>Prometheus / Node / App Metrics</x:v>
+        <x:v>GitHub Actions / Self-hosted Runner Delivery</x:v>
       </x:c>
       <x:c r="C14" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D14" s="13" t="str">
-        <x:v>Monitoring / Observability</x:v>
+        <x:v>CI/CD / Supply Chain</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
         <x:v>Task</x:v>
@@ -2314,42 +2331,42 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G14" s="13" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>To Do</x:v>
       </x:c>
       <x:c r="H14" s="19" t="n">
-        <x:v>46272</x:v>
+        <x:v>46266</x:v>
       </x:c>
       <x:c r="I14" s="19" t="n">
-        <x:v>46276</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="J14" s="61" t="n">
         <x:f>IF(OR(H14="",I14=""),"",I14-H14+1)</x:f>
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K14" s="61" t="n">
         <x:f>IF(OR(H14="",I14=""),"",NETWORKDAYS(H14,I14,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L14,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H14,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I14,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L14" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="M14" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="N14" s="13" t="str">
-        <x:v>D05; D14</x:v>
+        <x:v>D03; D04; D19</x:v>
       </x:c>
       <x:c r="O14" s="13" t="str">
-        <x:v>RISK-04; RISK-07</x:v>
+        <x:v>RISK-06; RISK-08</x:v>
       </x:c>
       <x:c r="P14" s="13" t="str">
-        <x:v>monitor01 Prometheus가 Node 9100/Kubelet 10250/App 8000/8001을 수집하고 거래·FDS·오류·상태 지표 조회 Evidence 확보</x:v>
+        <x:v>GitHub→Runner→Test→Build→Trivy→Harbor→Kubernetes Deploy→Health/E2E 흐름과 실패 시 Deploy 차단 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q14" s="13" t="str">
-        <x:v>이재환 09-04 개인 휴가로 실행 착수를 09-07로 이동한다. 사전 Metrics/Target 설계는 유지하고, 이권욱 지원 아래 K8S/APP 준비 후 통합한다. G2 09-11 목표 유지.</x:v>
+        <x:v>G1에는 Runner 연결·Harbor Push/Pull까지만 중간검증하고, 전체 Delivery Gate는 G2 전 09-09 완료한다. 이하영 2026-09-08 면접 휴가로 당일 지원 가용성이 없다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
       </x:c>
       <x:c r="R14" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S14" s="13" t="str">
         <x:f>IF(G14="Done","Complete",IF(OR(H14="",I14=""),"TBD",IF(I14&lt;'Executive Summary'!$B$4,"Past Due",IF(H14&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -2358,80 +2375,81 @@
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
       <x:c r="A15" s="13" t="str">
-        <x:v>MS-G1-01</x:v>
+        <x:v>P1-MON-01</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>G1 Infrastructure Ready</x:v>
+        <x:v>Prometheus / Node / App Metrics</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
-        <x:v>Milestone / Infrastructure</x:v>
+        <x:v>Monitoring / Observability</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G15" s="13" t="str">
-        <x:v>To Do</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="H15" s="19" t="n">
         <x:v>46272</x:v>
       </x:c>
       <x:c r="I15" s="19" t="n">
-        <x:v>46272</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="J15" s="61" t="n">
         <x:f>IF(OR(H15="",I15=""),"",I15-H15+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K15" s="61" t="n">
         <x:f>IF(OR(H15="",I15=""),"",NETWORKDAYS(H15,I15,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L15,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H15,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I15,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L15" s="13" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="M15" s="13" t="str">
         <x:v>이권욱</x:v>
       </x:c>
-      <x:c r="M15" s="13" t="str">
-        <x:v>이하영, 이재환</x:v>
-      </x:c>
       <x:c r="N15" s="13" t="str">
-        <x:v>D19; D25; D27</x:v>
+        <x:v>D05; D14</x:v>
       </x:c>
       <x:c r="O15" s="13" t="str">
-        <x:v>RISK-02; RISK-03; RISK-04; RISK-06; RISK-07; RISK-08</x:v>
+        <x:v>RISK-04; RISK-07</x:v>
       </x:c>
       <x:c r="P15" s="13" t="str">
-        <x:v>CentOS/containerd, Ansible Inventory/SSH/멱등성, 3CP+3Worker, API LB/Calico, Harbor/Runner/PostgreSQL, Node Connectivity와 Push/Pull 준비도 승인</x:v>
+        <x:v>monitor01 Prometheus가 Node 9100/Kubelet 10250/App 8000/8001을 수집하고 거래·FDS·오류·상태 지표 조회 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q15" s="13" t="str">
-        <x:v>이재환 09-04 개인 휴가와 P1-DB-01 완료일 조정에 연동해 G1을 09-07로 이동한다. P1-DNS-01 Done, P1-LB-01 Stage A PASS를 반영하며 G2/G3/Phase 1 Close는 유지한다.</x:v>
+        <x:v>이재환 09-04 개인 휴가로 실행 착수를 09-07로 이동한다. 사전 Metrics/Target 설계는 유지하고, 이권욱 지원 아래 K8S/APP 준비 후 통합한다. G2 09-11 목표 유지.</x:v>
       </x:c>
       <x:c r="R15" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
       </x:c>
       <x:c r="S15" s="13" t="str">
-        <x:v>Overdue / To Do</x:v>
+        <x:f>IF(G15="Done","Complete",IF(OR(H15="",I15=""),"TBD",IF(I15&lt;'Executive Summary'!$B$4,"Past Due",IF(H15&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
+        <x:v>Active Window</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="44" customHeight="1">
       <x:c r="A16" s="13" t="str">
-        <x:v>P1-SEC-01</x:v>
+        <x:v>MS-G1-01</x:v>
       </x:c>
       <x:c r="B16" s="13" t="str">
-        <x:v>Kubernetes Security Controls</x:v>
+        <x:v>G1 Infrastructure Ready</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D16" s="13" t="str">
-        <x:v>Security / Kubernetes</x:v>
+        <x:v>Milestone / Infrastructure</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Milestone</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
         <x:v>P0</x:v>
@@ -2440,56 +2458,56 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H16" s="19" t="n">
-        <x:v>46269</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="I16" s="19" t="n">
-        <x:v>46276</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="J16" s="61" t="n">
         <x:f>IF(OR(H16="",I16=""),"",I16-H16+1)</x:f>
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K16" s="61" t="n">
-        <x:v>5</x:v>
+        <x:f>IF(OR(H16="",I16=""),"",NETWORKDAYS(H16,I16,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L16,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H16,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I16,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L16" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="M16" s="13" t="str">
-        <x:v>이권욱, 이재환</x:v>
+        <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N16" s="13" t="str">
-        <x:v>Restricted SecurityContext와 PSA가 실제 클러스터에서 동작하고, .50/32→30080 Positive 및 비허용 Source→30080 Negative Test가 PASS한다.</x:v>
+        <x:v>D19; D25; D27</x:v>
       </x:c>
       <x:c r="O16" s="13" t="str">
-        <x:v>RISK-06; RISK-07</x:v>
+        <x:v>RISK-02; RISK-03; RISK-04; RISK-06; RISK-07; RISK-08</x:v>
       </x:c>
       <x:c r="P16" s="13" t="str">
-        <x:v>HO-ANS-02B SecurityContext/PSA Restricted live-cluster 호환성과 HO-ANS-04C edge01 .50/32→Worker NodePort 30080 허용·기타 Source 차단을 검증한다.</x:v>
+        <x:v>CentOS/containerd, Ansible Inventory/SSH/멱등성, 3CP+3Worker, API LB/Calico, Harbor/Runner/PostgreSQL, Node Connectivity와 Push/Pull 준비도 승인</x:v>
       </x:c>
       <x:c r="Q16" s="13" t="str">
-        <x:v>09-04 이재환 지원 부재는 이권욱이 커버한다. Lead 이하영 일정은 유지하며 D34/D35 및 P1-K8S-01 Gate 결과를 반영한다. 이하영 2026-09-08 면접 휴가로 당일 작업·단독 종료를 배치하지 않는다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>이재환 09-04 개인 휴가와 P1-DB-01 완료일 조정에 연동해 G1을 09-07로 이동한다. P1-DNS-01 Done, P1-LB-01 Stage A PASS를 반영하며 G2/G3/Phase 1 Close는 유지한다.</x:v>
       </x:c>
       <x:c r="R16" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D34; D35; D36</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
       </x:c>
       <x:c r="S16" s="13" t="str">
-        <x:f>IF(G16="Done","Complete",IF(OR(H16="",I16=""),"TBD",IF(I16&lt;'Executive Summary'!$B$4,"Past Due",IF(H16&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Active Window</x:v>
+        <x:v>Past Due</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="13" t="str">
-        <x:v>P1-E2E-01</x:v>
+        <x:v>P1-SEC-01</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>Initial / Final E2E &amp; Regression</x:v>
+        <x:v>Kubernetes Security Controls</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>QA / Integration Test</x:v>
+        <x:v>Security / Kubernetes</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
         <x:v>Task</x:v>
@@ -2501,57 +2519,56 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H17" s="19" t="n">
-        <x:v>46274</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="I17" s="19" t="n">
-        <x:v>46283</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="J17" s="61" t="n">
         <x:f>IF(OR(H17="",I17=""),"",I17-H17+1)</x:f>
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K17" s="61" t="n">
-        <x:f>IF(OR(H17="",I17=""),"",NETWORKDAYS(H17,I17,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L17,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H17,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I17,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L17" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="M17" s="13" t="str">
-        <x:v>이권욱, 이하영</x:v>
+        <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N17" s="13" t="str">
-        <x:v>D03; D05; D17; D18</x:v>
+        <x:v>Restricted SecurityContext와 PSA가 실제 클러스터에서 동작하고, .50/32→30080 Positive 및 비허용 Source→30080 Negative Test가 PASS한다.</x:v>
       </x:c>
       <x:c r="O17" s="13" t="str">
-        <x:v>RISK-05; RISK-07; RISK-09</x:v>
+        <x:v>RISK-06; RISK-07</x:v>
       </x:c>
       <x:c r="P17" s="13" t="str">
-        <x:v>Client→edge→transaction-api→fds-engine→PostgreSQL→Prometheus E2E, Rule·Negative·Regression PASS, Critical Issue 0 및 Evidence 승인</x:v>
+        <x:v>HO-ANS-02B SecurityContext/PSA Restricted live-cluster 호환성과 HO-ANS-04C edge01 .50/32→Worker NodePort 30080 허용·기타 Source 차단을 검증한다.</x:v>
       </x:c>
       <x:c r="Q17" s="13" t="str">
-        <x:v>이재환 09-14~09-17 부재 중 지원자가 Evidence 정리와 결함 추적을 수행하고, 최종 판정은 09-18 복귀 후 완료한다.</x:v>
+        <x:v>09-04 이재환 지원 부재는 이권욱이 커버한다. Lead 이하영 일정은 유지하며 D34/D35 및 P1-K8S-01 Gate 결과를 반영한다. 이하영 2026-09-08 면접 휴가로 당일 작업·단독 종료를 배치하지 않는다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
       </x:c>
       <x:c r="R17" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D34; D35; D36</x:v>
       </x:c>
       <x:c r="S17" s="13" t="str">
         <x:f>IF(G17="Done","Complete",IF(OR(H17="",I17=""),"TBD",IF(I17&lt;'Executive Summary'!$B$4,"Past Due",IF(H17&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:v>Active Window</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="44" customHeight="1">
       <x:c r="A18" s="13" t="str">
-        <x:v>P1-DR-01</x:v>
+        <x:v>P1-E2E-01</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>PostgreSQL Backup / Restore</x:v>
+        <x:v>Initial / Final E2E &amp; Regression</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D18" s="13" t="str">
-        <x:v>DR / Data Recovery</x:v>
+        <x:v>QA / Integration Test</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
         <x:v>Task</x:v>
@@ -2563,36 +2580,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H18" s="19" t="n">
-        <x:v>46275</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="I18" s="19" t="n">
-        <x:v>46278</x:v>
+        <x:v>46283</x:v>
       </x:c>
       <x:c r="J18" s="61" t="n">
         <x:f>IF(OR(H18="",I18=""),"",I18-H18+1)</x:f>
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K18" s="61" t="n">
         <x:f>IF(OR(H18="",I18=""),"",NETWORKDAYS(H18,I18,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L18,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H18,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I18,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L18" s="13" t="str">
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="M18" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이권욱, 이하영</x:v>
       </x:c>
       <x:c r="N18" s="13" t="str">
-        <x:v>D04</x:v>
+        <x:v>D03; D05; D17; D18</x:v>
       </x:c>
       <x:c r="O18" s="13" t="str">
-        <x:v>RISK-05; RISK-09</x:v>
+        <x:v>RISK-05; RISK-07; RISK-09</x:v>
       </x:c>
       <x:c r="P18" s="13" t="str">
-        <x:v>pg_dump Backup, 승인된 초기화/격리 환경 Restore, Row/Rule 결과 정합성 및 Restore 후 Final E2E PASS와 Runbook 확보</x:v>
+        <x:v>Client→edge→transaction-api→fds-engine→PostgreSQL→Prometheus E2E, Rule·Negative·Regression PASS, Critical Issue 0 및 Evidence 승인</x:v>
       </x:c>
       <x:c r="Q18" s="13" t="str">
-        <x:v>Harbor Restore와 etcd Snapshot/Restore는 P1이다. 운영 데이터 삭제 없이 별도 Restore DB 또는 승인 절차를 사용한다.</x:v>
+        <x:v>이재환 09-14~09-17 부재 중 지원자가 Evidence 정리와 결함 추적을 수행하고, 최종 판정은 09-18 복귀 후 완료한다.</x:v>
       </x:c>
       <x:c r="R18" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -2604,16 +2621,16 @@
     </x:row>
     <x:row r="19" ht="44" customHeight="1">
       <x:c r="A19" s="13" t="str">
-        <x:v>P1-HA-01</x:v>
+        <x:v>P1-DR-01</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>Worker Drain Continuity</x:v>
+        <x:v>PostgreSQL Backup / Restore</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>HA / Resilience</x:v>
+        <x:v>DR / Data Recovery</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
         <x:v>Task</x:v>
@@ -2642,19 +2659,19 @@
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="M19" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="N19" s="13" t="str">
-        <x:v>D02; D03</x:v>
+        <x:v>D04</x:v>
       </x:c>
       <x:c r="O19" s="13" t="str">
-        <x:v>RISK-03; RISK-05; RISK-07</x:v>
+        <x:v>RISK-05; RISK-09</x:v>
       </x:c>
       <x:c r="P19" s="13" t="str">
-        <x:v>FDS Replica 3개 Worker 분산, Worker Drain 중 승인된 서비스 지속 기준 충족, 복구·Uncordon 및 E2E Evidence 확보</x:v>
+        <x:v>pg_dump Backup, 승인된 초기화/격리 환경 Restore, Row/Rule 결과 정합성 및 Restore 후 Final E2E PASS와 Runbook 확보</x:v>
       </x:c>
       <x:c r="Q19" s="13" t="str">
-        <x:v>Control Plane 장애와 Rolling Update는 P1이다. 본 P0는 Worker 1대 Drain 시 서비스 지속만 검증한다.</x:v>
+        <x:v>Harbor Restore와 etcd Snapshot/Restore는 P1이다. 운영 데이터 삭제 없이 별도 Restore DB 또는 승인 절차를 사용한다.</x:v>
       </x:c>
       <x:c r="R19" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -2666,19 +2683,19 @@
     </x:row>
     <x:row r="20" ht="44" customHeight="1">
       <x:c r="A20" s="13" t="str">
-        <x:v>MS-G2-01</x:v>
+        <x:v>P1-HA-01</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>G2 Security / Feature Ready</x:v>
+        <x:v>Worker Drain Continuity</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>Milestone / Security &amp; Feature</x:v>
+        <x:v>HA / Resilience</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F20" s="13" t="str">
         <x:v>P0</x:v>
@@ -2687,36 +2704,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H20" s="19" t="n">
-        <x:v>46276</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="I20" s="19" t="n">
-        <x:v>46276</x:v>
+        <x:v>46278</x:v>
       </x:c>
       <x:c r="J20" s="61" t="n">
         <x:f>IF(OR(H20="",I20=""),"",I20-H20+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K20" s="61" t="n">
         <x:f>IF(OR(H20="",I20=""),"",NETWORKDAYS(H20,I20,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L20,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H20,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I20,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L20" s="13" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="M20" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
-      <x:c r="M20" s="13" t="str">
-        <x:v>이권욱, 이재환</x:v>
-      </x:c>
       <x:c r="N20" s="13" t="str">
-        <x:v>D17; D18; D19; D27</x:v>
+        <x:v>D02; D03</x:v>
       </x:c>
       <x:c r="O20" s="13" t="str">
-        <x:v>RISK-05; RISK-06; RISK-07; RISK-08; RISK-09</x:v>
+        <x:v>RISK-03; RISK-05; RISK-07</x:v>
       </x:c>
       <x:c r="P20" s="13" t="str">
-        <x:v>2-Service MSA, DB 저장, Security P0, CI/CD, Monitoring, Initial E2E/Negative Test/Worker Drain 준비도를 승인</x:v>
+        <x:v>FDS Replica 3개 Worker 분산, Worker Drain 중 승인된 서비스 지속 기준 충족, 복구·Uncordon 및 E2E Evidence 확보</x:v>
       </x:c>
       <x:c r="Q20" s="13" t="str">
-        <x:v>D-SEC-01/D17과 DEC-P1-ENTRY-01/D18을 G2 선행조건으로 판정한다. Scope·Approver·Exit Criteria 승인과 External Exposure 결정을 P1-SEC-01 및 P1-APP-01 Evidence에 연결한다.</x:v>
+        <x:v>Control Plane 장애와 Rolling Update는 P1이다. 본 P0는 Worker 1대 Drain 시 서비스 지속만 검증한다.</x:v>
       </x:c>
       <x:c r="R20" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -2728,19 +2745,19 @@
     </x:row>
     <x:row r="21" ht="44" customHeight="1">
       <x:c r="A21" s="13" t="str">
-        <x:v>P1-DOC-01</x:v>
+        <x:v>MS-G2-01</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>Architecture / Test / Runbook Freeze</x:v>
+        <x:v>G2 Security / Feature Ready</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D21" s="13" t="str">
-        <x:v>PMO / Documentation</x:v>
+        <x:v>Milestone / Security &amp; Feature</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Milestone</x:v>
       </x:c>
       <x:c r="F21" s="13" t="str">
         <x:v>P0</x:v>
@@ -2749,36 +2766,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H21" s="19" t="n">
-        <x:v>46277</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="I21" s="19" t="n">
-        <x:v>46283</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="J21" s="61" t="n">
         <x:f>IF(OR(H21="",I21=""),"",I21-H21+1)</x:f>
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K21" s="61" t="n">
         <x:f>IF(OR(H21="",I21=""),"",NETWORKDAYS(H21,I21,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L21,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H21,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I21,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L21" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="M21" s="13" t="str">
-        <x:v>이하영, 이재환</x:v>
+        <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N21" s="13" t="str">
-        <x:v>D12; D20; D25</x:v>
+        <x:v>D17; D18; D19; D27</x:v>
       </x:c>
       <x:c r="O21" s="13" t="str">
-        <x:v>RISK-05; RISK-13</x:v>
+        <x:v>RISK-05; RISK-06; RISK-07; RISK-08; RISK-09</x:v>
       </x:c>
       <x:c r="P21" s="13" t="str">
-        <x:v>As-built Architecture, Test/Evidence Index, 구축·운영·복구 Runbook, P1 미완료 Known Issue의 풀네임 Owner·Due, Version/Source 및 Review 재현성 승인</x:v>
+        <x:v>2-Service MSA, DB 저장, Security P0, CI/CD, Monitoring, Initial E2E/Negative Test/Worker Drain 준비도를 승인</x:v>
       </x:c>
       <x:c r="Q21" s="13" t="str">
-        <x:v>이재환 부재 전 09-13까지 HA/DR Evidence 초안을 인계하고 09-18 최종 검토한다.</x:v>
+        <x:v>D-SEC-01/D17과 DEC-P1-ENTRY-01/D18을 G2 선행조건으로 판정한다. Scope·Approver·Exit Criteria 승인과 External Exposure 결정을 P1-SEC-01 및 P1-APP-01 Evidence에 연결한다.</x:v>
       </x:c>
       <x:c r="R21" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -2790,22 +2807,22 @@
     </x:row>
     <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="13" t="str">
-        <x:v>P1-MON-02</x:v>
+        <x:v>P1-DOC-01</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>Dashboard / Alert Enhancement</x:v>
+        <x:v>Architecture / Test / Runbook Freeze</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D22" s="13" t="str">
-        <x:v>Monitoring / Observability</x:v>
+        <x:v>PMO / Documentation</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
         <x:v>Task</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G22" s="13" t="str">
         <x:v>To Do</x:v>
@@ -2822,25 +2839,25 @@
       </x:c>
       <x:c r="K22" s="61" t="n">
         <x:f>IF(OR(H22="",I22=""),"",NETWORKDAYS(H22,I22,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L22,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H22,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I22,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L22" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="M22" s="13" t="str">
-        <x:v>이권욱, 이하영</x:v>
+        <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N22" s="13" t="str">
-        <x:v>D25</x:v>
+        <x:v>D12; D20; D25</x:v>
       </x:c>
       <x:c r="O22" s="13" t="str">
-        <x:v>RISK-05; RISK-07; RISK-09; RISK-14</x:v>
+        <x:v>RISK-05; RISK-13</x:v>
       </x:c>
       <x:c r="P22" s="13" t="str">
-        <x:v>거래·FDS·Node·Pod 상태 Dashboard와 최소 Alert Rule을 구성하고 정상·장애 시나리오 Evidence 확보</x:v>
+        <x:v>As-built Architecture, Test/Evidence Index, 구축·운영·복구 Runbook, P1 미완료 Known Issue의 풀네임 Owner·Due, Version/Source 및 Review 재현성 승인</x:v>
       </x:c>
       <x:c r="Q22" s="13" t="str">
-        <x:v>P1-MON-01의 Metric 수집 완료 후 수행한다. Grafana 또는 Prometheus UI 중 승인된 최소 구현을 사용하며 Loki/SIEM은 Scope Out이다.</x:v>
+        <x:v>이재환 부재 전 09-13까지 HA/DR Evidence 초안을 인계하고 09-18 최종 검토한다.</x:v>
       </x:c>
       <x:c r="R22" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -2852,16 +2869,16 @@
     </x:row>
     <x:row r="23" ht="44" customHeight="1">
       <x:c r="A23" s="13" t="str">
-        <x:v>P1-DR-02</x:v>
+        <x:v>P1-MON-02</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
-        <x:v>Harbor / etcd Backup and Restore</x:v>
+        <x:v>Dashboard / Alert Enhancement</x:v>
       </x:c>
       <x:c r="C23" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D23" s="13" t="str">
-        <x:v>DR / Platform Recovery</x:v>
+        <x:v>Monitoring / Observability</x:v>
       </x:c>
       <x:c r="E23" s="13" t="str">
         <x:v>Task</x:v>
@@ -2873,36 +2890,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H23" s="19" t="n">
-        <x:v>46279</x:v>
+        <x:v>46277</x:v>
       </x:c>
       <x:c r="I23" s="19" t="n">
         <x:v>46283</x:v>
       </x:c>
       <x:c r="J23" s="61" t="n">
         <x:f>IF(OR(H23="",I23=""),"",I23-H23+1)</x:f>
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K23" s="61" t="n">
         <x:f>IF(OR(H23="",I23=""),"",NETWORKDAYS(H23,I23,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L23,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H23,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I23,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L23" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="M23" s="13" t="str">
-        <x:v>이권욱, 이재환</x:v>
+        <x:v>이권욱, 이하영</x:v>
       </x:c>
       <x:c r="N23" s="13" t="str">
-        <x:v>D04; D25</x:v>
+        <x:v>D25</x:v>
       </x:c>
       <x:c r="O23" s="13" t="str">
-        <x:v>RISK-05; RISK-06; RISK-08; RISK-14</x:v>
+        <x:v>RISK-05; RISK-07; RISK-09; RISK-14</x:v>
       </x:c>
       <x:c r="P23" s="13" t="str">
-        <x:v>Harbor Backup/Restore와 etcd Snapshot/Restore를 격리 대상에서 수행하고 무결성·복구·Runbook Evidence 확보</x:v>
+        <x:v>거래·FDS·Node·Pod 상태 Dashboard와 최소 Alert Rule을 구성하고 정상·장애 시나리오 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q23" s="13" t="str">
-        <x:v>기존 P1-DR-02와 기준선의 etcd Snapshot/Restore P1 범위를 통합한다. Harbor HA는 Scope Out이며 미완료 시 Known Issue로 이관한다.</x:v>
+        <x:v>P1-MON-01의 Metric 수집 완료 후 수행한다. Grafana 또는 Prometheus UI 중 승인된 최소 구현을 사용하며 Loki/SIEM은 Scope Out이다.</x:v>
       </x:c>
       <x:c r="R23" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -2914,16 +2931,16 @@
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="13" t="str">
-        <x:v>P1-HA-02</x:v>
+        <x:v>P1-DR-02</x:v>
       </x:c>
       <x:c r="B24" s="13" t="str">
-        <x:v>Platform Resilience P1 Validation</x:v>
+        <x:v>Harbor / etcd Backup and Restore</x:v>
       </x:c>
       <x:c r="C24" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D24" s="13" t="str">
-        <x:v>HA / Platform Resilience</x:v>
+        <x:v>DR / Platform Recovery</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
         <x:v>Task</x:v>
@@ -2955,16 +2972,16 @@
         <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N24" s="13" t="str">
-        <x:v>D02; D25</x:v>
+        <x:v>D04; D25</x:v>
       </x:c>
       <x:c r="O24" s="13" t="str">
-        <x:v>RISK-03; RISK-05; RISK-07; RISK-14</x:v>
+        <x:v>RISK-05; RISK-06; RISK-08; RISK-14</x:v>
       </x:c>
       <x:c r="P24" s="13" t="str">
-        <x:v>Rolling Update, Control Plane 1대 장애, PDB 및 TopologySpreadConstraint 검증 결과와 복구 Evidence 확보</x:v>
+        <x:v>Harbor Backup/Restore와 etcd Snapshot/Restore를 격리 대상에서 수행하고 무결성·복구·Runbook Evidence 확보</x:v>
       </x:c>
       <x:c r="Q24" s="13" t="str">
-        <x:v>기존 P1-HA-02와 P1-HA-03 및 기준선의 PDB/TopologySpreadConstraint P1 범위를 통합한다. 미완료 시 Phase 1 Close의 Known Issue에 Owner 이하영과 Due를 기록한다.</x:v>
+        <x:v>기존 P1-DR-02와 기준선의 etcd Snapshot/Restore P1 범위를 통합한다. Harbor HA는 Scope Out이며 미완료 시 Known Issue로 이관한다.</x:v>
       </x:c>
       <x:c r="R24" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -2976,60 +2993,60 @@
     </x:row>
     <x:row r="25" ht="44" customHeight="1">
       <x:c r="A25" s="13" t="str">
-        <x:v>DEC-CAL-P1-01</x:v>
+        <x:v>P1-HA-02</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
-        <x:v>Phase 1 Weekend Review Decision</x:v>
+        <x:v>Platform Resilience P1 Validation</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D25" s="13" t="str">
-        <x:v>Schedule / Governance</x:v>
+        <x:v>HA / Platform Resilience</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G25" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H25" s="19" t="n">
-        <x:v>46282</x:v>
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="I25" s="19" t="n">
         <x:v>46283</x:v>
       </x:c>
       <x:c r="J25" s="61" t="n">
         <x:f>IF(OR(H25="",I25=""),"",I25-H25+1)</x:f>
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K25" s="61" t="n">
         <x:f>IF(OR(H25="",I25=""),"",NETWORKDAYS(H25,I25,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L25,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H25,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I25,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L25" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="M25" s="13" t="str">
-        <x:v>이하영, 이재환</x:v>
+        <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N25" s="13" t="str">
-        <x:v>D20</x:v>
+        <x:v>D02; D25</x:v>
       </x:c>
       <x:c r="O25" s="13" t="str">
-        <x:v>RISK-05; RISK-13</x:v>
+        <x:v>RISK-03; RISK-05; RISK-07; RISK-14</x:v>
       </x:c>
       <x:c r="P25" s="13" t="str">
-        <x:v>09-20 일요일 Review 유지 또는 영업일 재배치, 참석자·승인권자·시간·대체일을 확정하고 WBS/Calendar 동기화</x:v>
+        <x:v>Rolling Update, Control Plane 1대 장애, PDB 및 TopologySpreadConstraint 검증 결과와 복구 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q25" s="13" t="str">
-        <x:v>09-20은 일요일이며 Working Days 0이다. 결정 전 해당 일정을 확정된 근무일로 간주하지 않는다.</x:v>
+        <x:v>기존 P1-HA-02와 P1-HA-03 및 기준선의 PDB/TopologySpreadConstraint P1 범위를 통합한다. 미완료 시 Phase 1 Close의 Known Issue에 Owner 이하영과 Due를 기록한다.</x:v>
       </x:c>
       <x:c r="R25" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; 2026 Calendar</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S25" s="13" t="str">
         <x:f>IF(G25="Done","Complete",IF(OR(H25="",I25=""),"TBD",IF(I25&lt;'Executive Summary'!$B$4,"Past Due",IF(H25&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -3038,19 +3055,19 @@
     </x:row>
     <x:row r="26" ht="44" customHeight="1">
       <x:c r="A26" s="13" t="str">
-        <x:v>MS-G3-01</x:v>
+        <x:v>DEC-CAL-P1-01</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>G3 Review Ready</x:v>
+        <x:v>Phase 1 Weekend Review Decision</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D26" s="13" t="str">
-        <x:v>Milestone / Review Readiness</x:v>
+        <x:v>Schedule / Governance</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
         <x:v>P0</x:v>
@@ -3059,18 +3076,18 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H26" s="19" t="n">
-        <x:v>46283</x:v>
+        <x:v>46282</x:v>
       </x:c>
       <x:c r="I26" s="19" t="n">
         <x:v>46283</x:v>
       </x:c>
       <x:c r="J26" s="61" t="n">
         <x:f>IF(OR(H26="",I26=""),"",I26-H26+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K26" s="61" t="n">
         <x:f>IF(OR(H26="",I26=""),"",NETWORKDAYS(H26,I26,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L26,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H26,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I26,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L26" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -3082,16 +3099,16 @@
         <x:v>D20</x:v>
       </x:c>
       <x:c r="O26" s="13" t="str">
-        <x:v>RISK-05; RISK-09; RISK-13</x:v>
+        <x:v>RISK-05; RISK-13</x:v>
       </x:c>
       <x:c r="P26" s="13" t="str">
-        <x:v>Final E2E/Regression, Worker Drain, PostgreSQL Restore, Critical Issue 0, Architecture/Test/Runbook 준비도를 승인</x:v>
+        <x:v>09-20 일요일 Review 유지 또는 영업일 재배치, 참석자·승인권자·시간·대체일을 확정하고 WBS/Calendar 동기화</x:v>
       </x:c>
       <x:c r="Q26" s="13" t="str">
-        <x:v>같은 날 DEC-CAL-P1-01을 종결해 Review 일정을 확정한다.</x:v>
+        <x:v>09-20은 일요일이며 Working Days 0이다. 결정 전 해당 일정을 확정된 근무일로 간주하지 않는다.</x:v>
       </x:c>
       <x:c r="R26" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; 2026 Calendar</x:v>
       </x:c>
       <x:c r="S26" s="13" t="str">
         <x:f>IF(G26="Done","Complete",IF(OR(H26="",I26=""),"TBD",IF(I26&lt;'Executive Summary'!$B$4,"Past Due",IF(H26&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -3100,19 +3117,19 @@
     </x:row>
     <x:row r="27" ht="44" customHeight="1">
       <x:c r="A27" s="13" t="str">
-        <x:v>P1-REV-01</x:v>
+        <x:v>MS-G3-01</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
-        <x:v>Phase 1 Review / Close Execution</x:v>
+        <x:v>G3 Review Ready</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D27" s="13" t="str">
-        <x:v>PMO / Review</x:v>
+        <x:v>Milestone / Review Readiness</x:v>
       </x:c>
       <x:c r="E27" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Milestone</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
         <x:v>P0</x:v>
@@ -3124,15 +3141,15 @@
         <x:v>46283</x:v>
       </x:c>
       <x:c r="I27" s="19" t="n">
-        <x:v>46288</x:v>
+        <x:v>46283</x:v>
       </x:c>
       <x:c r="J27" s="61" t="n">
         <x:f>IF(OR(H27="",I27=""),"",I27-H27+1)</x:f>
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K27" s="61" t="n">
         <x:f>IF(OR(H27="",I27=""),"",NETWORKDAYS(H27,I27,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L27,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H27,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I27,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L27" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -3141,16 +3158,16 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N27" s="13" t="str">
-        <x:v>D12; D20</x:v>
+        <x:v>D20</x:v>
       </x:c>
       <x:c r="O27" s="13" t="str">
-        <x:v>RISK-05; RISK-13</x:v>
+        <x:v>RISK-05; RISK-09; RISK-13</x:v>
       </x:c>
       <x:c r="P27" s="13" t="str">
-        <x:v>G3 결과, Demo, P0 Evidence, Known Issue, P1 이관, Review Action을 승인하고 Phase 1 Close Sign-off 확보</x:v>
+        <x:v>Final E2E/Regression, Worker Drain, PostgreSQL Restore, Critical Issue 0, Architecture/Test/Runbook 준비도를 승인</x:v>
       </x:c>
       <x:c r="Q27" s="13" t="str">
-        <x:v>Review 실행일은 D20 결과를 따른다. 09-24~09-25 비근무 전에 09-23 Close를 완료한다.</x:v>
+        <x:v>같은 날 DEC-CAL-P1-01을 종결해 Review 일정을 확정한다.</x:v>
       </x:c>
       <x:c r="R27" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -3162,19 +3179,19 @@
     </x:row>
     <x:row r="28" ht="44" customHeight="1">
       <x:c r="A28" s="13" t="str">
-        <x:v>MS-P1-REVIEW-01</x:v>
+        <x:v>P1-REV-01</x:v>
       </x:c>
       <x:c r="B28" s="13" t="str">
-        <x:v>Phase 1 Review</x:v>
+        <x:v>Phase 1 Review / Close Execution</x:v>
       </x:c>
       <x:c r="C28" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D28" s="13" t="str">
-        <x:v>Milestone / Review</x:v>
+        <x:v>PMO / Review</x:v>
       </x:c>
       <x:c r="E28" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F28" s="13" t="str">
         <x:v>P0</x:v>
@@ -3183,18 +3200,18 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H28" s="19" t="n">
-        <x:v>46285</x:v>
+        <x:v>46283</x:v>
       </x:c>
       <x:c r="I28" s="19" t="n">
-        <x:v>46285</x:v>
+        <x:v>46288</x:v>
       </x:c>
       <x:c r="J28" s="61" t="n">
         <x:f>IF(OR(H28="",I28=""),"",I28-H28+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K28" s="61" t="n">
         <x:f>IF(OR(H28="",I28=""),"",NETWORKDAYS(H28,I28,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L28,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H28,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I28,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L28" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -3203,16 +3220,16 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N28" s="13" t="str">
-        <x:v>D20</x:v>
+        <x:v>D12; D20</x:v>
       </x:c>
       <x:c r="O28" s="13" t="str">
         <x:v>RISK-05; RISK-13</x:v>
       </x:c>
       <x:c r="P28" s="13" t="str">
-        <x:v>승인된 일정에 Demo/산출물/G3/Known Issue Review를 수행하고 Action 및 승인결과를 기록</x:v>
+        <x:v>G3 결과, Demo, P0 Evidence, Known Issue, P1 이관, Review Action을 승인하고 Phase 1 Close Sign-off 확보</x:v>
       </x:c>
       <x:c r="Q28" s="13" t="str">
-        <x:v>2026-09-20은 일요일이며 Working Days 0이다. D20이 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
+        <x:v>Review 실행일은 D20 결과를 따른다. 09-24~09-25 비근무 전에 09-23 Close를 완료한다.</x:v>
       </x:c>
       <x:c r="R28" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -3224,16 +3241,16 @@
     </x:row>
     <x:row r="29" ht="44" customHeight="1">
       <x:c r="A29" s="13" t="str">
-        <x:v>MS-P1-CLOSE-01</x:v>
+        <x:v>MS-P1-REVIEW-01</x:v>
       </x:c>
       <x:c r="B29" s="13" t="str">
-        <x:v>Phase 1 Close</x:v>
+        <x:v>Phase 1 Review</x:v>
       </x:c>
       <x:c r="C29" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D29" s="13" t="str">
-        <x:v>Milestone / Close</x:v>
+        <x:v>Milestone / Review</x:v>
       </x:c>
       <x:c r="E29" s="13" t="str">
         <x:v>Milestone</x:v>
@@ -3245,10 +3262,10 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H29" s="19" t="n">
-        <x:v>46288</x:v>
+        <x:v>46285</x:v>
       </x:c>
       <x:c r="I29" s="19" t="n">
-        <x:v>46288</x:v>
+        <x:v>46285</x:v>
       </x:c>
       <x:c r="J29" s="61" t="n">
         <x:f>IF(OR(H29="",I29=""),"",I29-H29+1)</x:f>
@@ -3256,7 +3273,7 @@
       </x:c>
       <x:c r="K29" s="61" t="n">
         <x:f>IF(OR(H29="",I29=""),"",NETWORKDAYS(H29,I29,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L29,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H29,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I29,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -3271,10 +3288,10 @@
         <x:v>RISK-05; RISK-13</x:v>
       </x:c>
       <x:c r="P29" s="13" t="str">
-        <x:v>Review Action 처리, P0 승인, P1/Known Issue Owner·Due 이관 및 Phase 1 Close Sign-off 확보</x:v>
+        <x:v>승인된 일정에 Demo/산출물/G3/Known Issue Review를 수행하고 Action 및 승인결과를 기록</x:v>
       </x:c>
       <x:c r="Q29" s="13" t="str">
-        <x:v>09-24~09-25 비근무 전에 종결한다.</x:v>
+        <x:v>2026-09-20은 일요일이며 Working Days 0이다. D20이 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
       </x:c>
       <x:c r="R29" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
@@ -3286,16 +3303,16 @@
     </x:row>
     <x:row r="30" ht="44" customHeight="1">
       <x:c r="A30" s="13" t="str">
-        <x:v>MS-P2-START-01</x:v>
+        <x:v>MS-P1-CLOSE-01</x:v>
       </x:c>
       <x:c r="B30" s="13" t="str">
-        <x:v>Phase 2 Start</x:v>
+        <x:v>Phase 1 Close</x:v>
       </x:c>
       <x:c r="C30" s="13" t="str">
-        <x:v>Phase 2</x:v>
+        <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D30" s="13" t="str">
-        <x:v>Milestone / Start</x:v>
+        <x:v>Milestone / Close</x:v>
       </x:c>
       <x:c r="E30" s="13" t="str">
         <x:v>Milestone</x:v>
@@ -3307,10 +3324,10 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H30" s="19" t="n">
-        <x:v>46293</x:v>
+        <x:v>46288</x:v>
       </x:c>
       <x:c r="I30" s="19" t="n">
-        <x:v>46293</x:v>
+        <x:v>46288</x:v>
       </x:c>
       <x:c r="J30" s="61" t="n">
         <x:f>IF(OR(H30="",I30=""),"",I30-H30+1)</x:f>
@@ -3327,19 +3344,19 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N30" s="13" t="str">
-        <x:v>D10; D21</x:v>
+        <x:v>D20</x:v>
       </x:c>
       <x:c r="O30" s="13" t="str">
-        <x:v>RISK-05; RISK-10; RISK-11</x:v>
+        <x:v>RISK-05; RISK-13</x:v>
       </x:c>
       <x:c r="P30" s="13" t="str">
-        <x:v>Phase 1 Close, Phase 2 계정·권한·일정·P0 범위·OCI Go/No-Go 계획을 확인하고 착수 승인</x:v>
+        <x:v>Review Action 처리, P0 승인, P1/Known Issue Owner·Due 이관 및 Phase 1 Close Sign-off 확보</x:v>
       </x:c>
       <x:c r="Q30" s="13" t="str">
-        <x:v>09-24~09-25 비근무 후 첫 작업일에 착수한다.</x:v>
+        <x:v>09-24~09-25 비근무 전에 종결한다.</x:v>
       </x:c>
       <x:c r="R30" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S30" s="13" t="str">
         <x:f>IF(G30="Done","Complete",IF(OR(H30="",I30=""),"TBD",IF(I30&lt;'Executive Summary'!$B$4,"Past Due",IF(H30&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -3348,19 +3365,19 @@
     </x:row>
     <x:row r="31" ht="44" customHeight="1">
       <x:c r="A31" s="13" t="str">
-        <x:v>P2-ARC-01</x:v>
+        <x:v>MS-P2-START-01</x:v>
       </x:c>
       <x:c r="B31" s="13" t="str">
-        <x:v>Hybrid / OCI / AWS / ROSA Architecture Freeze</x:v>
+        <x:v>Phase 2 Start</x:v>
       </x:c>
       <x:c r="C31" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D31" s="13" t="str">
-        <x:v>Architecture / Hybrid Cloud</x:v>
+        <x:v>Milestone / Start</x:v>
       </x:c>
       <x:c r="E31" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Milestone</x:v>
       </x:c>
       <x:c r="F31" s="13" t="str">
         <x:v>P0</x:v>
@@ -3389,19 +3406,19 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N31" s="13" t="str">
-        <x:v>D10; D21; D22; D23; D25; D26</x:v>
+        <x:v>D10; D21</x:v>
       </x:c>
       <x:c r="O31" s="13" t="str">
-        <x:v>RISK-10; RISK-11; RISK-12; RISK-14; RISK-15</x:v>
+        <x:v>RISK-05; RISK-10; RISK-11</x:v>
       </x:c>
       <x:c r="P31" s="13" t="str">
-        <x:v>OCI Relay·AWS VPC/VPN·ROSA·On-Prem 연계 Architecture, Interface IF-17~IF-20, Security, Decision, Exit Criteria Freeze 승인</x:v>
+        <x:v>Phase 1 Close, Phase 2 계정·권한·일정·P0 범위·OCI Go/No-Go 계획을 확인하고 착수 승인</x:v>
       </x:c>
       <x:c r="Q31" s="13" t="str">
-        <x:v>MS-P2-START-01 직후 완료하며 Phase 2 모든 구현 티켓이 참조하는 Phase 2 OCI/AWS/ROSA Design의 권위 Source를 생성한다.</x:v>
+        <x:v>09-24~09-25 비근무 후 첫 작업일에 착수한다.</x:v>
       </x:c>
       <x:c r="R31" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
       </x:c>
       <x:c r="S31" s="13" t="str">
         <x:f>IF(G31="Done","Complete",IF(OR(H31="",I31=""),"TBD",IF(I31&lt;'Executive Summary'!$B$4,"Past Due",IF(H31&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -3410,16 +3427,16 @@
     </x:row>
     <x:row r="32" ht="44" customHeight="1">
       <x:c r="A32" s="13" t="str">
-        <x:v>P2-IAC-01</x:v>
+        <x:v>P2-ARC-01</x:v>
       </x:c>
       <x:c r="B32" s="13" t="str">
-        <x:v>AWS / ROSA Terraform IaC</x:v>
+        <x:v>Hybrid / OCI / AWS / ROSA Architecture Freeze</x:v>
       </x:c>
       <x:c r="C32" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D32" s="13" t="str">
-        <x:v>Cloud / Terraform</x:v>
+        <x:v>Architecture / Hybrid Cloud</x:v>
       </x:c>
       <x:c r="E32" s="13" t="str">
         <x:v>Task</x:v>
@@ -3434,36 +3451,36 @@
         <x:v>46293</x:v>
       </x:c>
       <x:c r="I32" s="19" t="n">
-        <x:v>46303</x:v>
+        <x:v>46293</x:v>
       </x:c>
       <x:c r="J32" s="61" t="n">
         <x:f>IF(OR(H32="",I32=""),"",I32-H32+1)</x:f>
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K32" s="61" t="n">
         <x:f>IF(OR(H32="",I32=""),"",NETWORKDAYS(H32,I32,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L32,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H32,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I32,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L32" s="13" t="str">
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="M32" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N32" s="13" t="str">
-        <x:v>D10; D21; D25</x:v>
+        <x:v>D10; D21; D22; D23; D25; D26</x:v>
       </x:c>
       <x:c r="O32" s="13" t="str">
-        <x:v>RISK-10; RISK-11; RISK-12</x:v>
+        <x:v>RISK-10; RISK-11; RISK-12; RISK-14; RISK-15</x:v>
       </x:c>
       <x:c r="P32" s="13" t="str">
-        <x:v>AWS VPC 10.20.0.0/16, ROSA 선행 인프라와 IAM/OIDC 최소권한의 Terraform fmt/validate/plan/apply, State·Secret 통제 및 G4 Evidence 확보</x:v>
+        <x:v>OCI Relay·AWS VPC/VPN·ROSA·On-Prem 연계 Architecture, Interface IF-17~IF-20, Security, Decision, Exit Criteria Freeze 승인</x:v>
       </x:c>
       <x:c r="Q32" s="13" t="str">
-        <x:v>10-05는 비근무일이다. OCI Go/No-Go 결과에 따라 VPN 입력과 경로를 갱신한다.</x:v>
+        <x:v>MS-P2-START-01 직후 완료하며 Phase 2 모든 구현 티켓이 참조하는 Phase 2 OCI/AWS/ROSA Design의 권위 Source를 생성한다.</x:v>
       </x:c>
       <x:c r="R32" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S32" s="13" t="str">
         <x:f>IF(G32="Done","Complete",IF(OR(H32="",I32=""),"TBD",IF(I32&lt;'Executive Summary'!$B$4,"Past Due",IF(H32&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -3472,19 +3489,19 @@
     </x:row>
     <x:row r="33" ht="44" customHeight="1">
       <x:c r="A33" s="13" t="str">
-        <x:v>P2-OCI-01</x:v>
+        <x:v>P2-IAC-01</x:v>
       </x:c>
       <x:c r="B33" s="13" t="str">
-        <x:v>OCI Relay Go / No-Go</x:v>
+        <x:v>AWS / ROSA Terraform IaC</x:v>
       </x:c>
       <x:c r="C33" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D33" s="13" t="str">
-        <x:v>Milestone / Hybrid Network</x:v>
+        <x:v>Cloud / Terraform</x:v>
       </x:c>
       <x:c r="E33" s="13" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F33" s="13" t="str">
         <x:v>P0</x:v>
@@ -3496,15 +3513,15 @@
         <x:v>46293</x:v>
       </x:c>
       <x:c r="I33" s="19" t="n">
-        <x:v>46297</x:v>
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="J33" s="61" t="n">
         <x:f>IF(OR(H33="",I33=""),"",I33-H33+1)</x:f>
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K33" s="61" t="n">
         <x:f>IF(OR(H33="",I33=""),"",NETWORKDAYS(H33,I33,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L33,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H33,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I33,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L33" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -3513,16 +3530,16 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N33" s="13" t="str">
-        <x:v>D10; D21</x:v>
+        <x:v>D10; D21; D25</x:v>
       </x:c>
       <x:c r="O33" s="13" t="str">
-        <x:v>RISK-10; RISK-12</x:v>
+        <x:v>RISK-10; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P33" s="13" t="str">
-        <x:v>OCI Relay 가능성·권한·Public Endpoint·IPsec/NAT-T·Route를 검증하고 Primary 또는 승인 Fallback 경로를 선택</x:v>
+        <x:v>AWS VPC 10.20.0.0/16, ROSA 선행 인프라와 IAM/OIDC 최소권한의 Terraform fmt/validate/plan/apply, State·Secret 통제 및 G4 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q33" s="13" t="str">
-        <x:v>10-02 Go/No-Go를 넘기지 않는다. No-Go 시 Vendor Endpoint→AWS EC2+EIP Relay→Overlay 순으로 승인된 Fallback을 선택한다.</x:v>
+        <x:v>10-05는 비근무일이다. OCI Go/No-Go 결과에 따라 VPN 입력과 경로를 갱신한다.</x:v>
       </x:c>
       <x:c r="R33" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -3534,19 +3551,19 @@
     </x:row>
     <x:row r="34" ht="44" customHeight="1">
       <x:c r="A34" s="13" t="str">
-        <x:v>P2-VPN-01</x:v>
+        <x:v>P2-OCI-01</x:v>
       </x:c>
       <x:c r="B34" s="13" t="str">
-        <x:v>OCI Relay / AWS Site-to-Site VPN</x:v>
+        <x:v>OCI Relay Go / No-Go</x:v>
       </x:c>
       <x:c r="C34" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D34" s="13" t="str">
-        <x:v>Hybrid Network / VPN</x:v>
+        <x:v>Milestone / Hybrid Network</x:v>
       </x:c>
       <x:c r="E34" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="F34" s="13" t="str">
         <x:v>P0</x:v>
@@ -3555,14 +3572,14 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H34" s="19" t="n">
-        <x:v>46296</x:v>
+        <x:v>46293</x:v>
       </x:c>
       <x:c r="I34" s="19" t="n">
-        <x:v>46303</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="J34" s="61" t="n">
         <x:f>IF(OR(H34="",I34=""),"",I34-H34+1)</x:f>
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K34" s="61" t="n">
         <x:f>IF(OR(H34="",I34=""),"",NETWORKDAYS(H34,I34,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L34,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H34,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I34,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
@@ -3578,13 +3595,13 @@
         <x:v>D10; D21</x:v>
       </x:c>
       <x:c r="O34" s="13" t="str">
-        <x:v>RISK-04; RISK-10; RISK-12</x:v>
+        <x:v>RISK-10; RISK-12</x:v>
       </x:c>
       <x:c r="P34" s="13" t="str">
-        <x:v>승인 Transit 경로의 Tunnel UP, On-Prem↔VPC Route, UDP 500/4500/IPsec, Source·승인 TCP Path 및 장애 Evidence 확보</x:v>
+        <x:v>OCI Relay 가능성·권한·Public Endpoint·IPsec/NAT-T·Route를 검증하고 Primary 또는 승인 Fallback 경로를 선택</x:v>
       </x:c>
       <x:c r="Q34" s="13" t="str">
-        <x:v>10-05는 비근무일이다. OCI No-Go 시 D21에서 승인된 Fallback만 사용한다.</x:v>
+        <x:v>10-02 Go/No-Go를 넘기지 않는다. No-Go 시 Vendor Endpoint→AWS EC2+EIP Relay→Overlay 순으로 승인된 Fallback을 선택한다.</x:v>
       </x:c>
       <x:c r="R34" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -3596,16 +3613,16 @@
     </x:row>
     <x:row r="35" ht="44" customHeight="1">
       <x:c r="A35" s="13" t="str">
-        <x:v>P2-ROSA-01</x:v>
+        <x:v>P2-VPN-01</x:v>
       </x:c>
       <x:c r="B35" s="13" t="str">
-        <x:v>ROSA Platform / Security</x:v>
+        <x:v>OCI Relay / AWS Site-to-Site VPN</x:v>
       </x:c>
       <x:c r="C35" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D35" s="13" t="str">
-        <x:v>OpenShift / ROSA</x:v>
+        <x:v>Hybrid Network / VPN</x:v>
       </x:c>
       <x:c r="E35" s="13" t="str">
         <x:v>Task</x:v>
@@ -3617,36 +3634,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H35" s="19" t="n">
-        <x:v>46301</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="I35" s="19" t="n">
-        <x:v>46311</x:v>
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="J35" s="61" t="n">
         <x:f>IF(OR(H35="",I35=""),"",I35-H35+1)</x:f>
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K35" s="61" t="n">
         <x:f>IF(OR(H35="",I35=""),"",NETWORKDAYS(H35,I35,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L35,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H35,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I35,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L35" s="13" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="M35" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
-      <x:c r="M35" s="13" t="str">
-        <x:v>이권욱</x:v>
-      </x:c>
       <x:c r="N35" s="13" t="str">
-        <x:v>D10; D12; D17; D21</x:v>
+        <x:v>D10; D21</x:v>
       </x:c>
       <x:c r="O35" s="13" t="str">
-        <x:v>RISK-07; RISK-10; RISK-11; RISK-12</x:v>
+        <x:v>RISK-04; RISK-10; RISK-12</x:v>
       </x:c>
       <x:c r="P35" s="13" t="str">
-        <x:v>ROSA Cluster Ready, Namespace/RBAC/NetworkPolicy/SecurityContext, Hybrid Route 및 Application 배포 선행조건과 G5 Evidence 확보</x:v>
+        <x:v>승인 Transit 경로의 Tunnel UP, On-Prem↔VPC Route, UDP 500/4500/IPsec, Source·승인 TCP Path 및 장애 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q35" s="13" t="str">
-        <x:v>10-09는 비근무일이다. 계정·Quota·리전 전제는 G4 이전에 확인하고 Cluster 범위를 최소화한다.</x:v>
+        <x:v>10-05는 비근무일이다. OCI No-Go 시 D21에서 승인된 Fallback만 사용한다.</x:v>
       </x:c>
       <x:c r="R35" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -3658,19 +3675,19 @@
     </x:row>
     <x:row r="36" ht="44" customHeight="1">
       <x:c r="A36" s="13" t="str">
-        <x:v>MS-G4-01</x:v>
+        <x:v>P2-ROSA-01</x:v>
       </x:c>
       <x:c r="B36" s="13" t="str">
-        <x:v>G4 Cloud / VPN Ready</x:v>
+        <x:v>ROSA Platform / Security</x:v>
       </x:c>
       <x:c r="C36" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D36" s="13" t="str">
-        <x:v>Milestone / Cloud &amp; VPN</x:v>
+        <x:v>OpenShift / ROSA</x:v>
       </x:c>
       <x:c r="E36" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F36" s="13" t="str">
         <x:v>P0</x:v>
@@ -3679,36 +3696,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H36" s="19" t="n">
-        <x:v>46303</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="I36" s="19" t="n">
-        <x:v>46303</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="J36" s="61" t="n">
         <x:f>IF(OR(H36="",I36=""),"",I36-H36+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K36" s="61" t="n">
         <x:f>IF(OR(H36="",I36=""),"",NETWORKDAYS(H36,I36,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L36,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H36,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I36,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L36" s="13" t="str">
+        <x:v>이하영</x:v>
+      </x:c>
+      <x:c r="M36" s="13" t="str">
         <x:v>이권욱</x:v>
       </x:c>
-      <x:c r="M36" s="13" t="str">
-        <x:v>이하영</x:v>
-      </x:c>
       <x:c r="N36" s="13" t="str">
-        <x:v>D21</x:v>
+        <x:v>D10; D12; D17; D21</x:v>
       </x:c>
       <x:c r="O36" s="13" t="str">
-        <x:v>RISK-10; RISK-11; RISK-12</x:v>
+        <x:v>RISK-07; RISK-10; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P36" s="13" t="str">
-        <x:v>Terraform 인프라, 승인 Transit/VPN, Route/Security, ROSA 선행조건 및 승인 TCP 경로 준비도 승인</x:v>
+        <x:v>ROSA Cluster Ready, Namespace/RBAC/NetworkPolicy/SecurityContext, Hybrid Route 및 Application 배포 선행조건과 G5 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q36" s="13" t="str">
-        <x:v>10-05 비근무를 반영한다. OCI No-Go 시 승인 Fallback 기준으로 판정한다.</x:v>
+        <x:v>10-09는 비근무일이다. 계정·Quota·리전 전제는 G4 이전에 확인하고 Cluster 범위를 최소화한다.</x:v>
       </x:c>
       <x:c r="R36" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -3720,39 +3737,39 @@
     </x:row>
     <x:row r="37" ht="44" customHeight="1">
       <x:c r="A37" s="13" t="str">
-        <x:v>DEC-P2-DNS-01</x:v>
+        <x:v>MS-G4-01</x:v>
       </x:c>
       <x:c r="B37" s="13" t="str">
-        <x:v>Hybrid DNS Scope Decision</x:v>
+        <x:v>G4 Cloud / VPN Ready</x:v>
       </x:c>
       <x:c r="C37" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D37" s="13" t="str">
-        <x:v>Architecture / DNS</x:v>
+        <x:v>Milestone / Cloud &amp; VPN</x:v>
       </x:c>
       <x:c r="E37" s="13" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Milestone</x:v>
       </x:c>
       <x:c r="F37" s="13" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G37" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H37" s="19" t="n">
-        <x:v>46307</x:v>
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="I37" s="19" t="n">
-        <x:v>46311</x:v>
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="J37" s="61" t="n">
         <x:f>IF(OR(H37="",I37=""),"",I37-H37+1)</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K37" s="61" t="n">
         <x:f>IF(OR(H37="",I37=""),"",NETWORKDAYS(H37,I37,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L37,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H37,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I37,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L37" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -3761,16 +3778,16 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N37" s="13" t="str">
-        <x:v>D11; D23</x:v>
+        <x:v>D21</x:v>
       </x:c>
       <x:c r="O37" s="13" t="str">
-        <x:v>RISK-10; RISK-12</x:v>
+        <x:v>RISK-10; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P37" s="13" t="str">
-        <x:v>P0 IP Endpoint 유지 또는 Hybrid DNS P1 적용을 확정하고 Resolver/Forwarding/Zone/Route/테스트·N/A 근거를 승인</x:v>
+        <x:v>Terraform 인프라, 승인 Transit/VPN, Route/Security, ROSA 선행조건 및 승인 TCP 경로 준비도 승인</x:v>
       </x:c>
       <x:c r="Q37" s="13" t="str">
-        <x:v>Hybrid P0 E2E는 IP Endpoint를 허용하므로 본 P1 결정 미완료가 G5/G6를 자동 차단하지 않는다.</x:v>
+        <x:v>10-05 비근무를 반영한다. OCI No-Go 시 승인 Fallback 기준으로 판정한다.</x:v>
       </x:c>
       <x:c r="R37" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -3782,16 +3799,16 @@
     </x:row>
     <x:row r="38" ht="44" customHeight="1">
       <x:c r="A38" s="13" t="str">
-        <x:v>DEC-P2-OP-01</x:v>
+        <x:v>DEC-P2-DNS-01</x:v>
       </x:c>
       <x:c r="B38" s="13" t="str">
-        <x:v>Operator Supply Chain Scope Decision</x:v>
+        <x:v>Hybrid DNS Scope Decision</x:v>
       </x:c>
       <x:c r="C38" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D38" s="13" t="str">
-        <x:v>Architecture / Operator Supply Chain</x:v>
+        <x:v>Architecture / DNS</x:v>
       </x:c>
       <x:c r="E38" s="13" t="str">
         <x:v>Decision</x:v>
@@ -3817,25 +3834,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L38" s="13" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="M38" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
-      <x:c r="M38" s="13" t="str">
-        <x:v>이권욱, 이재환</x:v>
-      </x:c>
       <x:c r="N38" s="13" t="str">
-        <x:v>D22; D26</x:v>
+        <x:v>D11; D23</x:v>
       </x:c>
       <x:c r="O38" s="13" t="str">
-        <x:v>RISK-06; RISK-11; RISK-15</x:v>
+        <x:v>RISK-10; RISK-12</x:v>
       </x:c>
       <x:c r="P38" s="13" t="str">
-        <x:v>ROSA Operator 공급망을 Direct Catalog 또는 oc-mirror/Harbor/Custom CatalogSource 중 하나로 결정하고 구현·N/A 기준 승인</x:v>
+        <x:v>P0 IP Endpoint 유지 또는 Hybrid DNS P1 적용을 확정하고 Resolver/Forwarding/Zone/Route/테스트·N/A 근거를 승인</x:v>
       </x:c>
       <x:c r="Q38" s="13" t="str">
-        <x:v>D26에서 Direct Catalog 선택 시 P2-OP-01은 Cancelled 처리하고, Mirror 선택 시 P2-OP-01을 활성화한다.</x:v>
+        <x:v>Hybrid P0 E2E는 IP Endpoint를 허용하므로 본 P1 결정 미완료가 G5/G6를 자동 차단하지 않는다.</x:v>
       </x:c>
       <x:c r="R38" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
       </x:c>
       <x:c r="S38" s="13" t="str">
         <x:f>IF(G38="Done","Complete",IF(OR(H38="",I38=""),"TBD",IF(I38&lt;'Executive Summary'!$B$4,"Past Due",IF(H38&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -3844,22 +3861,22 @@
     </x:row>
     <x:row r="39" ht="44" customHeight="1">
       <x:c r="A39" s="13" t="str">
-        <x:v>DEC-P2-REG-01</x:v>
+        <x:v>DEC-P2-OP-01</x:v>
       </x:c>
       <x:c r="B39" s="13" t="str">
-        <x:v>ROSA Image Registry Source Decision</x:v>
+        <x:v>Operator Supply Chain Scope Decision</x:v>
       </x:c>
       <x:c r="C39" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D39" s="13" t="str">
-        <x:v>Architecture / Registry</x:v>
+        <x:v>Architecture / Operator Supply Chain</x:v>
       </x:c>
       <x:c r="E39" s="13" t="str">
         <x:v>Decision</x:v>
       </x:c>
       <x:c r="F39" s="13" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G39" s="13" t="str">
         <x:v>To Do</x:v>
@@ -3885,19 +3902,19 @@
         <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N39" s="13" t="str">
-        <x:v>D22</x:v>
+        <x:v>D22; D26</x:v>
       </x:c>
       <x:c r="O39" s="13" t="str">
-        <x:v>RISK-06; RISK-10; RISK-11; RISK-12</x:v>
+        <x:v>RISK-06; RISK-11; RISK-15</x:v>
       </x:c>
       <x:c r="P39" s="13" t="str">
-        <x:v>ROSA Image Source를 On-Prem Harbor 또는 승인 Cloud Registry로 확정하고 Route·TLS·Credential·비용·Fallback을 승인</x:v>
+        <x:v>ROSA Operator 공급망을 Direct Catalog 또는 oc-mirror/Harbor/Custom CatalogSource 중 하나로 결정하고 구현·N/A 기준 승인</x:v>
       </x:c>
       <x:c r="Q39" s="13" t="str">
-        <x:v>기준선의 ROSA→Harbor는 Optional이다. P2-APP-01 최종 Image 경로 전 10-16까지 확정한다.</x:v>
+        <x:v>D26에서 Direct Catalog 선택 시 P2-OP-01은 Cancelled 처리하고, Mirror 선택 시 P2-OP-01을 활성화한다.</x:v>
       </x:c>
       <x:c r="R39" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S39" s="13" t="str">
         <x:f>IF(G39="Done","Complete",IF(OR(H39="",I39=""),"TBD",IF(I39&lt;'Executive Summary'!$B$4,"Past Due",IF(H39&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -3906,19 +3923,19 @@
     </x:row>
     <x:row r="40" ht="44" customHeight="1">
       <x:c r="A40" s="13" t="str">
-        <x:v>P2-APP-01</x:v>
+        <x:v>DEC-P2-REG-01</x:v>
       </x:c>
       <x:c r="B40" s="13" t="str">
-        <x:v>ROSA Application Deployment</x:v>
+        <x:v>ROSA Image Registry Source Decision</x:v>
       </x:c>
       <x:c r="C40" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D40" s="13" t="str">
-        <x:v>Application / OpenShift</x:v>
+        <x:v>Architecture / Registry</x:v>
       </x:c>
       <x:c r="E40" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="F40" s="13" t="str">
         <x:v>P0</x:v>
@@ -3941,22 +3958,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L40" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="M40" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N40" s="13" t="str">
-        <x:v>D03; D22</x:v>
+        <x:v>D22</x:v>
       </x:c>
       <x:c r="O40" s="13" t="str">
-        <x:v>RISK-06; RISK-07; RISK-11</x:v>
+        <x:v>RISK-06; RISK-10; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P40" s="13" t="str">
-        <x:v>Phase 1과 동일한 transaction-api/fds-engine Image/Contract를 ROSA에 배포하고 Route/Health/Rule 기본검증 PASS</x:v>
+        <x:v>ROSA Image Source를 On-Prem Harbor 또는 승인 Cloud Registry로 확정하고 Route·TLS·Credential·비용·Fallback을 승인</x:v>
       </x:c>
       <x:c r="Q40" s="13" t="str">
-        <x:v>Image Source는 D22 결정에 따르며 Harbor 사용을 사전 가정하지 않는다. Manifest/Image 계약은 P2-CICD-01의 Runner 기반 ROSA Delivery에 연결한다.</x:v>
+        <x:v>기준선의 ROSA→Harbor는 Optional이다. P2-APP-01 최종 Image 경로 전 10-16까지 확정한다.</x:v>
       </x:c>
       <x:c r="R40" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -3968,16 +3985,16 @@
     </x:row>
     <x:row r="41" ht="44" customHeight="1">
       <x:c r="A41" s="13" t="str">
-        <x:v>P2-OADP-01</x:v>
+        <x:v>P2-APP-01</x:v>
       </x:c>
       <x:c r="B41" s="13" t="str">
-        <x:v>OADP / S3 Backup</x:v>
+        <x:v>ROSA Application Deployment</x:v>
       </x:c>
       <x:c r="C41" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D41" s="13" t="str">
-        <x:v>Backup / OpenShift</x:v>
+        <x:v>Application / OpenShift</x:v>
       </x:c>
       <x:c r="E41" s="13" t="str">
         <x:v>Task</x:v>
@@ -3989,36 +4006,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H41" s="19" t="n">
-        <x:v>46310</x:v>
+        <x:v>46307</x:v>
       </x:c>
       <x:c r="I41" s="19" t="n">
-        <x:v>46317</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="J41" s="61" t="n">
         <x:f>IF(OR(H41="",I41=""),"",I41-H41+1)</x:f>
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K41" s="61" t="n">
         <x:f>IF(OR(H41="",I41=""),"",NETWORKDAYS(H41,I41,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L41,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H41,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I41,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L41" s="13" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="M41" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
-      <x:c r="M41" s="13" t="str">
-        <x:v>이권욱</x:v>
-      </x:c>
       <x:c r="N41" s="13" t="str">
-        <x:v>D12</x:v>
+        <x:v>D03; D22</x:v>
       </x:c>
       <x:c r="O41" s="13" t="str">
-        <x:v>RISK-11; RISK-12</x:v>
+        <x:v>RISK-06; RISK-07; RISK-11</x:v>
       </x:c>
       <x:c r="P41" s="13" t="str">
-        <x:v>OADP→S3 443, Backup 대상·Credential·Schedule, Restore 또는 승인 복구검증과 Evidence 확보</x:v>
+        <x:v>Phase 1과 동일한 transaction-api/fds-engine Image/Contract를 ROSA에 배포하고 Route/Health/Rule 기본검증 PASS</x:v>
       </x:c>
       <x:c r="Q41" s="13" t="str">
-        <x:v>Backup 생성만으로 DONE 처리하지 않고 Restore 또는 승인된 복구 검증이 필요하다.</x:v>
+        <x:v>Image Source는 D22 결정에 따르며 Harbor 사용을 사전 가정하지 않는다. Manifest/Image 계약은 P2-CICD-01의 Runner 기반 ROSA Delivery에 연결한다.</x:v>
       </x:c>
       <x:c r="R41" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -4030,19 +4047,19 @@
     </x:row>
     <x:row r="42" ht="44" customHeight="1">
       <x:c r="A42" s="13" t="str">
-        <x:v>MS-G5-01</x:v>
+        <x:v>P2-OADP-01</x:v>
       </x:c>
       <x:c r="B42" s="13" t="str">
-        <x:v>G5 ROSA Application Ready</x:v>
+        <x:v>OADP / S3 Backup</x:v>
       </x:c>
       <x:c r="C42" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D42" s="13" t="str">
-        <x:v>Milestone / ROSA Application</x:v>
+        <x:v>Backup / OpenShift</x:v>
       </x:c>
       <x:c r="E42" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F42" s="13" t="str">
         <x:v>P0</x:v>
@@ -4051,36 +4068,36 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H42" s="19" t="n">
-        <x:v>46311</x:v>
+        <x:v>46310</x:v>
       </x:c>
       <x:c r="I42" s="19" t="n">
-        <x:v>46311</x:v>
+        <x:v>46317</x:v>
       </x:c>
       <x:c r="J42" s="61" t="n">
         <x:f>IF(OR(H42="",I42=""),"",I42-H42+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K42" s="61" t="n">
         <x:f>IF(OR(H42="",I42=""),"",NETWORKDAYS(H42,I42,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L42,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H42,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I42,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L42" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="M42" s="13" t="str">
-        <x:v>이권욱, 이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="N42" s="13" t="str">
-        <x:v>D22; D23; D25; D26</x:v>
+        <x:v>D12</x:v>
       </x:c>
       <x:c r="O42" s="13" t="str">
-        <x:v>RISK-06; RISK-07; RISK-11; RISK-12</x:v>
+        <x:v>RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P42" s="13" t="str">
-        <x:v>ROSA Platform/Security, P2-CICD-01 Runner 기반 Delivery, transaction-api/fds-engine Health·Rule Smoke Test와 Registry/DNS/Operator Decision 상태 승인</x:v>
+        <x:v>OADP→S3 443, Backup 대상·Credential·Schedule, Restore 또는 승인 복구검증과 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q42" s="13" t="str">
-        <x:v>Registry는 D22, Hybrid DNS는 D23을 따른다. D23 미적용은 P0 IP Endpoint 사용 시 Non-blocker다.</x:v>
+        <x:v>Backup 생성만으로 DONE 처리하지 않고 Restore 또는 승인된 복구 검증이 필요하다.</x:v>
       </x:c>
       <x:c r="R42" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -4092,19 +4109,19 @@
     </x:row>
     <x:row r="43" ht="44" customHeight="1">
       <x:c r="A43" s="13" t="str">
-        <x:v>P2-CICD-01</x:v>
+        <x:v>MS-G5-01</x:v>
       </x:c>
       <x:c r="B43" s="13" t="str">
-        <x:v>Runner to ROSA Delivery</x:v>
+        <x:v>G5 ROSA Application Ready</x:v>
       </x:c>
       <x:c r="C43" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D43" s="13" t="str">
-        <x:v>CI/CD / OpenShift Delivery</x:v>
+        <x:v>Milestone / ROSA Application</x:v>
       </x:c>
       <x:c r="E43" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Milestone</x:v>
       </x:c>
       <x:c r="F43" s="13" t="str">
         <x:v>P0</x:v>
@@ -4116,36 +4133,36 @@
         <x:v>46311</x:v>
       </x:c>
       <x:c r="I43" s="19" t="n">
-        <x:v>46314</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="J43" s="61" t="n">
         <x:f>IF(OR(H43="",I43=""),"",I43-H43+1)</x:f>
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K43" s="61" t="n">
         <x:f>IF(OR(H43="",I43=""),"",NETWORKDAYS(H43,I43,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L43,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H43,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I43,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L43" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="M43" s="13" t="str">
-        <x:v>이하영, 이재환</x:v>
+        <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N43" s="13" t="str">
-        <x:v>D22; D25</x:v>
+        <x:v>D22; D23; D25; D26</x:v>
       </x:c>
       <x:c r="O43" s="13" t="str">
-        <x:v>RISK-06; RISK-08; RISK-11; RISK-14</x:v>
+        <x:v>RISK-06; RISK-07; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P43" s="13" t="str">
-        <x:v>GitHub→Self-hosted Runner→승인 Registry→ROSA Deploy→Health/Rule Smoke Test 흐름과 실패 시 배포차단 Evidence 확보</x:v>
+        <x:v>ROSA Platform/Security, P2-CICD-01 Runner 기반 Delivery, transaction-api/fds-engine Health·Rule Smoke Test와 Registry/DNS/Operator Decision 상태 승인</x:v>
       </x:c>
       <x:c r="Q43" s="13" t="str">
-        <x:v>P2-ROSA-01과 P2-APP-01의 Manifest/Image 계약을 사용하고 Registry는 D22 결과를 따른다. G5 ROSA Application Ready에 연결한다.</x:v>
+        <x:v>Registry는 D22, Hybrid DNS는 D23을 따른다. D23 미적용은 P0 IP Endpoint 사용 시 Non-blocker다.</x:v>
       </x:c>
       <x:c r="R43" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
       </x:c>
       <x:c r="S43" s="13" t="str">
         <x:f>IF(G43="Done","Complete",IF(OR(H43="",I43=""),"TBD",IF(I43&lt;'Executive Summary'!$B$4,"Past Due",IF(H43&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -4154,16 +4171,16 @@
     </x:row>
     <x:row r="44" ht="44" customHeight="1">
       <x:c r="A44" s="13" t="str">
-        <x:v>P2-HYB-01</x:v>
+        <x:v>P2-CICD-01</x:v>
       </x:c>
       <x:c r="B44" s="13" t="str">
-        <x:v>Hybrid DB / Registry Integration</x:v>
+        <x:v>Runner to ROSA Delivery</x:v>
       </x:c>
       <x:c r="C44" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D44" s="13" t="str">
-        <x:v>Hybrid Integration</x:v>
+        <x:v>CI/CD / OpenShift Delivery</x:v>
       </x:c>
       <x:c r="E44" s="13" t="str">
         <x:v>Task</x:v>
@@ -4178,36 +4195,36 @@
         <x:v>46311</x:v>
       </x:c>
       <x:c r="I44" s="19" t="n">
-        <x:v>46317</x:v>
+        <x:v>46314</x:v>
       </x:c>
       <x:c r="J44" s="61" t="n">
         <x:f>IF(OR(H44="",I44=""),"",I44-H44+1)</x:f>
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K44" s="61" t="n">
         <x:f>IF(OR(H44="",I44=""),"",NETWORKDAYS(H44,I44,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L44,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H44,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I44,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L44" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="M44" s="13" t="str">
-        <x:v>이권욱, 이하영</x:v>
+        <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N44" s="13" t="str">
-        <x:v>D21; D22; D23</x:v>
+        <x:v>D22; D25</x:v>
       </x:c>
       <x:c r="O44" s="13" t="str">
-        <x:v>RISK-09; RISK-10; RISK-11; RISK-12</x:v>
+        <x:v>RISK-06; RISK-08; RISK-11; RISK-14</x:v>
       </x:c>
       <x:c r="P44" s="13" t="str">
-        <x:v>ROSA→On-Prem db01 .55:5432와 승인 Registry 경로의 Route·Security·Source·Application 통합 검증 PASS</x:v>
+        <x:v>GitHub→Self-hosted Runner→승인 Registry→ROSA Deploy→Health/Rule Smoke Test 흐름과 실패 시 배포차단 Evidence 확보</x:v>
       </x:c>
       <x:c r="Q44" s="13" t="str">
-        <x:v>Harbor는 D22에 따라 사용 또는 Cancelled 처리한다. Hybrid DNS는 D23에 따라 적용 또는 IP Endpoint로 검증한다.</x:v>
+        <x:v>P2-ROSA-01과 P2-APP-01의 Manifest/Image 계약을 사용하고 Registry는 D22 결과를 따른다. G5 ROSA Application Ready에 연결한다.</x:v>
       </x:c>
       <x:c r="R44" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S44" s="13" t="str">
         <x:f>IF(G44="Done","Complete",IF(OR(H44="",I44=""),"TBD",IF(I44&lt;'Executive Summary'!$B$4,"Past Due",IF(H44&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -4216,60 +4233,60 @@
     </x:row>
     <x:row r="45" ht="44" customHeight="1">
       <x:c r="A45" s="13" t="str">
-        <x:v>P2-DNS-01</x:v>
+        <x:v>P2-HYB-01</x:v>
       </x:c>
       <x:c r="B45" s="13" t="str">
-        <x:v>Hybrid DNS Implementation Conditional</x:v>
+        <x:v>Hybrid DB / Registry Integration</x:v>
       </x:c>
       <x:c r="C45" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D45" s="13" t="str">
-        <x:v>DNS / Hybrid Integration</x:v>
+        <x:v>Hybrid Integration</x:v>
       </x:c>
       <x:c r="E45" s="13" t="str">
         <x:v>Task</x:v>
       </x:c>
       <x:c r="F45" s="13" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G45" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H45" s="19" t="n">
-        <x:v>46314</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="I45" s="19" t="n">
-        <x:v>46315</x:v>
+        <x:v>46317</x:v>
       </x:c>
       <x:c r="J45" s="61" t="n">
         <x:f>IF(OR(H45="",I45=""),"",I45-H45+1)</x:f>
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K45" s="61" t="n">
         <x:f>IF(OR(H45="",I45=""),"",NETWORKDAYS(H45,I45,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L45,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H45,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I45,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L45" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="M45" s="13" t="str">
-        <x:v>이하영, 이재환</x:v>
+        <x:v>이권욱, 이하영</x:v>
       </x:c>
       <x:c r="N45" s="13" t="str">
-        <x:v>D11; D23</x:v>
+        <x:v>D21; D22; D23</x:v>
       </x:c>
       <x:c r="O45" s="13" t="str">
-        <x:v>RISK-10; RISK-12; RISK-15</x:v>
+        <x:v>RISK-09; RISK-10; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P45" s="13" t="str">
-        <x:v>D23이 Hybrid DNS를 선택한 경우 Resolver/Conditional Forwarding/Route/Query Test PASS; IP Endpoint 유지 시 N/A 근거 승인</x:v>
+        <x:v>ROSA→On-Prem db01 .55:5432와 승인 Registry 경로의 Route·Security·Source·Application 통합 검증 PASS</x:v>
       </x:c>
       <x:c r="Q45" s="13" t="str">
-        <x:v>DEC-P2-DNS-01 / D23 결정 결과가 미구현이면 Status=Cancelled와 결정 근거를 기록한다. 구현 시 Hybrid E2E IP Endpoint에 대한 영향을 검증한다.</x:v>
+        <x:v>Harbor는 D22에 따라 사용 또는 Cancelled 처리한다. Hybrid DNS는 D23에 따라 적용 또는 IP Endpoint로 검증한다.</x:v>
       </x:c>
       <x:c r="R45" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
       </x:c>
       <x:c r="S45" s="13" t="str">
         <x:f>IF(G45="Done","Complete",IF(OR(H45="",I45=""),"TBD",IF(I45&lt;'Executive Summary'!$B$4,"Past Due",IF(H45&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -4278,22 +4295,22 @@
     </x:row>
     <x:row r="46" ht="44" customHeight="1">
       <x:c r="A46" s="13" t="str">
-        <x:v>P2-DOC-01</x:v>
+        <x:v>P2-DNS-01</x:v>
       </x:c>
       <x:c r="B46" s="13" t="str">
-        <x:v>Cloud / Hybrid Deliverable Freeze</x:v>
+        <x:v>Hybrid DNS Implementation Conditional</x:v>
       </x:c>
       <x:c r="C46" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D46" s="13" t="str">
-        <x:v>PMO / Documentation</x:v>
+        <x:v>DNS / Hybrid Integration</x:v>
       </x:c>
       <x:c r="E46" s="13" t="str">
         <x:v>Task</x:v>
       </x:c>
       <x:c r="F46" s="13" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G46" s="13" t="str">
         <x:v>To Do</x:v>
@@ -4302,15 +4319,15 @@
         <x:v>46314</x:v>
       </x:c>
       <x:c r="I46" s="19" t="n">
-        <x:v>46318</x:v>
+        <x:v>46315</x:v>
       </x:c>
       <x:c r="J46" s="61" t="n">
         <x:f>IF(OR(H46="",I46=""),"",I46-H46+1)</x:f>
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K46" s="61" t="n">
         <x:f>IF(OR(H46="",I46=""),"",NETWORKDAYS(H46,I46,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L46,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H46,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I46,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L46" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -4319,19 +4336,19 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N46" s="13" t="str">
-        <x:v>D12; D21; D22; D23; D24; D25; D26</x:v>
+        <x:v>D11; D23</x:v>
       </x:c>
       <x:c r="O46" s="13" t="str">
-        <x:v>RISK-10; RISK-11; RISK-12; RISK-13</x:v>
+        <x:v>RISK-10; RISK-12; RISK-15</x:v>
       </x:c>
       <x:c r="P46" s="13" t="str">
-        <x:v>Terraform/ROSA/VPN/Hybrid Architecture, CI/CD, Test/Evidence, Backup/Recovery Runbook, D22/D23/D26 Decision, Known Issue 및 Deliverable Freeze 승인</x:v>
+        <x:v>D23이 Hybrid DNS를 선택한 경우 Resolver/Conditional Forwarding/Route/Query Test PASS; IP Endpoint 유지 시 N/A 근거 승인</x:v>
       </x:c>
       <x:c r="Q46" s="13" t="str">
-        <x:v>10-23 Deliverable Freeze와 DEC-CAL-P2-01을 함께 완료한다.</x:v>
+        <x:v>DEC-P2-DNS-01 / D23 결정 결과가 미구현이면 Status=Cancelled와 결정 근거를 기록한다. 구현 시 Hybrid E2E IP Endpoint에 대한 영향을 검증한다.</x:v>
       </x:c>
       <x:c r="R46" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S46" s="13" t="str">
         <x:f>IF(G46="Done","Complete",IF(OR(H46="",I46=""),"TBD",IF(I46&lt;'Executive Summary'!$B$4,"Past Due",IF(H46&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -4340,16 +4357,16 @@
     </x:row>
     <x:row r="47" ht="44" customHeight="1">
       <x:c r="A47" s="13" t="str">
-        <x:v>P2-E2E-01</x:v>
+        <x:v>P2-DOC-01</x:v>
       </x:c>
       <x:c r="B47" s="13" t="str">
-        <x:v>Hybrid E2E / Regression</x:v>
+        <x:v>Cloud / Hybrid Deliverable Freeze</x:v>
       </x:c>
       <x:c r="C47" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D47" s="13" t="str">
-        <x:v>QA / Hybrid E2E</x:v>
+        <x:v>PMO / Documentation</x:v>
       </x:c>
       <x:c r="E47" s="13" t="str">
         <x:v>Task</x:v>
@@ -4364,33 +4381,33 @@
         <x:v>46314</x:v>
       </x:c>
       <x:c r="I47" s="19" t="n">
-        <x:v>46317</x:v>
+        <x:v>46318</x:v>
       </x:c>
       <x:c r="J47" s="61" t="n">
         <x:f>IF(OR(H47="",I47=""),"",I47-H47+1)</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K47" s="61" t="n">
         <x:f>IF(OR(H47="",I47=""),"",NETWORKDAYS(H47,I47,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L47,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H47,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I47,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L47" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="M47" s="13" t="str">
-        <x:v>이권욱, 이하영</x:v>
+        <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N47" s="13" t="str">
-        <x:v>D21; D22; D23</x:v>
+        <x:v>D12; D21; D22; D23; D24; D25; D26</x:v>
       </x:c>
       <x:c r="O47" s="13" t="str">
-        <x:v>RISK-09; RISK-10; RISK-11; RISK-12</x:v>
+        <x:v>RISK-10; RISK-11; RISK-12; RISK-13</x:v>
       </x:c>
       <x:c r="P47" s="13" t="str">
-        <x:v>ROSA transaction-api→fds-engine→On-Prem PostgreSQL Hybrid E2E, Rule/Negative/Recovery Regression PASS와 Critical Issue 0</x:v>
+        <x:v>Terraform/ROSA/VPN/Hybrid Architecture, CI/CD, Test/Evidence, Backup/Recovery Runbook, D22/D23/D26 Decision, Known Issue 및 Deliverable Freeze 승인</x:v>
       </x:c>
       <x:c r="Q47" s="13" t="str">
-        <x:v>IP Endpoint와 Registry N/A 여부는 승인 Decision 결과를 Expected에 반영한다.</x:v>
+        <x:v>10-23 Deliverable Freeze와 DEC-CAL-P2-01을 함께 완료한다.</x:v>
       </x:c>
       <x:c r="R47" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -4402,22 +4419,22 @@
     </x:row>
     <x:row r="48" ht="44" customHeight="1">
       <x:c r="A48" s="13" t="str">
-        <x:v>P2-OP-01</x:v>
+        <x:v>P2-E2E-01</x:v>
       </x:c>
       <x:c r="B48" s="13" t="str">
-        <x:v>Operator Supply Chain Implementation Conditional</x:v>
+        <x:v>Hybrid E2E / Regression</x:v>
       </x:c>
       <x:c r="C48" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D48" s="13" t="str">
-        <x:v>Operator Supply Chain</x:v>
+        <x:v>QA / Hybrid E2E</x:v>
       </x:c>
       <x:c r="E48" s="13" t="str">
         <x:v>Task</x:v>
       </x:c>
       <x:c r="F48" s="13" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G48" s="13" t="str">
         <x:v>To Do</x:v>
@@ -4426,36 +4443,36 @@
         <x:v>46314</x:v>
       </x:c>
       <x:c r="I48" s="19" t="n">
-        <x:v>46315</x:v>
+        <x:v>46317</x:v>
       </x:c>
       <x:c r="J48" s="61" t="n">
         <x:f>IF(OR(H48="",I48=""),"",I48-H48+1)</x:f>
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K48" s="61" t="n">
         <x:f>IF(OR(H48="",I48=""),"",NETWORKDAYS(H48,I48,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L48,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H48,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I48,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L48" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="M48" s="13" t="str">
-        <x:v>이권욱, 이재환</x:v>
+        <x:v>이권욱, 이하영</x:v>
       </x:c>
       <x:c r="N48" s="13" t="str">
-        <x:v>D22; D26</x:v>
+        <x:v>D21; D22; D23</x:v>
       </x:c>
       <x:c r="O48" s="13" t="str">
-        <x:v>RISK-06; RISK-11; RISK-15</x:v>
+        <x:v>RISK-09; RISK-10; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P48" s="13" t="str">
-        <x:v>D26이 Mirror를 선택한 경우 oc-mirror ImageSet·Harbor Push·Custom CatalogSource·Package 조회 PASS; Direct Catalog 선택 시 N/A 근거 승인</x:v>
+        <x:v>ROSA transaction-api→fds-engine→On-Prem PostgreSQL Hybrid E2E, Rule/Negative/Recovery Regression PASS와 Critical Issue 0</x:v>
       </x:c>
       <x:c r="Q48" s="13" t="str">
-        <x:v>DEC-P2-OP-01 / D26에서 Direct Catalog를 선택하면 Status=Cancelled와 결정 근거를 기록한다. Mirror 선택 시 구현을 진행한다.</x:v>
+        <x:v>IP Endpoint와 Registry N/A 여부는 승인 Decision 결과를 Expected에 반영한다.</x:v>
       </x:c>
       <x:c r="R48" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
       </x:c>
       <x:c r="S48" s="13" t="str">
         <x:f>IF(G48="Done","Complete",IF(OR(H48="",I48=""),"TBD",IF(I48&lt;'Executive Summary'!$B$4,"Past Due",IF(H48&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -4464,31 +4481,31 @@
     </x:row>
     <x:row r="49" ht="44" customHeight="1">
       <x:c r="A49" s="13" t="str">
-        <x:v>DEC-CAL-P2-01</x:v>
+        <x:v>P2-OP-01</x:v>
       </x:c>
       <x:c r="B49" s="13" t="str">
-        <x:v>Phase 2 Weekend Review Decision</x:v>
+        <x:v>Operator Supply Chain Implementation Conditional</x:v>
       </x:c>
       <x:c r="C49" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D49" s="13" t="str">
-        <x:v>Schedule / Governance</x:v>
+        <x:v>Operator Supply Chain</x:v>
       </x:c>
       <x:c r="E49" s="13" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F49" s="13" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G49" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H49" s="19" t="n">
-        <x:v>46317</x:v>
+        <x:v>46314</x:v>
       </x:c>
       <x:c r="I49" s="19" t="n">
-        <x:v>46318</x:v>
+        <x:v>46315</x:v>
       </x:c>
       <x:c r="J49" s="61" t="n">
         <x:f>IF(OR(H49="",I49=""),"",I49-H49+1)</x:f>
@@ -4499,25 +4516,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L49" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="M49" s="13" t="str">
-        <x:v>이하영, 이재환</x:v>
+        <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N49" s="13" t="str">
-        <x:v>D24</x:v>
+        <x:v>D22; D26</x:v>
       </x:c>
       <x:c r="O49" s="13" t="str">
-        <x:v>RISK-05; RISK-13</x:v>
+        <x:v>RISK-06; RISK-11; RISK-15</x:v>
       </x:c>
       <x:c r="P49" s="13" t="str">
-        <x:v>10-24 토요일 Review 유지 또는 영업일 재배치, 참석자·승인권자·시간·Project Close 영향도를 확정하고 WBS 동기화</x:v>
+        <x:v>D26이 Mirror를 선택한 경우 oc-mirror ImageSet·Harbor Push·Custom CatalogSource·Package 조회 PASS; Direct Catalog 선택 시 N/A 근거 승인</x:v>
       </x:c>
       <x:c r="Q49" s="13" t="str">
-        <x:v>2026-10-24는 토요일이며 Working Days 0이다. Project Close 10-26 영향을 함께 검토한다.</x:v>
+        <x:v>DEC-P2-OP-01 / D26에서 Direct Catalog를 선택하면 Status=Cancelled와 결정 근거를 기록한다. Mirror 선택 시 구현을 진행한다.</x:v>
       </x:c>
       <x:c r="R49" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; 2026 Calendar</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
       </x:c>
       <x:c r="S49" s="13" t="str">
         <x:f>IF(G49="Done","Complete",IF(OR(H49="",I49=""),"TBD",IF(I49&lt;'Executive Summary'!$B$4,"Past Due",IF(H49&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -4526,19 +4543,19 @@
     </x:row>
     <x:row r="50" ht="44" customHeight="1">
       <x:c r="A50" s="13" t="str">
-        <x:v>MS-G6-01</x:v>
+        <x:v>DEC-CAL-P2-01</x:v>
       </x:c>
       <x:c r="B50" s="13" t="str">
-        <x:v>G6 Hybrid Integration Ready</x:v>
+        <x:v>Phase 2 Weekend Review Decision</x:v>
       </x:c>
       <x:c r="C50" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D50" s="13" t="str">
-        <x:v>Milestone / Hybrid Integration</x:v>
+        <x:v>Schedule / Governance</x:v>
       </x:c>
       <x:c r="E50" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="F50" s="13" t="str">
         <x:v>P0</x:v>
@@ -4550,15 +4567,15 @@
         <x:v>46317</x:v>
       </x:c>
       <x:c r="I50" s="19" t="n">
-        <x:v>46317</x:v>
+        <x:v>46318</x:v>
       </x:c>
       <x:c r="J50" s="61" t="n">
         <x:f>IF(OR(H50="",I50=""),"",I50-H50+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K50" s="61" t="n">
         <x:f>IF(OR(H50="",I50=""),"",NETWORKDAYS(H50,I50,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L50,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H50,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I50,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L50" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -4567,19 +4584,19 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N50" s="13" t="str">
-        <x:v>D21; D22; D23; D26</x:v>
+        <x:v>D24</x:v>
       </x:c>
       <x:c r="O50" s="13" t="str">
-        <x:v>RISK-09; RISK-10; RISK-11; RISK-12</x:v>
+        <x:v>RISK-05; RISK-13</x:v>
       </x:c>
       <x:c r="P50" s="13" t="str">
-        <x:v>Hybrid DB/Registry Integration, OADP 복구검증, Hybrid E2E/Regression, Critical Issue 0을 승인</x:v>
+        <x:v>10-24 토요일 Review 유지 또는 영업일 재배치, 참석자·승인권자·시간·Project Close 영향도를 확정하고 WBS 동기화</x:v>
       </x:c>
       <x:c r="Q50" s="13" t="str">
-        <x:v>Hybrid DNS와 Operator 공급망은 D23/D26 결과에 따라 구현 또는 Cancelled 처리한다. 같은 날 DEC-CAL-P2-01 검토를 시작해 Review 일정을 10-23까지 확정한다.</x:v>
+        <x:v>2026-10-24는 토요일이며 Working Days 0이다. Project Close 10-26 영향을 함께 검토한다.</x:v>
       </x:c>
       <x:c r="R50" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; 2026 Calendar</x:v>
       </x:c>
       <x:c r="S50" s="13" t="str">
         <x:f>IF(G50="Done","Complete",IF(OR(H50="",I50=""),"TBD",IF(I50&lt;'Executive Summary'!$B$4,"Past Due",IF(H50&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
@@ -4588,16 +4605,16 @@
     </x:row>
     <x:row r="51" ht="44" customHeight="1">
       <x:c r="A51" s="13" t="str">
-        <x:v>MS-DELIVERABLE-FREEZE-01</x:v>
+        <x:v>MS-G6-01</x:v>
       </x:c>
       <x:c r="B51" s="13" t="str">
-        <x:v>Deliverable Freeze</x:v>
+        <x:v>G6 Hybrid Integration Ready</x:v>
       </x:c>
       <x:c r="C51" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D51" s="13" t="str">
-        <x:v>Milestone / Deliverable</x:v>
+        <x:v>Milestone / Hybrid Integration</x:v>
       </x:c>
       <x:c r="E51" s="13" t="str">
         <x:v>Milestone</x:v>
@@ -4609,10 +4626,10 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H51" s="19" t="n">
-        <x:v>46318</x:v>
+        <x:v>46317</x:v>
       </x:c>
       <x:c r="I51" s="19" t="n">
-        <x:v>46318</x:v>
+        <x:v>46317</x:v>
       </x:c>
       <x:c r="J51" s="61" t="n">
         <x:f>IF(OR(H51="",I51=""),"",I51-H51+1)</x:f>
@@ -4629,16 +4646,16 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N51" s="13" t="str">
-        <x:v>D12; D21; D22; D23; D24</x:v>
+        <x:v>D21; D22; D23; D26</x:v>
       </x:c>
       <x:c r="O51" s="13" t="str">
-        <x:v>RISK-10; RISK-11; RISK-12; RISK-13</x:v>
+        <x:v>RISK-09; RISK-10; RISK-11; RISK-12</x:v>
       </x:c>
       <x:c r="P51" s="13" t="str">
-        <x:v>Architecture/IaC/Test/Runbook/Evidence/Decision/Known Issue의 최종 Version과 변경금지를 승인</x:v>
+        <x:v>Hybrid DB/Registry Integration, OADP 복구검증, Hybrid E2E/Regression, Critical Issue 0을 승인</x:v>
       </x:c>
       <x:c r="Q51" s="13" t="str">
-        <x:v>Freeze 이후 변경은 Review Action 또는 Change Request로만 허용한다.</x:v>
+        <x:v>Hybrid DNS와 Operator 공급망은 D23/D26 결과에 따라 구현 또는 Cancelled 처리한다. 같은 날 DEC-CAL-P2-01 검토를 시작해 Review 일정을 10-23까지 확정한다.</x:v>
       </x:c>
       <x:c r="R51" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -4650,19 +4667,19 @@
     </x:row>
     <x:row r="52" ht="44" customHeight="1">
       <x:c r="A52" s="13" t="str">
-        <x:v>P2-REV-01</x:v>
+        <x:v>MS-DELIVERABLE-FREEZE-01</x:v>
       </x:c>
       <x:c r="B52" s="13" t="str">
-        <x:v>Phase 2 Review / Project Close Execution</x:v>
+        <x:v>Deliverable Freeze</x:v>
       </x:c>
       <x:c r="C52" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D52" s="13" t="str">
-        <x:v>PMO / Review</x:v>
+        <x:v>Milestone / Deliverable</x:v>
       </x:c>
       <x:c r="E52" s="13" t="str">
-        <x:v>Task</x:v>
+        <x:v>Milestone</x:v>
       </x:c>
       <x:c r="F52" s="13" t="str">
         <x:v>P0</x:v>
@@ -4674,15 +4691,15 @@
         <x:v>46318</x:v>
       </x:c>
       <x:c r="I52" s="19" t="n">
-        <x:v>46321</x:v>
+        <x:v>46318</x:v>
       </x:c>
       <x:c r="J52" s="61" t="n">
         <x:f>IF(OR(H52="",I52=""),"",I52-H52+1)</x:f>
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K52" s="61" t="n">
         <x:f>IF(OR(H52="",I52=""),"",NETWORKDAYS(H52,I52,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L52,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H52,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I52,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L52" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -4697,10 +4714,10 @@
         <x:v>RISK-10; RISK-11; RISK-12; RISK-13</x:v>
       </x:c>
       <x:c r="P52" s="13" t="str">
-        <x:v>G6/Deliverable Freeze, Hybrid Demo, P0 Evidence, Decision/Known Issue, 비용·자원 정리 및 Project Close Sign-off 확보</x:v>
+        <x:v>Architecture/IaC/Test/Runbook/Evidence/Decision/Known Issue의 최종 Version과 변경금지를 승인</x:v>
       </x:c>
       <x:c r="Q52" s="13" t="str">
-        <x:v>Review 실행일은 D24 결과를 따른다. 최종 Close 목표는 10-26이다.</x:v>
+        <x:v>Freeze 이후 변경은 Review Action 또는 Change Request로만 허용한다.</x:v>
       </x:c>
       <x:c r="R52" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -4712,19 +4729,19 @@
     </x:row>
     <x:row r="53" ht="44" customHeight="1">
       <x:c r="A53" s="13" t="str">
-        <x:v>MS-P2-REVIEW-01</x:v>
+        <x:v>P2-REV-01</x:v>
       </x:c>
       <x:c r="B53" s="13" t="str">
-        <x:v>Phase 2 Review</x:v>
+        <x:v>Phase 2 Review / Project Close Execution</x:v>
       </x:c>
       <x:c r="C53" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D53" s="13" t="str">
-        <x:v>Milestone / Review</x:v>
+        <x:v>PMO / Review</x:v>
       </x:c>
       <x:c r="E53" s="13" t="str">
-        <x:v>Milestone</x:v>
+        <x:v>Task</x:v>
       </x:c>
       <x:c r="F53" s="13" t="str">
         <x:v>P0</x:v>
@@ -4733,18 +4750,18 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H53" s="19" t="n">
-        <x:v>46319</x:v>
+        <x:v>46318</x:v>
       </x:c>
       <x:c r="I53" s="19" t="n">
-        <x:v>46319</x:v>
+        <x:v>46321</x:v>
       </x:c>
       <x:c r="J53" s="61" t="n">
         <x:f>IF(OR(H53="",I53=""),"",I53-H53+1)</x:f>
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K53" s="61" t="n">
         <x:f>IF(OR(H53="",I53=""),"",NETWORKDAYS(H53,I53,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L53,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H53,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I53,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L53" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -4753,16 +4770,16 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N53" s="13" t="str">
-        <x:v>D24</x:v>
+        <x:v>D12; D21; D22; D23; D24</x:v>
       </x:c>
       <x:c r="O53" s="13" t="str">
-        <x:v>RISK-05; RISK-13</x:v>
+        <x:v>RISK-10; RISK-11; RISK-12; RISK-13</x:v>
       </x:c>
       <x:c r="P53" s="13" t="str">
-        <x:v>승인된 일정에 Hybrid Demo/산출물/G6/Known Issue/Cloud Resource Review를 수행하고 Action·승인결과를 기록</x:v>
+        <x:v>G6/Deliverable Freeze, Hybrid Demo, P0 Evidence, Decision/Known Issue, 비용·자원 정리 및 Project Close Sign-off 확보</x:v>
       </x:c>
       <x:c r="Q53" s="13" t="str">
-        <x:v>2026-10-24는 토요일이며 Working Days 0이다. D24가 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
+        <x:v>Review 실행일은 D24 결과를 따른다. 최종 Close 목표는 10-26이다.</x:v>
       </x:c>
       <x:c r="R53" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
@@ -4774,16 +4791,16 @@
     </x:row>
     <x:row r="54" ht="44" customHeight="1">
       <x:c r="A54" s="13" t="str">
-        <x:v>MS-PROJECT-CLOSE-01</x:v>
+        <x:v>MS-P2-REVIEW-01</x:v>
       </x:c>
       <x:c r="B54" s="13" t="str">
-        <x:v>Project Close</x:v>
+        <x:v>Phase 2 Review</x:v>
       </x:c>
       <x:c r="C54" s="13" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
       <x:c r="D54" s="13" t="str">
-        <x:v>Milestone / Close</x:v>
+        <x:v>Milestone / Review</x:v>
       </x:c>
       <x:c r="E54" s="13" t="str">
         <x:v>Milestone</x:v>
@@ -4795,10 +4812,10 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="H54" s="19" t="n">
-        <x:v>46321</x:v>
+        <x:v>46319</x:v>
       </x:c>
       <x:c r="I54" s="19" t="n">
-        <x:v>46321</x:v>
+        <x:v>46319</x:v>
       </x:c>
       <x:c r="J54" s="61" t="n">
         <x:f>IF(OR(H54="",I54=""),"",I54-H54+1)</x:f>
@@ -4806,7 +4823,7 @@
       </x:c>
       <x:c r="K54" s="61" t="n">
         <x:f>IF(OR(H54="",I54=""),"",NETWORKDAYS(H54,I54,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L54,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H54,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I54,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L54" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -4818,19 +4835,81 @@
         <x:v>D24</x:v>
       </x:c>
       <x:c r="O54" s="13" t="str">
-        <x:v>RISK-05; RISK-11; RISK-13</x:v>
+        <x:v>RISK-05; RISK-13</x:v>
       </x:c>
       <x:c r="P54" s="13" t="str">
-        <x:v>Review Action, P0 승인, 후속 P1/Known Issue, Cloud Resource/Cost, Source/Deliverable 인계 및 Project Close Sign-off 확보</x:v>
+        <x:v>승인된 일정에 Hybrid Demo/산출물/G6/Known Issue/Cloud Resource Review를 수행하고 Action·승인결과를 기록</x:v>
       </x:c>
       <x:c r="Q54" s="13" t="str">
-        <x:v>D24가 Review를 10-26 이후로 이동시키면 Project Close도 Change Request 대상이다.</x:v>
+        <x:v>2026-10-24는 토요일이며 Working Days 0이다. D24가 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
       </x:c>
       <x:c r="R54" s="13" t="str">
         <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
       </x:c>
       <x:c r="S54" s="13" t="str">
         <x:f>IF(G54="Done","Complete",IF(OR(H54="",I54=""),"TBD",IF(I54&lt;'Executive Summary'!$B$4,"Past Due",IF(H54&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>MS-PROJECT-CLOSE-01</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>Project Close</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>Milestone / Close</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>Milestone</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G55" t="str">
+        <x:v>To Do</x:v>
+      </x:c>
+      <x:c r="H55" t="n">
+        <x:v>46321</x:v>
+      </x:c>
+      <x:c r="I55" t="n">
+        <x:v>46321</x:v>
+      </x:c>
+      <x:c r="J55" t="n">
+        <x:f>IF(OR(H55="",I55=""),"",I55-H55+1)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K55" t="n">
+        <x:f>IF(OR(H55="",I55=""),"",NETWORKDAYS(H55,I55,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L55,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H55,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I55,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L55" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="M55" t="str">
+        <x:v>이하영, 이재환</x:v>
+      </x:c>
+      <x:c r="N55" t="str">
+        <x:v>D24</x:v>
+      </x:c>
+      <x:c r="O55" t="str">
+        <x:v>RISK-05; RISK-11; RISK-13</x:v>
+      </x:c>
+      <x:c r="P55" t="str">
+        <x:v>Review Action, P0 승인, 후속 P1/Known Issue, Cloud Resource/Cost, Source/Deliverable 인계 및 Project Close Sign-off 확보</x:v>
+      </x:c>
+      <x:c r="Q55" t="str">
+        <x:v>D24가 Review를 10-26 이후로 이동시키면 Project Close도 Change Request 대상이다.</x:v>
+      </x:c>
+      <x:c r="R55" t="str">
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+      </x:c>
+      <x:c r="S55" t="str">
+        <x:f>IF(G55="Done","Complete",IF(OR(H55="",I55=""),"TBD",IF(I55&lt;'Executive Summary'!$B$4,"Past Due",IF(H55&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
         <x:v>Planned</x:v>
       </x:c>
     </x:row>
@@ -4858,7 +4937,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R977405648bc84180"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ac23de9b2b248f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6071,22 +6150,22 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="13" t="str">
-        <x:v>P1-APP-01</x:v>
+        <x:v>CR-P1-ANS-01-01</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>transaction-api / fds-engine</x:v>
+        <x:v>Kubernetes Node DNS Resolver Automation</x:v>
       </x:c>
       <x:c r="C13" s="13" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D13" s="19" t="n">
-        <x:v>46266</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="E13" s="19" t="n">
-        <x:v>46275</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(G$4=$D13,1,""),IF(AND(G$4&gt;=$D13,G$4&lt;=$E13),1,"")))</x:f>
@@ -6106,20 +6185,18 @@
       <x:c r="L13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(L$4=$D13,1,""),IF(AND(L$4&gt;=$D13,L$4&lt;=$E13),1,"")))</x:f>
       </x:c>
-      <x:c r="M13" s="27" t="n">
+      <x:c r="M13" s="27" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(M$4=$D13,1,""),IF(AND(M$4&gt;=$D13,M$4&lt;=$E13),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N13" s="23" t="n">
+      </x:c>
+      <x:c r="N13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(N$4=$D13,1,""),IF(AND(N$4&gt;=$D13,N$4&lt;=$E13),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="23" t="n">
+      </x:c>
+      <x:c r="O13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(O$4=$D13,1,""),IF(AND(O$4&gt;=$D13,O$4&lt;=$E13),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P13" s="66" t="str">
-        <x:v>L</x:v>
+      </x:c>
+      <x:c r="P13" s="66" t="n">
+        <x:f>IF($D13="","",IF($E13="",IF(P$4=$D13,1,""),IF(AND(P$4&gt;=$D13,P$4&lt;=$E13),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q13" s="25" t="n">
         <x:f>IF($D13="","",IF($E13="",IF(Q$4=$D13,1,""),IF(AND(Q$4&gt;=$D13,Q$4&lt;=$E13),1,"")))</x:f>
@@ -6133,17 +6210,14 @@
         <x:f>IF($D13="","",IF($E13="",IF(S$4=$D13,1,""),IF(AND(S$4&gt;=$D13,S$4&lt;=$E13),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T13" s="23" t="n">
+      <x:c r="T13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(T$4=$D13,1,""),IF(AND(T$4&gt;=$D13,T$4&lt;=$E13),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U13" s="23" t="n">
+      </x:c>
+      <x:c r="U13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(U$4=$D13,1,""),IF(AND(U$4&gt;=$D13,U$4&lt;=$E13),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V13" s="23" t="n">
+      </x:c>
+      <x:c r="V13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(V$4=$D13,1,""),IF(AND(V$4&gt;=$D13,V$4&lt;=$E13),1,"")))</x:f>
-        <x:v>1</x:v>
       </x:c>
       <x:c r="W13" s="23" t="str">
         <x:f>IF($D13="","",IF($E13="",IF(W$4=$D13,1,""),IF(AND(W$4&gt;=$D13,W$4&lt;=$E13),1,"")))</x:f>
@@ -6187,22 +6261,22 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="13" t="str">
-        <x:v>P1-CICD-01</x:v>
+        <x:v>P1-APP-01</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
-        <x:v>GitHub Actions / Self-hosted Runner Delivery</x:v>
+        <x:v>transaction-api / fds-engine</x:v>
       </x:c>
       <x:c r="C14" s="13" t="str">
-        <x:v>To Do</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="D14" s="19" t="n">
         <x:v>46266</x:v>
       </x:c>
       <x:c r="E14" s="19" t="n">
-        <x:v>46274</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="F14" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="G14" s="23" t="str">
         <x:f>IF($D14="","",IF($E14="",IF(G$4=$D14,1,""),IF(AND(G$4&gt;=$D14,G$4&lt;=$E14),1,"")))</x:f>
@@ -6235,7 +6309,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P14" s="23" t="n">
-        <x:f>IF($D14="","",IF($E14="",IF(P$4=$D14,1,""),IF(AND(P$4&gt;=$D14,P$4&lt;=$E14),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q14" s="25" t="n">
@@ -6258,8 +6331,9 @@
         <x:f>IF($D14="","",IF($E14="",IF(U$4=$D14,1,""),IF(AND(U$4&gt;=$D14,U$4&lt;=$E14),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="V14" s="23" t="str">
+      <x:c r="V14" s="23" t="n">
         <x:f>IF($D14="","",IF($E14="",IF(V$4=$D14,1,""),IF(AND(V$4&gt;=$D14,V$4&lt;=$E14),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W14" s="23" t="str">
         <x:f>IF($D14="","",IF($E14="",IF(W$4=$D14,1,""),IF(AND(W$4&gt;=$D14,W$4&lt;=$E14),1,"")))</x:f>
@@ -6303,19 +6377,19 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="13" t="str">
-        <x:v>MS-G1-01</x:v>
+        <x:v>P1-CICD-01</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>G1 Infrastructure Ready</x:v>
+        <x:v>GitHub Actions / Self-hosted Runner Delivery</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D15" s="19" t="n">
-        <x:v>46272</x:v>
+        <x:v>46266</x:v>
       </x:c>
       <x:c r="E15" s="19" t="n">
-        <x:v>46272</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -6338,33 +6412,41 @@
       <x:c r="L15" s="23" t="str">
         <x:f>IF($D15="","",IF($E15="",IF(L$4=$D15,1,""),IF(AND(L$4&gt;=$D15,L$4&lt;=$E15),1,"")))</x:f>
       </x:c>
-      <x:c r="M15" s="27" t="str">
+      <x:c r="M15" s="27" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(M$4=$D15,1,""),IF(AND(M$4&gt;=$D15,M$4&lt;=$E15),1,"")))</x:f>
-      </x:c>
-      <x:c r="N15" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N15" s="23" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(N$4=$D15,1,""),IF(AND(N$4&gt;=$D15,N$4&lt;=$E15),1,"")))</x:f>
-      </x:c>
-      <x:c r="O15" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O15" s="23" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(O$4=$D15,1,""),IF(AND(O$4&gt;=$D15,O$4&lt;=$E15),1,"")))</x:f>
-      </x:c>
-      <x:c r="P15" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P15" s="23" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(P$4=$D15,1,""),IF(AND(P$4&gt;=$D15,P$4&lt;=$E15),1,"")))</x:f>
-      </x:c>
-      <x:c r="Q15" s="25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q15" s="25" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(Q$4=$D15,1,""),IF(AND(Q$4&gt;=$D15,Q$4&lt;=$E15),1,"")))</x:f>
-      </x:c>
-      <x:c r="R15" s="25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R15" s="25" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(R$4=$D15,1,""),IF(AND(R$4&gt;=$D15,R$4&lt;=$E15),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S15" s="23" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(S$4=$D15,1,""),IF(AND(S$4&gt;=$D15,S$4&lt;=$E15),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T15" s="23" t="str">
+      <x:c r="T15" s="23" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(T$4=$D15,1,""),IF(AND(T$4&gt;=$D15,T$4&lt;=$E15),1,"")))</x:f>
-      </x:c>
-      <x:c r="U15" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U15" s="23" t="n">
         <x:f>IF($D15="","",IF($E15="",IF(U$4=$D15,1,""),IF(AND(U$4&gt;=$D15,U$4&lt;=$E15),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V15" s="23" t="str">
         <x:f>IF($D15="","",IF($E15="",IF(V$4=$D15,1,""),IF(AND(V$4&gt;=$D15,V$4&lt;=$E15),1,"")))</x:f>
@@ -6411,22 +6493,22 @@
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="13" t="str">
-        <x:v>P1-MON-01</x:v>
+        <x:v>MS-G1-01</x:v>
       </x:c>
       <x:c r="B16" s="13" t="str">
-        <x:v>Prometheus / Node / App Metrics</x:v>
+        <x:v>G1 Infrastructure Ready</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>To Do</x:v>
       </x:c>
       <x:c r="D16" s="19" t="n">
         <x:v>46272</x:v>
       </x:c>
       <x:c r="E16" s="19" t="n">
-        <x:v>46276</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G16" s="23" t="str">
         <x:f>IF($D16="","",IF($E16="",IF(G$4=$D16,1,""),IF(AND(G$4&gt;=$D16,G$4&lt;=$E16),1,"")))</x:f>
@@ -6456,7 +6538,7 @@
         <x:f>IF($D16="","",IF($E16="",IF(O$4=$D16,1,""),IF(AND(O$4&gt;=$D16,O$4&lt;=$E16),1,"")))</x:f>
       </x:c>
       <x:c r="P16" s="66" t="str">
-        <x:v>L</x:v>
+        <x:f>IF($D16="","",IF($E16="",IF(P$4=$D16,1,""),IF(AND(P$4&gt;=$D16,P$4&lt;=$E16),1,"")))</x:f>
       </x:c>
       <x:c r="Q16" s="25" t="str">
         <x:f>IF($D16="","",IF($E16="",IF(Q$4=$D16,1,""),IF(AND(Q$4&gt;=$D16,Q$4&lt;=$E16),1,"")))</x:f>
@@ -6468,21 +6550,17 @@
         <x:f>IF($D16="","",IF($E16="",IF(S$4=$D16,1,""),IF(AND(S$4&gt;=$D16,S$4&lt;=$E16),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T16" s="23" t="n">
+      <x:c r="T16" s="23" t="str">
         <x:f>IF($D16="","",IF($E16="",IF(T$4=$D16,1,""),IF(AND(T$4&gt;=$D16,T$4&lt;=$E16),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U16" s="23" t="n">
+      </x:c>
+      <x:c r="U16" s="23" t="str">
         <x:f>IF($D16="","",IF($E16="",IF(U$4=$D16,1,""),IF(AND(U$4&gt;=$D16,U$4&lt;=$E16),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V16" s="23" t="n">
+      </x:c>
+      <x:c r="V16" s="23" t="str">
         <x:f>IF($D16="","",IF($E16="",IF(V$4=$D16,1,""),IF(AND(V$4&gt;=$D16,V$4&lt;=$E16),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W16" s="23" t="n">
+      </x:c>
+      <x:c r="W16" s="23" t="str">
         <x:f>IF($D16="","",IF($E16="",IF(W$4=$D16,1,""),IF(AND(W$4&gt;=$D16,W$4&lt;=$E16),1,"")))</x:f>
-        <x:v>1</x:v>
       </x:c>
       <x:c r="X16" s="25" t="str">
         <x:f>IF($D16="","",IF($E16="",IF(X$4=$D16,1,""),IF(AND(X$4&gt;=$D16,X$4&lt;=$E16),1,"")))</x:f>
@@ -6523,22 +6601,22 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="13" t="str">
-        <x:v>P1-SEC-01</x:v>
+        <x:v>P1-MON-01</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>Kubernetes Security Controls</x:v>
+        <x:v>Prometheus / Node / App Metrics</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
-        <x:v>To Do</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="D17" s="19" t="n">
-        <x:v>46269</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="E17" s="19" t="n">
         <x:v>46276</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="G17" s="23" t="str">
         <x:f>IF($D17="","",IF($E17="",IF(G$4=$D17,1,""),IF(AND(G$4&gt;=$D17,G$4&lt;=$E17),1,"")))</x:f>
@@ -6567,24 +6645,20 @@
       <x:c r="O17" s="23" t="str">
         <x:f>IF($D17="","",IF($E17="",IF(O$4=$D17,1,""),IF(AND(O$4&gt;=$D17,O$4&lt;=$E17),1,"")))</x:f>
       </x:c>
-      <x:c r="P17" s="23" t="n">
-        <x:f>IF($D17="","",IF($E17="",IF(P$4=$D17,1,""),IF(AND(P$4&gt;=$D17,P$4&lt;=$E17),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q17" s="25" t="n">
+      <x:c r="P17" s="23" t="str"/>
+      <x:c r="Q17" s="25" t="str">
         <x:f>IF($D17="","",IF($E17="",IF(Q$4=$D17,1,""),IF(AND(Q$4&gt;=$D17,Q$4&lt;=$E17),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R17" s="25" t="n">
+      </x:c>
+      <x:c r="R17" s="25" t="str">
         <x:f>IF($D17="","",IF($E17="",IF(R$4=$D17,1,""),IF(AND(R$4&gt;=$D17,R$4&lt;=$E17),1,"")))</x:f>
-        <x:v>1</x:v>
       </x:c>
       <x:c r="S17" s="23" t="n">
         <x:f>IF($D17="","",IF($E17="",IF(S$4=$D17,1,""),IF(AND(S$4&gt;=$D17,S$4&lt;=$E17),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T17" s="75" t="str">
-        <x:v>L</x:v>
+      <x:c r="T17" s="75" t="n">
+        <x:f>IF($D17="","",IF($E17="",IF(T$4=$D17,1,""),IF(AND(T$4&gt;=$D17,T$4&lt;=$E17),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U17" s="23" t="n">
         <x:f>IF($D17="","",IF($E17="",IF(U$4=$D17,1,""),IF(AND(U$4&gt;=$D17,U$4&lt;=$E17),1,"")))</x:f>
@@ -6637,22 +6711,22 @@
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="13" t="str">
-        <x:v>P1-E2E-01</x:v>
+        <x:v>P1-SEC-01</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>Initial / Final E2E &amp; Regression</x:v>
+        <x:v>Kubernetes Security Controls</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D18" s="19" t="n">
-        <x:v>46274</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="E18" s="19" t="n">
-        <x:v>46283</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="F18" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="G18" s="23" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(G$4=$D18,1,""),IF(AND(G$4&gt;=$D18,G$4&lt;=$E18),1,"")))</x:f>
@@ -6681,20 +6755,24 @@
       <x:c r="O18" s="23" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(O$4=$D18,1,""),IF(AND(O$4&gt;=$D18,O$4&lt;=$E18),1,"")))</x:f>
       </x:c>
-      <x:c r="P18" s="23" t="str">
+      <x:c r="P18" s="23" t="n">
         <x:f>IF($D18="","",IF($E18="",IF(P$4=$D18,1,""),IF(AND(P$4&gt;=$D18,P$4&lt;=$E18),1,"")))</x:f>
-      </x:c>
-      <x:c r="Q18" s="25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q18" s="25" t="n">
         <x:f>IF($D18="","",IF($E18="",IF(Q$4=$D18,1,""),IF(AND(Q$4&gt;=$D18,Q$4&lt;=$E18),1,"")))</x:f>
-      </x:c>
-      <x:c r="R18" s="25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R18" s="25" t="n">
         <x:f>IF($D18="","",IF($E18="",IF(R$4=$D18,1,""),IF(AND(R$4&gt;=$D18,R$4&lt;=$E18),1,"")))</x:f>
-      </x:c>
-      <x:c r="S18" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S18" s="23" t="n">
         <x:f>IF($D18="","",IF($E18="",IF(S$4=$D18,1,""),IF(AND(S$4&gt;=$D18,S$4&lt;=$E18),1,"")))</x:f>
-      </x:c>
-      <x:c r="T18" s="23" t="str">
-        <x:f>IF($D18="","",IF($E18="",IF(T$4=$D18,1,""),IF(AND(T$4&gt;=$D18,T$4&lt;=$E18),1,"")))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T18" s="23" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U18" s="23" t="n">
         <x:f>IF($D18="","",IF($E18="",IF(U$4=$D18,1,""),IF(AND(U$4&gt;=$D18,U$4&lt;=$E18),1,"")))</x:f>
@@ -6708,33 +6786,26 @@
         <x:f>IF($D18="","",IF($E18="",IF(W$4=$D18,1,""),IF(AND(W$4&gt;=$D18,W$4&lt;=$E18),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X18" s="25" t="n">
+      <x:c r="X18" s="25" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(X$4=$D18,1,""),IF(AND(X$4&gt;=$D18,X$4&lt;=$E18),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y18" s="25" t="n">
+      </x:c>
+      <x:c r="Y18" s="25" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(Y$4=$D18,1,""),IF(AND(Y$4&gt;=$D18,Y$4&lt;=$E18),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z18" s="23" t="n">
+      </x:c>
+      <x:c r="Z18" s="23" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(Z$4=$D18,1,""),IF(AND(Z$4&gt;=$D18,Z$4&lt;=$E18),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA18" s="23" t="n">
+      </x:c>
+      <x:c r="AA18" s="23" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(AA$4=$D18,1,""),IF(AND(AA$4&gt;=$D18,AA$4&lt;=$E18),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB18" s="23" t="n">
+      </x:c>
+      <x:c r="AB18" s="23" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(AB$4=$D18,1,""),IF(AND(AB$4&gt;=$D18,AB$4&lt;=$E18),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC18" s="23" t="n">
+      </x:c>
+      <x:c r="AC18" s="23" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(AC$4=$D18,1,""),IF(AND(AC$4&gt;=$D18,AC$4&lt;=$E18),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD18" s="23" t="n">
+      </x:c>
+      <x:c r="AD18" s="23" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(AD$4=$D18,1,""),IF(AND(AD$4&gt;=$D18,AD$4&lt;=$E18),1,"")))</x:f>
-        <x:v>1</x:v>
       </x:c>
       <x:c r="AE18" s="25" t="str">
         <x:f>IF($D18="","",IF($E18="",IF(AE$4=$D18,1,""),IF(AND(AE$4&gt;=$D18,AE$4&lt;=$E18),1,"")))</x:f>
@@ -6754,19 +6825,19 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="13" t="str">
-        <x:v>P1-DR-01</x:v>
+        <x:v>P1-E2E-01</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>PostgreSQL Backup / Restore</x:v>
+        <x:v>Initial / Final E2E &amp; Regression</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D19" s="19" t="n">
-        <x:v>46275</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="E19" s="19" t="n">
-        <x:v>46278</x:v>
+        <x:v>46283</x:v>
       </x:c>
       <x:c r="F19" s="13" t="str">
         <x:v>이재환</x:v>
@@ -6813,8 +6884,9 @@
       <x:c r="T19" s="23" t="str">
         <x:f>IF($D19="","",IF($E19="",IF(T$4=$D19,1,""),IF(AND(T$4&gt;=$D19,T$4&lt;=$E19),1,"")))</x:f>
       </x:c>
-      <x:c r="U19" s="23" t="str">
+      <x:c r="U19" s="23" t="n">
         <x:f>IF($D19="","",IF($E19="",IF(U$4=$D19,1,""),IF(AND(U$4&gt;=$D19,U$4&lt;=$E19),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V19" s="23" t="n">
         <x:f>IF($D19="","",IF($E19="",IF(V$4=$D19,1,""),IF(AND(V$4&gt;=$D19,V$4&lt;=$E19),1,"")))</x:f>
@@ -6832,20 +6904,25 @@
         <x:f>IF($D19="","",IF($E19="",IF(Y$4=$D19,1,""),IF(AND(Y$4&gt;=$D19,Y$4&lt;=$E19),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z19" s="23" t="str">
+      <x:c r="Z19" s="23" t="n">
         <x:f>IF($D19="","",IF($E19="",IF(Z$4=$D19,1,""),IF(AND(Z$4&gt;=$D19,Z$4&lt;=$E19),1,"")))</x:f>
-      </x:c>
-      <x:c r="AA19" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA19" s="23" t="n">
         <x:f>IF($D19="","",IF($E19="",IF(AA$4=$D19,1,""),IF(AND(AA$4&gt;=$D19,AA$4&lt;=$E19),1,"")))</x:f>
-      </x:c>
-      <x:c r="AB19" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB19" s="23" t="n">
         <x:f>IF($D19="","",IF($E19="",IF(AB$4=$D19,1,""),IF(AND(AB$4&gt;=$D19,AB$4&lt;=$E19),1,"")))</x:f>
-      </x:c>
-      <x:c r="AC19" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC19" s="23" t="n">
         <x:f>IF($D19="","",IF($E19="",IF(AC$4=$D19,1,""),IF(AND(AC$4&gt;=$D19,AC$4&lt;=$E19),1,"")))</x:f>
-      </x:c>
-      <x:c r="AD19" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD19" s="23" t="n">
         <x:f>IF($D19="","",IF($E19="",IF(AD$4=$D19,1,""),IF(AND(AD$4&gt;=$D19,AD$4&lt;=$E19),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AE19" s="25" t="str">
         <x:f>IF($D19="","",IF($E19="",IF(AE$4=$D19,1,""),IF(AND(AE$4&gt;=$D19,AE$4&lt;=$E19),1,"")))</x:f>
@@ -6865,10 +6942,10 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="13" t="str">
-        <x:v>P1-HA-01</x:v>
+        <x:v>P1-DR-01</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>Worker Drain Continuity</x:v>
+        <x:v>PostgreSQL Backup / Restore</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
         <x:v>To Do</x:v>
@@ -6976,22 +7053,22 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="13" t="str">
-        <x:v>MS-G2-01</x:v>
+        <x:v>P1-HA-01</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>G2 Security / Feature Ready</x:v>
+        <x:v>Worker Drain Continuity</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D21" s="19" t="n">
-        <x:v>46276</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="E21" s="19" t="n">
-        <x:v>46276</x:v>
+        <x:v>46278</x:v>
       </x:c>
       <x:c r="F21" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="G21" s="23" t="str">
         <x:f>IF($D21="","",IF($E21="",IF(G$4=$D21,1,""),IF(AND(G$4&gt;=$D21,G$4&lt;=$E21),1,"")))</x:f>
@@ -7038,18 +7115,21 @@
       <x:c r="U21" s="23" t="str">
         <x:f>IF($D21="","",IF($E21="",IF(U$4=$D21,1,""),IF(AND(U$4&gt;=$D21,U$4&lt;=$E21),1,"")))</x:f>
       </x:c>
-      <x:c r="V21" s="23" t="str">
+      <x:c r="V21" s="23" t="n">
         <x:f>IF($D21="","",IF($E21="",IF(V$4=$D21,1,""),IF(AND(V$4&gt;=$D21,V$4&lt;=$E21),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W21" s="23" t="n">
         <x:f>IF($D21="","",IF($E21="",IF(W$4=$D21,1,""),IF(AND(W$4&gt;=$D21,W$4&lt;=$E21),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X21" s="25" t="str">
+      <x:c r="X21" s="25" t="n">
         <x:f>IF($D21="","",IF($E21="",IF(X$4=$D21,1,""),IF(AND(X$4&gt;=$D21,X$4&lt;=$E21),1,"")))</x:f>
-      </x:c>
-      <x:c r="Y21" s="25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y21" s="25" t="n">
         <x:f>IF($D21="","",IF($E21="",IF(Y$4=$D21,1,""),IF(AND(Y$4&gt;=$D21,Y$4&lt;=$E21),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z21" s="23" t="str">
         <x:f>IF($D21="","",IF($E21="",IF(Z$4=$D21,1,""),IF(AND(Z$4&gt;=$D21,Z$4&lt;=$E21),1,"")))</x:f>
@@ -7084,22 +7164,22 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="13" t="str">
-        <x:v>P1-DOC-01</x:v>
+        <x:v>MS-G2-01</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>Architecture / Test / Runbook Freeze</x:v>
+        <x:v>G2 Security / Feature Ready</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D22" s="19" t="n">
-        <x:v>46277</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="E22" s="19" t="n">
-        <x:v>46283</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="G22" s="23" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(G$4=$D22,1,""),IF(AND(G$4&gt;=$D22,G$4&lt;=$E22),1,"")))</x:f>
@@ -7149,36 +7229,30 @@
       <x:c r="V22" s="23" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(V$4=$D22,1,""),IF(AND(V$4&gt;=$D22,V$4&lt;=$E22),1,"")))</x:f>
       </x:c>
-      <x:c r="W22" s="23" t="str">
+      <x:c r="W22" s="23" t="n">
         <x:f>IF($D22="","",IF($E22="",IF(W$4=$D22,1,""),IF(AND(W$4&gt;=$D22,W$4&lt;=$E22),1,"")))</x:f>
-      </x:c>
-      <x:c r="X22" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X22" s="25" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(X$4=$D22,1,""),IF(AND(X$4&gt;=$D22,X$4&lt;=$E22),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y22" s="25" t="n">
+      </x:c>
+      <x:c r="Y22" s="25" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(Y$4=$D22,1,""),IF(AND(Y$4&gt;=$D22,Y$4&lt;=$E22),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z22" s="23" t="n">
+      </x:c>
+      <x:c r="Z22" s="23" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(Z$4=$D22,1,""),IF(AND(Z$4&gt;=$D22,Z$4&lt;=$E22),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA22" s="23" t="n">
+      </x:c>
+      <x:c r="AA22" s="23" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(AA$4=$D22,1,""),IF(AND(AA$4&gt;=$D22,AA$4&lt;=$E22),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB22" s="23" t="n">
+      </x:c>
+      <x:c r="AB22" s="23" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(AB$4=$D22,1,""),IF(AND(AB$4&gt;=$D22,AB$4&lt;=$E22),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC22" s="23" t="n">
+      </x:c>
+      <x:c r="AC22" s="23" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(AC$4=$D22,1,""),IF(AND(AC$4&gt;=$D22,AC$4&lt;=$E22),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD22" s="23" t="n">
+      </x:c>
+      <x:c r="AD22" s="23" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(AD$4=$D22,1,""),IF(AND(AD$4&gt;=$D22,AD$4&lt;=$E22),1,"")))</x:f>
-        <x:v>1</x:v>
       </x:c>
       <x:c r="AE22" s="25" t="str">
         <x:f>IF($D22="","",IF($E22="",IF(AE$4=$D22,1,""),IF(AND(AE$4&gt;=$D22,AE$4&lt;=$E22),1,"")))</x:f>
@@ -7198,10 +7272,10 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="13" t="str">
-        <x:v>P1-MON-02</x:v>
+        <x:v>P1-DOC-01</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
-        <x:v>Dashboard / Alert Enhancement</x:v>
+        <x:v>Architecture / Test / Runbook Freeze</x:v>
       </x:c>
       <x:c r="C23" s="13" t="str">
         <x:v>To Do</x:v>
@@ -7213,7 +7287,7 @@
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F23" s="13" t="str">
-        <x:v>이재환</x:v>
+        <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G23" s="23" t="str">
         <x:f>IF($D23="","",IF($E23="",IF(G$4=$D23,1,""),IF(AND(G$4&gt;=$D23,G$4&lt;=$E23),1,"")))</x:f>
@@ -7312,22 +7386,22 @@
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="13" t="str">
-        <x:v>P1-DR-02</x:v>
+        <x:v>P1-MON-02</x:v>
       </x:c>
       <x:c r="B24" s="13" t="str">
-        <x:v>Harbor / etcd Backup and Restore</x:v>
+        <x:v>Dashboard / Alert Enhancement</x:v>
       </x:c>
       <x:c r="C24" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D24" s="19" t="n">
-        <x:v>46279</x:v>
+        <x:v>46277</x:v>
       </x:c>
       <x:c r="E24" s="19" t="n">
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F24" s="13" t="str">
-        <x:v>이하영</x:v>
+        <x:v>이재환</x:v>
       </x:c>
       <x:c r="G24" s="23" t="str">
         <x:f>IF($D24="","",IF($E24="",IF(G$4=$D24,1,""),IF(AND(G$4&gt;=$D24,G$4&lt;=$E24),1,"")))</x:f>
@@ -7380,11 +7454,13 @@
       <x:c r="W24" s="23" t="str">
         <x:f>IF($D24="","",IF($E24="",IF(W$4=$D24,1,""),IF(AND(W$4&gt;=$D24,W$4&lt;=$E24),1,"")))</x:f>
       </x:c>
-      <x:c r="X24" s="25" t="str">
+      <x:c r="X24" s="25" t="n">
         <x:f>IF($D24="","",IF($E24="",IF(X$4=$D24,1,""),IF(AND(X$4&gt;=$D24,X$4&lt;=$E24),1,"")))</x:f>
-      </x:c>
-      <x:c r="Y24" s="25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y24" s="25" t="n">
         <x:f>IF($D24="","",IF($E24="",IF(Y$4=$D24,1,""),IF(AND(Y$4&gt;=$D24,Y$4&lt;=$E24),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z24" s="23" t="n">
         <x:f>IF($D24="","",IF($E24="",IF(Z$4=$D24,1,""),IF(AND(Z$4&gt;=$D24,Z$4&lt;=$E24),1,"")))</x:f>
@@ -7424,10 +7500,10 @@
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="13" t="str">
-        <x:v>P1-HA-02</x:v>
+        <x:v>P1-DR-02</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
-        <x:v>Platform Resilience P1 Validation</x:v>
+        <x:v>Harbor / etcd Backup and Restore</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
         <x:v>To Do</x:v>
@@ -7536,22 +7612,22 @@
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="13" t="str">
-        <x:v>DEC-CAL-P1-01</x:v>
+        <x:v>P1-HA-02</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>Phase 1 Weekend Review Decision</x:v>
+        <x:v>Platform Resilience P1 Validation</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D26" s="19" t="n">
-        <x:v>46282</x:v>
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="E26" s="19" t="n">
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
-        <x:v>이권욱</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="G26" s="23" t="str">
         <x:f>IF($D26="","",IF($E26="",IF(G$4=$D26,1,""),IF(AND(G$4&gt;=$D26,G$4&lt;=$E26),1,"")))</x:f>
@@ -7610,14 +7686,17 @@
       <x:c r="Y26" s="25" t="str">
         <x:f>IF($D26="","",IF($E26="",IF(Y$4=$D26,1,""),IF(AND(Y$4&gt;=$D26,Y$4&lt;=$E26),1,"")))</x:f>
       </x:c>
-      <x:c r="Z26" s="23" t="str">
+      <x:c r="Z26" s="23" t="n">
         <x:f>IF($D26="","",IF($E26="",IF(Z$4=$D26,1,""),IF(AND(Z$4&gt;=$D26,Z$4&lt;=$E26),1,"")))</x:f>
-      </x:c>
-      <x:c r="AA26" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA26" s="23" t="n">
         <x:f>IF($D26="","",IF($E26="",IF(AA$4=$D26,1,""),IF(AND(AA$4&gt;=$D26,AA$4&lt;=$E26),1,"")))</x:f>
-      </x:c>
-      <x:c r="AB26" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB26" s="23" t="n">
         <x:f>IF($D26="","",IF($E26="",IF(AB$4=$D26,1,""),IF(AND(AB$4&gt;=$D26,AB$4&lt;=$E26),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC26" s="23" t="n">
         <x:f>IF($D26="","",IF($E26="",IF(AC$4=$D26,1,""),IF(AND(AC$4&gt;=$D26,AC$4&lt;=$E26),1,"")))</x:f>
@@ -7645,16 +7724,16 @@
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="13" t="str">
-        <x:v>MS-G3-01</x:v>
+        <x:v>DEC-CAL-P1-01</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
-        <x:v>G3 Review Ready</x:v>
+        <x:v>Phase 1 Weekend Review Decision</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D27" s="19" t="n">
-        <x:v>46283</x:v>
+        <x:v>46282</x:v>
       </x:c>
       <x:c r="E27" s="19" t="n">
         <x:v>46283</x:v>
@@ -7728,8 +7807,9 @@
       <x:c r="AB27" s="23" t="str">
         <x:f>IF($D27="","",IF($E27="",IF(AB$4=$D27,1,""),IF(AND(AB$4&gt;=$D27,AB$4&lt;=$E27),1,"")))</x:f>
       </x:c>
-      <x:c r="AC27" s="23" t="str">
+      <x:c r="AC27" s="23" t="n">
         <x:f>IF($D27="","",IF($E27="",IF(AC$4=$D27,1,""),IF(AND(AC$4&gt;=$D27,AC$4&lt;=$E27),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD27" s="23" t="n">
         <x:f>IF($D27="","",IF($E27="",IF(AD$4=$D27,1,""),IF(AND(AD$4&gt;=$D27,AD$4&lt;=$E27),1,"")))</x:f>
@@ -7753,10 +7833,10 @@
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="13" t="str">
-        <x:v>P1-REV-01</x:v>
+        <x:v>MS-G3-01</x:v>
       </x:c>
       <x:c r="B28" s="13" t="str">
-        <x:v>Phase 1 Review / Close Execution</x:v>
+        <x:v>G3 Review Ready</x:v>
       </x:c>
       <x:c r="C28" s="13" t="str">
         <x:v>To Do</x:v>
@@ -7765,7 +7845,7 @@
         <x:v>46283</x:v>
       </x:c>
       <x:c r="E28" s="19" t="n">
-        <x:v>46288</x:v>
+        <x:v>46283</x:v>
       </x:c>
       <x:c r="F28" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -7843,42 +7923,37 @@
         <x:f>IF($D28="","",IF($E28="",IF(AD$4=$D28,1,""),IF(AND(AD$4&gt;=$D28,AD$4&lt;=$E28),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AE28" s="25" t="n">
+      <x:c r="AE28" s="25" t="str">
         <x:f>IF($D28="","",IF($E28="",IF(AE$4=$D28,1,""),IF(AND(AE$4&gt;=$D28,AE$4&lt;=$E28),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF28" s="25" t="n">
+      </x:c>
+      <x:c r="AF28" s="25" t="str">
         <x:f>IF($D28="","",IF($E28="",IF(AF$4=$D28,1,""),IF(AND(AF$4&gt;=$D28,AF$4&lt;=$E28),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG28" s="23" t="n">
+      </x:c>
+      <x:c r="AG28" s="23" t="str">
         <x:f>IF($D28="","",IF($E28="",IF(AG$4=$D28,1,""),IF(AND(AG$4&gt;=$D28,AG$4&lt;=$E28),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH28" s="23" t="n">
+      </x:c>
+      <x:c r="AH28" s="23" t="str">
         <x:f>IF($D28="","",IF($E28="",IF(AH$4=$D28,1,""),IF(AND(AH$4&gt;=$D28,AH$4&lt;=$E28),1,"")))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI28" s="23" t="n">
+      </x:c>
+      <x:c r="AI28" s="23" t="str">
         <x:f>IF($D28="","",IF($E28="",IF(AI$4=$D28,1,""),IF(AND(AI$4&gt;=$D28,AI$4&lt;=$E28),1,"")))</x:f>
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="13" t="str">
-        <x:v>MS-P1-REVIEW-01</x:v>
+        <x:v>P1-REV-01</x:v>
       </x:c>
       <x:c r="B29" s="13" t="str">
-        <x:v>Phase 1 Review</x:v>
+        <x:v>Phase 1 Review / Close Execution</x:v>
       </x:c>
       <x:c r="C29" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D29" s="19" t="n">
-        <x:v>46285</x:v>
+        <x:v>46283</x:v>
       </x:c>
       <x:c r="E29" s="19" t="n">
-        <x:v>46285</x:v>
+        <x:v>46288</x:v>
       </x:c>
       <x:c r="F29" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -7952,41 +8027,46 @@
       <x:c r="AC29" s="23" t="str">
         <x:f>IF($D29="","",IF($E29="",IF(AC$4=$D29,1,""),IF(AND(AC$4&gt;=$D29,AC$4&lt;=$E29),1,"")))</x:f>
       </x:c>
-      <x:c r="AD29" s="23" t="str">
+      <x:c r="AD29" s="23" t="n">
         <x:f>IF($D29="","",IF($E29="",IF(AD$4=$D29,1,""),IF(AND(AD$4&gt;=$D29,AD$4&lt;=$E29),1,"")))</x:f>
-      </x:c>
-      <x:c r="AE29" s="25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE29" s="25" t="n">
         <x:f>IF($D29="","",IF($E29="",IF(AE$4=$D29,1,""),IF(AND(AE$4&gt;=$D29,AE$4&lt;=$E29),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AF29" s="25" t="n">
         <x:f>IF($D29="","",IF($E29="",IF(AF$4=$D29,1,""),IF(AND(AF$4&gt;=$D29,AF$4&lt;=$E29),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG29" s="23" t="str">
+      <x:c r="AG29" s="23" t="n">
         <x:f>IF($D29="","",IF($E29="",IF(AG$4=$D29,1,""),IF(AND(AG$4&gt;=$D29,AG$4&lt;=$E29),1,"")))</x:f>
-      </x:c>
-      <x:c r="AH29" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH29" s="23" t="n">
         <x:f>IF($D29="","",IF($E29="",IF(AH$4=$D29,1,""),IF(AND(AH$4&gt;=$D29,AH$4&lt;=$E29),1,"")))</x:f>
-      </x:c>
-      <x:c r="AI29" s="23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI29" s="23" t="n">
         <x:f>IF($D29="","",IF($E29="",IF(AI$4=$D29,1,""),IF(AND(AI$4&gt;=$D29,AI$4&lt;=$E29),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="13" t="str">
-        <x:v>MS-P1-CLOSE-01</x:v>
+        <x:v>MS-P1-REVIEW-01</x:v>
       </x:c>
       <x:c r="B30" s="13" t="str">
-        <x:v>Phase 1 Close</x:v>
+        <x:v>Phase 1 Review</x:v>
       </x:c>
       <x:c r="C30" s="13" t="str">
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="D30" s="19" t="n">
-        <x:v>46288</x:v>
+        <x:v>46285</x:v>
       </x:c>
       <x:c r="E30" s="19" t="n">
-        <x:v>46288</x:v>
+        <x:v>46285</x:v>
       </x:c>
       <x:c r="F30" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -8066,8 +8146,9 @@
       <x:c r="AE30" s="25" t="str">
         <x:f>IF($D30="","",IF($E30="",IF(AE$4=$D30,1,""),IF(AND(AE$4&gt;=$D30,AE$4&lt;=$E30),1,"")))</x:f>
       </x:c>
-      <x:c r="AF30" s="25" t="str">
+      <x:c r="AF30" s="25" t="n">
         <x:f>IF($D30="","",IF($E30="",IF(AF$4=$D30,1,""),IF(AND(AF$4&gt;=$D30,AF$4&lt;=$E30),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AG30" s="23" t="str">
         <x:f>IF($D30="","",IF($E30="",IF(AG$4=$D30,1,""),IF(AND(AG$4&gt;=$D30,AG$4&lt;=$E30),1,"")))</x:f>
@@ -8075,8 +8156,115 @@
       <x:c r="AH30" s="23" t="str">
         <x:f>IF($D30="","",IF($E30="",IF(AH$4=$D30,1,""),IF(AND(AH$4&gt;=$D30,AH$4&lt;=$E30),1,"")))</x:f>
       </x:c>
-      <x:c r="AI30" s="23" t="n">
+      <x:c r="AI30" s="23" t="str">
         <x:f>IF($D30="","",IF($E30="",IF(AI$4=$D30,1,""),IF(AND(AI$4&gt;=$D30,AI$4&lt;=$E30),1,"")))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>MS-P1-CLOSE-01</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Phase 1 Close</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>To Do</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(G$4=$D31,1,""),IF(AND(G$4&gt;=$D31,G$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(H$4=$D31,1,""),IF(AND(H$4&gt;=$D31,H$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(I$4=$D31,1,""),IF(AND(I$4&gt;=$D31,I$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(J$4=$D31,1,""),IF(AND(J$4&gt;=$D31,J$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(K$4=$D31,1,""),IF(AND(K$4&gt;=$D31,K$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(L$4=$D31,1,""),IF(AND(L$4&gt;=$D31,L$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(M$4=$D31,1,""),IF(AND(M$4&gt;=$D31,M$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(N$4=$D31,1,""),IF(AND(N$4&gt;=$D31,N$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(O$4=$D31,1,""),IF(AND(O$4&gt;=$D31,O$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(P$4=$D31,1,""),IF(AND(P$4&gt;=$D31,P$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="Q31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(Q$4=$D31,1,""),IF(AND(Q$4&gt;=$D31,Q$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="R31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(R$4=$D31,1,""),IF(AND(R$4&gt;=$D31,R$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="S31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(S$4=$D31,1,""),IF(AND(S$4&gt;=$D31,S$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="T31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(T$4=$D31,1,""),IF(AND(T$4&gt;=$D31,T$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="U31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(U$4=$D31,1,""),IF(AND(U$4&gt;=$D31,U$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="V31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(V$4=$D31,1,""),IF(AND(V$4&gt;=$D31,V$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="W31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(W$4=$D31,1,""),IF(AND(W$4&gt;=$D31,W$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="X31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(X$4=$D31,1,""),IF(AND(X$4&gt;=$D31,X$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="Y31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(Y$4=$D31,1,""),IF(AND(Y$4&gt;=$D31,Y$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="Z31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(Z$4=$D31,1,""),IF(AND(Z$4&gt;=$D31,Z$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AA31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AA$4=$D31,1,""),IF(AND(AA$4&gt;=$D31,AA$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AB31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AB$4=$D31,1,""),IF(AND(AB$4&gt;=$D31,AB$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AC31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AC$4=$D31,1,""),IF(AND(AC$4&gt;=$D31,AC$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AD31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AD$4=$D31,1,""),IF(AND(AD$4&gt;=$D31,AD$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AE31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AE$4=$D31,1,""),IF(AND(AE$4&gt;=$D31,AE$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AF31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AF$4=$D31,1,""),IF(AND(AF$4&gt;=$D31,AF$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AG31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AG$4=$D31,1,""),IF(AND(AG$4&gt;=$D31,AG$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AH31" t="str">
+        <x:f>IF($D31="","",IF($E31="",IF(AH$4=$D31,1,""),IF(AND(AH$4&gt;=$D31,AH$4&lt;=$E31),1,"")))</x:f>
+      </x:c>
+      <x:c r="AI31" s="77" t="n">
+        <x:f>IF($D31="","",IF($E31="",IF(AI$4=$D31,1,""),IF(AND(AI$4&gt;=$D31,AI$4&lt;=$E31),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -11866,6 +12054,38 @@
         <x:v>User instruction 2026-09-08</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="52" customHeight="1">
+      <x:c r="A22" s="67" t="str">
+        <x:v>CR-P1-ANS-01-01</x:v>
+      </x:c>
+      <x:c r="B22" s="67" t="str">
+        <x:v>Kubernetes Node DNS Resolver Automation</x:v>
+      </x:c>
+      <x:c r="C22" s="67" t="str">
+        <x:v>Change Request</x:v>
+      </x:c>
+      <x:c r="D22" s="67" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E22" s="68" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="F22" s="68" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+      <x:c r="G22" s="67" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="H22" s="67" t="str">
+        <x:v>11개 Acceptance Criteria PASS; 이하영 Support Review; 승인 HEAD·Merge Commit 고정</x:v>
+      </x:c>
+      <x:c r="I22" s="67" t="str">
+        <x:v>GitHub Actions NOT RUN; K8s API·LB Stage B·kubeadm·ICR Runtime 완료를 의미하지 않음</x:v>
+      </x:c>
+      <x:c r="J22" s="67" t="str">
+        <x:v>v3.1.18 정본 묶음에 Baseline·WBS/Gantt·Ticket Pack·완료 기록·증적 참조 동기화</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
@@ -12535,6 +12755,38 @@
       <x:c r="I13" s="67"/>
       <x:c r="J13" s="67"/>
     </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="67" t="str">
+        <x:v>Canonical Candidate</x:v>
+      </x:c>
+      <x:c r="B14" s="67" t="str">
+        <x:v>CR-P1-ANS-01-01 / infra-ansible PR #1</x:v>
+      </x:c>
+      <x:c r="C14" s="67" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="D14" s="67" t="str">
+        <x:v>완료 CR 정본 동기화</x:v>
+      </x:c>
+      <x:c r="E14" s="67" t="str">
+        <x:v>Acceptance Criteria 11/11 PASS; Support Review 및 수동 병합 완료</x:v>
+      </x:c>
+      <x:c r="F14" s="67" t="str">
+        <x:v>507d8882a04f53640b07251bcc234b7d6ee81c09</x:v>
+      </x:c>
+      <x:c r="G14" s="67" t="str">
+        <x:v>Merge Commit</x:v>
+      </x:c>
+      <x:c r="H14" s="67" t="str">
+        <x:v>4f9bdb7c08704eebb3d1b294751e51b0721b6af4</x:v>
+      </x:c>
+      <x:c r="I14" s="67" t="str">
+        <x:v>CI</x:v>
+      </x:c>
+      <x:c r="J14" s="67" t="str">
+        <x:v>NOT RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>

--- a/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
+++ b/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R486aaf9d6802480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R207e763e04b54d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="R9ba909f268a64f04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="R52ba5c3e90e44bca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="R5f7cdf00ff05440d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="R6a6ffc223e394926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="R208af04e414f44b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="R05137d543b7d4c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R84d014aa830c491a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R30215edb6fdd436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="Ra2433bc27f8a409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="Rc89de2fd2f94456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="Rcba15939fe6840a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="R3e333d839c57444f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="Re4c466f5c9714d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="Rbcfc80d2c6c94059"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,14 +20,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="m/d"/>
     <x:numFmt numFmtId="202" formatCode=";;;"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
     <x:numFmt numFmtId="204" formatCode="@"/>
+    <x:numFmt numFmtId="205" formatCode="mm-dd"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -119,8 +120,19 @@
       <x:color rgb="FF9FB4C5"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Noto Sans CJK KR"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF183C5A"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -192,8 +204,13 @@
         <x:fgColor rgb="FF9FB4C5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF183C5A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="4">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -223,11 +240,25 @@
         <x:color rgb="FFCCD8E2"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC7D8E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC7D8E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC7D8E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC7D8E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="78">
+  <x:cellXfs count="92">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -392,11 +423,47 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="15" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="23">
+  <x:dxfs count="37">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -604,6 +671,140 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFFFF1CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF167A52"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF5E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF146CAA"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF4FF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA86400"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB4233D"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE3E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB4233D"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE3E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA86400"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FF40B883"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF167A52"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF5E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FF3D8DFF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF146CAA"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF4FF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF4B740"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA86400"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE45C72"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FF9CB0C3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -857,7 +1058,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc327255a297e49e9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f4e773a67194659"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -887,7 +1088,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56a1f92c97ea4fe0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R49b886749bc94351"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1144,72 +1345,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · Executive Schedule Summary (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="N1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="O1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="Q1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="S1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="T1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="U1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
-      <x:c r="V1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Executive Schedule Summary</x:v>
-      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
+      <x:c r="K1" s="79"/>
+      <x:c r="L1" s="79"/>
+      <x:c r="M1" s="79"/>
+      <x:c r="N1" s="79"/>
+      <x:c r="O1" s="79"/>
+      <x:c r="P1" s="79"/>
+      <x:c r="Q1" s="79"/>
+      <x:c r="R1" s="79"/>
+      <x:c r="S1" s="79"/>
+      <x:c r="T1" s="79"/>
+      <x:c r="U1" s="79"/>
+      <x:c r="V1" s="79"/>
     </x:row>
     <x:row r="2">
       <x:c r="B2"/>
@@ -1234,7 +1393,7 @@
         <x:v>As of</x:v>
       </x:c>
       <x:c r="B4" s="19" t="n">
-        <x:v>46273</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
         <x:v>G0 Design Freeze</x:v>
@@ -1262,7 +1421,8 @@
         <x:v>Planning records</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>52</x:v>
+        <x:f>COUNTA(WBS!A4:A58)</x:f>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
         <x:v>G2 Target</x:v>
@@ -1273,9 +1433,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="str">
-        <x:v>Tasks + ICR</x:v>
+        <x:v>Tasks + CR</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
+        <x:f>COUNTIF(WBS!E4:E58,"Task")+COUNTIF(WBS!E4:E58,"Change Request")</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
@@ -1290,6 +1451,7 @@
         <x:v>Milestones</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
+        <x:f>COUNTIF(WBS!E4:E58,"Milestone")</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="13" t="str">
@@ -1326,14 +1488,14 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B12" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$55,A12)</x:f>
-        <x:v>4</x:v>
+        <x:f>COUNTIF(WBS!$G$4:$G$58,A12)</x:f>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="E12" s="13" t="n">
-        <x:f>COUNTIF(WBS!$L$4:$L$55,D12)</x:f>
+        <x:f>COUNTIF(WBS!$L$4:$L$58,D12)</x:f>
         <x:v>29</x:v>
       </x:c>
     </x:row>
@@ -1342,15 +1504,15 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$55,A13)</x:f>
-        <x:v>6</x:v>
+        <x:f>COUNTIF(WBS!$G$4:$G$58,A13)</x:f>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="E13" s="13" t="n">
-        <x:f>COUNTIF(WBS!$L$4:$L$55,D13)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIF(WBS!$L$4:$L$58,D13)</x:f>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1358,15 +1520,15 @@
         <x:v>In Review</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$55,A14)</x:f>
+        <x:f>COUNTIF(WBS!$G$4:$G$58,A14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="13" t="str">
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="E14" s="13" t="n">
-        <x:f>COUNTIF(WBS!$L$4:$L$55,D14)</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIF(WBS!$L$4:$L$58,D14)</x:f>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1374,8 +1536,8 @@
         <x:v>To Do</x:v>
       </x:c>
       <x:c r="B15" s="13" t="n">
-        <x:f>COUNTIF(WBS!$G$4:$G$55,A15)</x:f>
-        <x:v>42</x:v>
+        <x:f>COUNTIF(WBS!$G$4:$G$58,A15)</x:f>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1516,13 +1678,73 @@
         <x:v>이권욱</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" ht="40" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>G1 target remains 2026-09-07</x:v>
+      </x:c>
+      <x:c r="C27" s="67" t="str">
+        <x:v>Gate To Do; target is overdue. Runtime / handoff approval remains open.</x:v>
+      </x:c>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
+      <x:c r="M27"/>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
+      <x:c r="Q27"/>
+      <x:c r="R27"/>
+      <x:c r="S27"/>
+      <x:c r="T27"/>
+      <x:c r="U27"/>
+      <x:c r="V27"/>
+    </x:row>
+    <x:row r="28" ht="40" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>MON-02 capacity / scope</x:v>
+      </x:c>
+      <x:c r="C28" s="67" t="str">
+        <x:v>2026-09-12–09-18 contains 1 lead working day; retain dates for separate review.</x:v>
+      </x:c>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+      <x:c r="I28"/>
+      <x:c r="J28"/>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
+      <x:c r="M28"/>
+      <x:c r="N28"/>
+      <x:c r="O28"/>
+      <x:c r="P28"/>
+      <x:c r="Q28"/>
+      <x:c r="R28"/>
+      <x:c r="S28"/>
+      <x:c r="T28"/>
+      <x:c r="U28"/>
+      <x:c r="V28"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:V1"/>
     <x:mergeCell ref="A18:V18"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80ddee034ef24f8a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ab737843cd04326"/>
 </x:worksheet>
 </file>
 
@@ -1530,7 +1752,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
@@ -1552,70 +1774,34 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · WBS (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="N1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="O1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="Q1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
-      <x:c r="S1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Work Breakdown Structure</x:v>
-      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
+      <x:c r="K1" s="79"/>
+      <x:c r="L1" s="79"/>
+      <x:c r="M1" s="79"/>
+      <x:c r="N1" s="79"/>
+      <x:c r="O1" s="79"/>
+      <x:c r="P1" s="79"/>
+      <x:c r="Q1" s="79"/>
+      <x:c r="R1" s="79"/>
+      <x:c r="S1" s="79"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="17" t="str">
         <x:v>As of</x:v>
       </x:c>
       <x:c r="B2" s="18" t="n">
-        <x:v>46273</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="C2" s="17" t="str">
         <x:v>Canonical</x:v>
@@ -1627,7 +1813,8 @@
         <x:v>Records</x:v>
       </x:c>
       <x:c r="F2" s="17" t="n">
-        <x:v>51</x:v>
+        <x:f>COUNTA(A4:A58)</x:f>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G2" s="17" t="str"/>
       <x:c r="H2" s="17" t="str"/>
@@ -1735,7 +1922,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K4" s="61" t="n">
-        <x:f>IF(OR(H4="",I4=""),"",NETWORKDAYS(H4,I4,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L4,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H4,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I4,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H4="",I4=""),"",NETWORKDAYS(H4,I4,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L4,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H4,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I4,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="L4" s="13" t="str">
@@ -1757,11 +1944,11 @@
         <x:v>v3.1.14 최종 승인·정본 반영 완료. 구현은 P1-SEC-01로 이관.</x:v>
       </x:c>
       <x:c r="R4" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.14; D-SEC-01_Kubernetes_Security_Design_Baseline_v1.0</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #7 snapshot 2026-09-09T12:13:54Z</x:v>
       </x:c>
       <x:c r="S4" s="13" t="str">
-        <x:f>IF(G4="Done","Complete",IF(OR(H4="",I4=""),"TBD",IF(I4&lt;'Executive Summary'!$B$4,"Past Due",IF(H4&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Complete</x:v>
+        <x:f>IF(G4="Done","Done",IF(I4="","End TBD",IF(I4&lt;'Executive Summary'!$B$4,"Overdue",IF(H4&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
@@ -1797,7 +1984,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K5" s="61" t="n">
-        <x:f>IF(OR(H5="",I5=""),"",NETWORKDAYS(H5,I5,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L5,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H5,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I5,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H5="",I5=""),"",NETWORKDAYS(H5,I5,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L5,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H5,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I5,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L5" s="13" t="str">
@@ -1807,23 +1994,23 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N5" s="13" t="str">
-        <x:v>D17; D28; D32</x:v>
+        <x:v>D17; D28; D32; D34; D35</x:v>
       </x:c>
       <x:c r="O5" s="13" t="str">
         <x:v>RISK-05; RISK-07</x:v>
       </x:c>
       <x:c r="P5" s="13" t="str">
-        <x:v>D-ARC-01·D-NET-01·D-WBS-01·D-SEC-01의 승인 상태와 Evidence를 확인하고 Architecture·Network·WBS·Security Scope/Owner/Exit Criteria를 동결한 뒤 G0 Full PASS 승인 기록 확보</x:v>
+        <x:v>D-ARC-01·D-NET-01·D-WBS-01·D-SEC-01 승인과 정본 Evidence를 확인하고 G0 FULL PASS 기록 확보</x:v>
       </x:c>
       <x:c r="Q5" s="13" t="str">
         <x:v>G0 Design Freeze FULL PASS (2026-09-01).</x:v>
       </x:c>
       <x:c r="R5" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.14; FDS_v3.1.14_Canonical_Ticket_Update_Pack_v1.0</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #8 snapshot 2026-09-09T12:14:17Z</x:v>
       </x:c>
       <x:c r="S5" s="13" t="str">
-        <x:f>IF(G5="Done","Complete",IF(OR(H5="",I5=""),"TBD",IF(I5&lt;'Executive Summary'!$B$4,"Past Due",IF(H5&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Complete</x:v>
+        <x:f>IF(G5="Done","Done",IF(I5="","End TBD",IF(I5&lt;'Executive Summary'!$B$4,"Overdue",IF(H5&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
@@ -1859,7 +2046,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K6" s="61" t="n">
-        <x:f>IF(OR(H6="",I6=""),"",NETWORKDAYS(H6,I6,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L6,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H6,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I6,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H6="",I6=""),"",NETWORKDAYS(H6,I6,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L6,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H6,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I6,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="L6" s="13" t="str">
@@ -1869,22 +2056,23 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N6" s="13" t="str">
-        <x:v>HO-ANS-04B 전달 경로의 Positive/Negative Test, Health Check, Backout Evidence가 승인된다.</x:v>
+        <x:v>D02; D05; D27; D31; D34; D35</x:v>
       </x:c>
       <x:c r="O6" s="13" t="str">
         <x:v>RISK-02; RISK-03; RISK-04</x:v>
       </x:c>
       <x:c r="P6" s="13" t="str">
-        <x:v>API LB .109:6443에서 control-plane .102~.104:6443으로 전달하는 HO-ANS-04B를 Stage A/B, Health Check, Rollback Gate와 함께 검증한다.</x:v>
+        <x:v>IF-11/IF-11A/IF-06A Source Allowlist, `.109:6443→.102~.104:6443` Stage A Listener/Handoff와 Stage B Backend Health/API/Failover Evidence</x:v>
       </x:c>
       <x:c r="Q6" s="13" t="str">
         <x:v>Stage A PASS 2026-09-03. Stage B target rebaselined to approved D36 G1 target 2026-09-07; remains In Progress until backend/auth/failover/recovery evidence is PASS.</x:v>
       </x:c>
       <x:c r="R6" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; P1-LB-01 Stage A Evidence 01-18c; D35; IF-11/IF-11A/IF-12</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #9 snapshot 2026-09-10T02:09:13Z</x:v>
       </x:c>
       <x:c r="S6" s="13" t="str">
-        <x:v>Overdue / In Progress</x:v>
+        <x:f>IF(G6="Done","Done",IF(I6="","End TBD",IF(I6&lt;'Executive Summary'!$B$4,"Overdue",IF(H6&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Overdue</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -1920,7 +2108,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K7" s="61" t="n">
-        <x:f>IF(OR(H7="",I7=""),"",NETWORKDAYS(H7,I7,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L7,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H7,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I7,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H7="",I7=""),"",NETWORKDAYS(H7,I7,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L7,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H7,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I7,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="L7" s="13" t="str">
@@ -1930,22 +2118,23 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="N7" s="13" t="str">
-        <x:v>HO-ANS-01/02A/03/04A의 6대 노드 Preflight, Runtime·kubelet·Calico 호환성 및 필수 포트 결과가 PASS하고 증적이 승인된다.</x:v>
+        <x:v>D01; D02; D05; D27; D31; D34; D35</x:v>
       </x:c>
       <x:c r="O7" s="13" t="str">
         <x:v>RISK-02; RISK-03; RISK-04; RISK-07; RISK-14</x:v>
       </x:c>
       <x:c r="P7" s="13" t="str">
-        <x:v>HO-ANS-01 cgroup driver, HO-ANS-02A SELinux Enforcing Runtime/kubelet/Calico, HO-ANS-03 hostname/MAC/product_uuid 고유성, HO-ANS-04A Kubernetes/Calico 필수 포트를 Preflight와 Cluster Apply Gate에서 검증한다.</x:v>
+        <x:v>LB Stage A 확인, 6개 Node의 보호 공백 없는 firewalld→named HEP/GNP 전환, containerd/kubelet·SELinux·identity·Port Matrix, BGP Disabled+VXLANCrossSubnet Calico, 6/6 Ready, CoreDNS, static local PV Evidence</x:v>
       </x:c>
       <x:c r="Q7" s="13" t="str">
-        <x:v>2026-09-03 착수. P1-LB-01 Stage A PASS를 인계받아 Gate 0~2 수행 중. SELinux Enforcing 유지, firewalld→Calico HostEndpoint 전환, D34 확정값 적용. 이하영 2026-09-08 면접 휴가로 당일 작업·단독 종료를 배치하지 않는다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>승인 목표는 SELinux Enforcing·Calico named HEP/GNP 보호 전환이다. 실제 적용은 현행 Gate와 고정 변경안의 리뷰·실행 결정 후 노드별 검증으로 진행한다. CP1 준비/진단은 전체 6대 Runtime PASS가 아니며 날짜 재기준선화는 하지 않는다.</x:v>
       </x:c>
       <x:c r="R7" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; FDS_P1-K8S-01_Preflight_Review_v1.1; P1-LB-01 Stage A Evidence</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #10 snapshot 2026-09-10T05:03:27Z</x:v>
       </x:c>
       <x:c r="S7" s="13" t="str">
-        <x:v>Overdue / Leave</x:v>
+        <x:f>IF(G7="Done","Done",IF(I7="","End TBD",IF(I7&lt;'Executive Summary'!$B$4,"Overdue",IF(H7&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Overdue</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -1981,7 +2170,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K8" s="61" t="n">
-        <x:f>IF(OR(H8="",I8=""),"",NETWORKDAYS(H8,I8,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L8,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H8,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I8,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H8="",I8=""),"",NETWORKDAYS(H8,I8,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L8,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H8,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I8,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="L8" s="13" t="str">
@@ -2003,10 +2192,11 @@
         <x:v>이재환 2026-09-04 개인 휴가로 당일 작업·단독 종료를 배치하지 않는다. 09-07 복귀 후 완료하여 Lead 가용 작업일 6일을 보존한다. PostgreSQL HA는 Scope Out.</x:v>
       </x:c>
       <x:c r="R8" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #11 snapshot 2026-09-10T04:01:06Z</x:v>
       </x:c>
       <x:c r="S8" s="13" t="str">
-        <x:v>Overdue / In Progress</x:v>
+        <x:f>IF(G8="Done","Done",IF(I8="","End TBD",IF(I8&lt;'Executive Summary'!$B$4,"Overdue",IF(H8&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Overdue</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
@@ -2014,7 +2204,7 @@
         <x:v>P1-DNS-01</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
-        <x:v>BIND Primary / Secondary</x:v>
+        <x:v>Internal DNS Primary/Secondary</x:v>
       </x:c>
       <x:c r="C9" s="13" t="str">
         <x:v>Phase 1</x:v>
@@ -2042,7 +2232,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K9" s="61" t="n">
-        <x:f>IF(OR(H9="",I9=""),"",NETWORKDAYS(H9,I9,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L9,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H9,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I9,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H9="",I9=""),"",NETWORKDAYS(H9,I9,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L9,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H9,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I9,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L9" s="13" t="str">
@@ -2052,23 +2242,23 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N9" s="13" t="str">
-        <x:v>D08; D09</x:v>
+        <x:v>D08; D09; D34; D35</x:v>
       </x:c>
       <x:c r="O9" s="13" t="str">
         <x:v>RISK-02; RISK-04; RISK-07</x:v>
       </x:c>
       <x:c r="P9" s="13" t="str">
-        <x:v>dns01 .52/dns02 .53의 fds.internal Forward Zone, 제한 Query·Forward, TSIG 기반 Zone Transfer, Primary 장애 Resolution Test 및 Reverse/PTR N/A 기록</x:v>
+        <x:v>Primary/Secondary·TSIG·제한 Query/Recursion·Failover Evidence와 k8s-api-lb01 `.109` Resolver/ACL/IPSet 검증 및 Support Review 승인</x:v>
       </x:c>
       <x:c r="Q9" s="13" t="str">
         <x:v>기술 검증·Support Review·.109 ACL/Resolver/Failover Delta 확인 완료. 2026-09-03 Done 승인.</x:v>
       </x:c>
       <x:c r="R9" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; P1-DNS-01 approved Evidence; D36</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #12 snapshot 2026-09-10T02:09:19Z</x:v>
       </x:c>
       <x:c r="S9" s="13" t="str">
-        <x:f>IF(G9="Done","Complete",IF(OR(H9="",I9=""),"TBD",IF(I9&lt;'Executive Summary'!$B$4,"Past Due",IF(H9&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Complete</x:v>
+        <x:f>IF(G9="Done","Done",IF(I9="","End TBD",IF(I9&lt;'Executive Summary'!$B$4,"Overdue",IF(H9&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
@@ -2091,7 +2281,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G10" s="13" t="str">
-        <x:v>To Do</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="H10" s="19" t="n">
         <x:v>46265</x:v>
@@ -2104,7 +2294,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K10" s="61" t="n">
-        <x:f>IF(OR(H10="",I10=""),"",NETWORKDAYS(H10,I10,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L10,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H10,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I10,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H10="",I10=""),"",NETWORKDAYS(H10,I10,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L10,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H10,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I10,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L10" s="13" t="str">
@@ -2114,22 +2304,23 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="N10" s="13" t="str">
-        <x:v>D04; D05; D19</x:v>
+        <x:v>D04; D17; D19; D35</x:v>
       </x:c>
       <x:c r="O10" s="13" t="str">
-        <x:v>RISK-02; RISK-06; RISK-08</x:v>
+        <x:v>RISK-04; RISK-06; RISK-07</x:v>
       </x:c>
       <x:c r="P10" s="13" t="str">
-        <x:v>harbor01 10.1.93.54:443 구축, Project/User 권한, Runner Push·Worker Pull, Trivy Scan Gate와 Evidence 확보</x:v>
+        <x:v>harbor01 `.54:443`, Private CA Trust, 최소권한 Robot Account, IF-09 Runner Push·IF-10 Worker Pull/Pod Start, 비승인 Push/Pull DENY, Trivy/Digest/Evidence PASS</x:v>
       </x:c>
       <x:c r="Q10" s="13" t="str">
-        <x:v>이하영 08-28 휴가를 반영해 08-31 시작한다. TLS 결정 D19를 선행하고 Harbor HA/실제 Restore는 P1이다. 이하영 2026-09-08 면접 휴가로 당일 작업·단독 종료를 배치하지 않는다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>D19 TLS와 Harbor 구현·6차 리뷰 보완 진행 중. 2026-09-08 이하영 개인 부재는 이권욱이 지원하며 Plan End는 유지한다. Harbor HA는 Phase 1 Scope Out/P2 검토, 실제 Backup/Restore는 P1-DR-02 범위다.</x:v>
       </x:c>
       <x:c r="R10" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #13 snapshot 2026-09-10T03:15:50Z</x:v>
       </x:c>
       <x:c r="S10" s="13" t="str">
-        <x:v>Overdue / Leave</x:v>
+        <x:f>IF(G10="Done","Done",IF(I10="","End TBD",IF(I10&lt;'Executive Summary'!$B$4,"Overdue",IF(H10&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Overdue</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
@@ -2137,13 +2328,13 @@
         <x:v>ICR-D-NET-01-01</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
-        <x:v>Kubernetes Node Host Firewall &amp; Monitoring Route</x:v>
+        <x:v>Kubernetes Node Host Firewall / Monitoring Route</x:v>
       </x:c>
       <x:c r="C11" s="13" t="str">
         <x:v>Phase 1</x:v>
       </x:c>
       <x:c r="D11" s="13" t="str">
-        <x:v>Network / Change Control</x:v>
+        <x:v>Network / Interface Change Control</x:v>
       </x:c>
       <x:c r="E11" s="13" t="str">
         <x:v>Change Request</x:v>
@@ -2162,7 +2353,7 @@
         <x:f>IF(OR(H11="",I11=""),"",I11-H11+1)</x:f>
       </x:c>
       <x:c r="K11" s="61" t="str">
-        <x:f>IF(OR(H11="",I11=""),"",NETWORKDAYS(H11,I11,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L11,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H11,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I11,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H11="",I11=""),"",NETWORKDAYS(H11,I11,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L11,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H11,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I11,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
       </x:c>
       <x:c r="L11" s="13" t="str">
         <x:v>이권욱</x:v>
@@ -2171,23 +2362,23 @@
         <x:v>이하영, 이재환</x:v>
       </x:c>
       <x:c r="N11" s="13" t="str">
-        <x:v>D-NET-01 §15.2; P1-LB Stage A; P1-MON-01</x:v>
+        <x:v>D17; D18; D33; D34; D35</x:v>
       </x:c>
       <x:c r="O11" s="13" t="str">
-        <x:v>RISK-02; RISK-04; RISK-07</x:v>
+        <x:v>RISK-04; RISK-07</x:v>
       </x:c>
       <x:c r="P11" s="13" t="str">
-        <x:v>Worker/Control Plane Host Firewall 대안과 Node Exporter 9100·kubelet 10250 최소 허용, Alertmanager/Prometheus↔monitor01 관리망 경로를 변경 통제로 구현·검증한다.</x:v>
+        <x:v>Kubernetes 6개 Node의 보호 공백 없는 firewalld→Calico named HEP/GNP 전환, 30080/9100/10250 최소 허용, 관리망 반환 경로와 IF-06B 정합화, Positive/Negative/Regression/Reboot/Rollback 및 무결성 Evidence 완료</x:v>
       </x:c>
       <x:c r="Q11" s="13" t="str">
-        <x:v>종료일은 Lead 승인 후 확정(TBD). mgmt-gw01 경유 Return Route와 9100/10250 최소 허용 Evidence가 필요. 이하영 2026-09-08 면접 휴가로 당일 지원 가용성이 없다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>CP1 사전 진단 완료, 최소 CP 통신 canary 적용·독립 리뷰·운영 인수 대기. 6대 HEP/GNP·IF-06B·IF-16 및 NTP 목적지/Worker 검증은 잔여. End/기간 TBD 유지.</x:v>
       </x:c>
       <x:c r="R11" s="13" t="str">
-        <x:v>ICR-D-NET-01-01_Kubernetes_Node_Host_Firewall_및_Monitoring_Route_변경요청_v1.4; FDS_Project_Implementation_Baseline_v3.1.17</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #14 snapshot 2026-09-10T05:03:39Z</x:v>
       </x:c>
       <x:c r="S11" s="13" t="str">
-        <x:f>IF(G11="Done","Complete",IF(OR(H11="",I11=""),"TBD",IF(I11&lt;'Executive Summary'!$B$4,"Past Due",IF(H11&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>TBD</x:v>
+        <x:f>IF(G11="Done","Done",IF(I11="","End TBD",IF(I11&lt;'Executive Summary'!$B$4,"Overdue",IF(H11&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>End TBD</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
@@ -2195,7 +2386,7 @@
         <x:v>CR-P1-ANS-01-01</x:v>
       </x:c>
       <x:c r="B12" s="13" t="str">
-        <x:v>Kubernetes Node DNS Resolver Automation</x:v>
+        <x:v>Ansible Kubernetes Node DNS Resolver 변경</x:v>
       </x:c>
       <x:c r="C12" s="13" t="str">
         <x:v>Phase 1</x:v>
@@ -2219,9 +2410,11 @@
         <x:v>46272</x:v>
       </x:c>
       <x:c r="J12" s="61" t="n">
+        <x:f>IF(OR(H12="",I12=""),"",I12-H12+1)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="K12" s="61" t="n">
+        <x:f>IF(OR(H12="",I12=""),"",NETWORKDAYS(H12,I12,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L12,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H12,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I12,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L12" s="13" t="str">
@@ -2231,22 +2424,23 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N12" s="13" t="str">
-        <x:v>D08; D09; D34; D35; P1-DNS-01; P1-LB-01 Stage A</x:v>
+        <x:v>D08; D09; D34; D35</x:v>
       </x:c>
       <x:c r="O12" s="13" t="str">
         <x:v>RISK-02; RISK-04; RISK-07</x:v>
       </x:c>
       <x:c r="P12" s="13" t="str">
-        <x:v>6개 Kubernetes 노드의 Resolver를 dns01(.52)→dns02(.53) 순서로 자동화하고 fds.internal FQDN·short name, 외부 DNS, 직접 질의, 서비스 회귀, 멱등성, Rollback, 증적 및 Support Review를 모두 검증한다.</x:v>
+        <x:v>Kubernetes 6개 Node의 DNS 전환, 검색 도메인·API FQDN/Short Name·외부 DNS·직접 질의·서비스 회귀·멱등성·Rollback·Evidence 무결성 및 Support Review 완료</x:v>
       </x:c>
       <x:c r="Q12" s="13" t="str">
-        <x:v>2026-09-07 구현·검토·수동 병합 완료. GitHub Actions는 NOT RUN. 다음 정본에 동기화하되 후속 Gate 완료를 자동 승인하지 않는다.</x:v>
+        <x:v>2026-09-07 Runtime·멱등성·회귀·Rollback·무결성 증적과 이하영 승인 리뷰를 완료하고 이권욱 수동 승인으로 PR #1을 병합했다. GitHub Actions 실행은 0건이므로 CI PASS로 기록하지 않는다. v3.1.17의 `In Review` 표시는 발행 시점 스냅샷이며 다음 정본에서 `Done`으로 동기화한다.</x:v>
       </x:c>
       <x:c r="R12" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; 321Team/infra-ansible PR #1; approved HEAD 507d8882a04f53640b07251bcc234b7d6ee81c09; merge 4f9bdb7c08704eebb3d1b294751e51b0721b6af4</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #58 snapshot 2026-09-09T12:14:54Z</x:v>
       </x:c>
       <x:c r="S12" s="13" t="str">
-        <x:v>Complete</x:v>
+        <x:f>IF(G12="Done","Done",IF(I12="","End TBD",IF(I12&lt;'Executive Summary'!$B$4,"Overdue",IF(H12&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
@@ -2282,7 +2476,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K13" s="61" t="n">
-        <x:f>IF(OR(H13="",I13=""),"",NETWORKDAYS(H13,I13,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L13,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H13,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I13,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H13="",I13=""),"",NETWORKDAYS(H13,I13,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L13,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H13,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I13,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="L13" s="13" t="str">
@@ -2292,23 +2486,23 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N13" s="13" t="str">
-        <x:v>Service 80→8000, readiness /readyz, liveness /livez가 배포·호출·복구 시험에서 PASS하고 증적이 승인된다.</x:v>
+        <x:v>D03; D04; D18; D27; D31; D34</x:v>
       </x:c>
       <x:c r="O13" s="13" t="str">
         <x:v>RISK-07; RISK-09</x:v>
       </x:c>
       <x:c r="P13" s="13" t="str">
-        <x:v>transaction-api Service 80→8000과 /readyz·/livez Probe를 구현하고 P1-LB-01·P1-SEC-01의 Entry/Policy 검증 입력으로 제공한다.</x:v>
+        <x:v>2개 Deployment/Service, 업무 8000/8001·metrics 9091/9090, `/livez`·`/readyz`, DB/FDS 장애정책, Resource, local endpoint topology, Contract/E2E Evidence</x:v>
       </x:c>
       <x:c r="Q13" s="13" t="str">
-        <x:v>이재환 09-04 개인 휴가를 owner-specific 비가용일로 반영해 종료를 09-10으로 조정한다. 이하영이 기술 지원하며 G2 09-11 목표는 유지한다. 이하영 2026-09-08 면접 휴가로 당일 지원 가용성이 없다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>이재환 09-04 개인 휴가를 owner-specific 비가용일로 반영해 종료를 09-10으로 조정한다. 이하영이 기술 지원하며 G2 09-11 목표는 유지한다.</x:v>
       </x:c>
       <x:c r="R13" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #15 snapshot 2026-09-10T04:01:11Z</x:v>
       </x:c>
       <x:c r="S13" s="13" t="str">
-        <x:f>IF(G13="Done","Complete",IF(OR(H13="",I13=""),"TBD",IF(I13&lt;'Executive Summary'!$B$4,"Past Due",IF(H13&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Active Window</x:v>
+        <x:f>IF(G13="Done","Done",IF(I13="","End TBD",IF(I13&lt;'Executive Summary'!$B$4,"Overdue",IF(H13&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Active window</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
@@ -2331,7 +2525,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G14" s="13" t="str">
-        <x:v>To Do</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="H14" s="19" t="n">
         <x:v>46266</x:v>
@@ -2344,7 +2538,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K14" s="61" t="n">
-        <x:f>IF(OR(H14="",I14=""),"",NETWORKDAYS(H14,I14,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L14,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H14,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I14,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H14="",I14=""),"",NETWORKDAYS(H14,I14,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L14,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H14,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I14,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="L14" s="13" t="str">
@@ -2354,23 +2548,23 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="N14" s="13" t="str">
-        <x:v>D03; D04; D19</x:v>
+        <x:v>D03; D04; D19; D34; D35</x:v>
       </x:c>
       <x:c r="O14" s="13" t="str">
         <x:v>RISK-06; RISK-08</x:v>
       </x:c>
       <x:c r="P14" s="13" t="str">
-        <x:v>GitHub→Runner→Test→Build→Trivy→Harbor→Kubernetes Deploy→Health/E2E 흐름과 실패 시 Deploy 차단 Evidence 확보</x:v>
+        <x:v>GitHub→Runner→Test→Build→Trivy→Harbor→Kubernetes Deploy→Health/E2E 흐름과 실패 시 Deploy 차단 Evidence 확보; 승인 Digest와 이전 Digest 복구 추적</x:v>
       </x:c>
       <x:c r="Q14" s="13" t="str">
-        <x:v>G1에는 Runner 연결·Harbor Push/Pull까지만 중간검증하고, 전체 Delivery Gate는 G2 전 09-09 완료한다. 이하영 2026-09-08 면접 휴가로 당일 지원 가용성이 없다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>2026-09-08 사전 점검·구현 준비 착수. 기존 계획 09-01~09-09 보존. G1 09-07 목표일은 경과했으나 Runner/Harbor 실제 완료 증적은 미확인. G2 09-11 유지. 일정 재산정은 선행 증적·앱 저장소 확인 후 변경관리로 처리. Ansible 연관 이슈 #5는 앱 Delivery AC를 대체하지 않음.</x:v>
       </x:c>
       <x:c r="R14" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #16 snapshot 2026-09-10T02:09:24Z</x:v>
       </x:c>
       <x:c r="S14" s="13" t="str">
-        <x:f>IF(G14="Done","Complete",IF(OR(H14="",I14=""),"TBD",IF(I14&lt;'Executive Summary'!$B$4,"Past Due",IF(H14&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Active Window</x:v>
+        <x:f>IF(G14="Done","Done",IF(I14="","End TBD",IF(I14&lt;'Executive Summary'!$B$4,"Overdue",IF(H14&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Overdue</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -2378,7 +2572,7 @@
         <x:v>P1-MON-01</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>Prometheus / Node / App Metrics</x:v>
+        <x:v>Kubernetes-Integrated Hybrid Monitoring 구축 및 검증</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
         <x:v>Phase 1</x:v>
@@ -2406,7 +2600,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K15" s="61" t="n">
-        <x:f>IF(OR(H15="",I15=""),"",NETWORKDAYS(H15,I15,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L15,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H15,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I15,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H15="",I15=""),"",NETWORKDAYS(H15,I15,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L15,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H15,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I15,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L15" s="13" t="str">
@@ -2416,23 +2610,23 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="N15" s="13" t="str">
-        <x:v>D05; D14</x:v>
+        <x:v>D05; D14; D17; D19; D33; D34</x:v>
       </x:c>
       <x:c r="O15" s="13" t="str">
         <x:v>RISK-04; RISK-07</x:v>
       </x:c>
       <x:c r="P15" s="13" t="str">
-        <x:v>monitor01 Prometheus가 Node 9100/Kubelet 10250/App 8000/8001을 수집하고 거래·FDS·오류·상태 지표 조회 Evidence 확보</x:v>
+        <x:v>Hybrid Monitoring의 Runtime Acceptance 14개와 필수 보조통제 2개, 구축·복구·Rollback Runbook 및 Support Review 증적 확보</x:v>
       </x:c>
       <x:c r="Q15" s="13" t="str">
         <x:v>이재환 09-04 개인 휴가로 실행 착수를 09-07로 이동한다. 사전 Metrics/Target 설계는 유지하고, 이권욱 지원 아래 K8S/APP 준비 후 통합한다. G2 09-11 목표 유지.</x:v>
       </x:c>
       <x:c r="R15" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #17 snapshot 2026-09-10T04:01:45Z</x:v>
       </x:c>
       <x:c r="S15" s="13" t="str">
-        <x:f>IF(G15="Done","Complete",IF(OR(H15="",I15=""),"TBD",IF(I15&lt;'Executive Summary'!$B$4,"Past Due",IF(H15&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Active Window</x:v>
+        <x:f>IF(G15="Done","Done",IF(I15="","End TBD",IF(I15&lt;'Executive Summary'!$B$4,"Overdue",IF(H15&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Active window</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="44" customHeight="1">
@@ -2468,7 +2662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K16" s="61" t="n">
-        <x:f>IF(OR(H16="",I16=""),"",NETWORKDAYS(H16,I16,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L16,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H16,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I16,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H16="",I16=""),"",NETWORKDAYS(H16,I16,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L16,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H16,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I16,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L16" s="13" t="str">
@@ -2490,10 +2684,11 @@
         <x:v>이재환 09-04 개인 휴가와 P1-DB-01 완료일 조정에 연동해 G1을 09-07로 이동한다. P1-DNS-01 Done, P1-LB-01 Stage A PASS를 반영하며 G2/G3/Phase 1 Close는 유지한다.</x:v>
       </x:c>
       <x:c r="R16" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D36 Team Availability and Status Update</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #18 snapshot 2026-09-09T12:01:41Z</x:v>
       </x:c>
       <x:c r="S16" s="13" t="str">
-        <x:v>Past Due</x:v>
+        <x:f>IF(G16="Done","Done",IF(I16="","End TBD",IF(I16&lt;'Executive Summary'!$B$4,"Overdue",IF(H16&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Overdue</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="44" customHeight="1">
@@ -2516,7 +2711,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G17" s="13" t="str">
-        <x:v>To Do</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="H17" s="19" t="n">
         <x:v>46269</x:v>
@@ -2529,7 +2724,8 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K17" s="61" t="n">
-        <x:v>6</x:v>
+        <x:f>IF(OR(H17="",I17=""),"",NETWORKDAYS(H17,I17,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L17,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H17,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I17,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L17" s="13" t="str">
         <x:v>이하영</x:v>
@@ -2538,23 +2734,23 @@
         <x:v>이권욱, 이재환</x:v>
       </x:c>
       <x:c r="N17" s="13" t="str">
-        <x:v>Restricted SecurityContext와 PSA가 실제 클러스터에서 동작하고, .50/32→30080 Positive 및 비허용 Source→30080 Negative Test가 PASS한다.</x:v>
+        <x:v>D12; D17; D18; D19; D27; D31; D34</x:v>
       </x:c>
       <x:c r="O17" s="13" t="str">
-        <x:v>RISK-06; RISK-07</x:v>
+        <x:v>RISK-06; RISK-07; RISK-08</x:v>
       </x:c>
       <x:c r="P17" s="13" t="str">
-        <x:v>HO-ANS-02B SecurityContext/PSA Restricted live-cluster 호환성과 HO-ANS-04C edge01 .50/32→Worker NodePort 30080 허용·기타 Source 차단을 검증한다.</x:v>
+        <x:v>PSA/SecurityContext/Default Deny/RBAC/HEP-GNP/Secretbox/LimitRange/Probe와 `.50/32→30080` 포함 Positive·Negative·Rollback Evidence PASS</x:v>
       </x:c>
       <x:c r="Q17" s="13" t="str">
-        <x:v>09-04 이재환 지원 부재는 이권욱이 커버한다. Lead 이하영 일정은 유지하며 D34/D35 및 P1-K8S-01 Gate 결과를 반영한다. 이하영 2026-09-08 면접 휴가로 당일 작업·단독 종료를 배치하지 않는다. 일정 재기준선은 별도 Lead 승인 전 수행하지 않는다.</x:v>
+        <x:v>D17/D34 설계 승인 후 Manifest/Prework 착수. 09-08 이하영 개인 부재와 이권욱 지원을 기록하며 기존 일정은 유지한다. Runtime은 Platform Ready·보호 인계·Positive/Negative 증적 조건부다.</x:v>
       </x:c>
       <x:c r="R17" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17; D34; D35; D36</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #19 snapshot 2026-09-10T05:05:52Z</x:v>
       </x:c>
       <x:c r="S17" s="13" t="str">
-        <x:f>IF(G17="Done","Complete",IF(OR(H17="",I17=""),"TBD",IF(I17&lt;'Executive Summary'!$B$4,"Past Due",IF(H17&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Active Window</x:v>
+        <x:f>IF(G17="Done","Done",IF(I17="","End TBD",IF(I17&lt;'Executive Summary'!$B$4,"Overdue",IF(H17&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Active window</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="44" customHeight="1">
@@ -2590,7 +2786,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K18" s="61" t="n">
-        <x:f>IF(OR(H18="",I18=""),"",NETWORKDAYS(H18,I18,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L18,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H18,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I18,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H18="",I18=""),"",NETWORKDAYS(H18,I18,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L18,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H18,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I18,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="L18" s="13" t="str">
@@ -2612,11 +2808,11 @@
         <x:v>이재환 09-14~09-17 부재 중 지원자가 Evidence 정리와 결함 추적을 수행하고, 최종 판정은 09-18 복귀 후 완료한다.</x:v>
       </x:c>
       <x:c r="R18" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #20 snapshot 2026-09-10T04:08:25Z</x:v>
       </x:c>
       <x:c r="S18" s="13" t="str">
-        <x:f>IF(G18="Done","Complete",IF(OR(H18="",I18=""),"TBD",IF(I18&lt;'Executive Summary'!$B$4,"Past Due",IF(H18&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G18="Done","Done",IF(I18="","End TBD",IF(I18&lt;'Executive Summary'!$B$4,"Overdue",IF(H18&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Active window</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="44" customHeight="1">
@@ -2652,7 +2848,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K19" s="61" t="n">
-        <x:f>IF(OR(H19="",I19=""),"",NETWORKDAYS(H19,I19,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L19,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H19,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I19,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H19="",I19=""),"",NETWORKDAYS(H19,I19,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L19,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H19,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I19,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L19" s="13" t="str">
@@ -2674,11 +2870,11 @@
         <x:v>Harbor Restore와 etcd Snapshot/Restore는 P1이다. 운영 데이터 삭제 없이 별도 Restore DB 또는 승인 절차를 사용한다.</x:v>
       </x:c>
       <x:c r="R19" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #21 snapshot 2026-09-10T04:02:43Z</x:v>
       </x:c>
       <x:c r="S19" s="13" t="str">
-        <x:f>IF(G19="Done","Complete",IF(OR(H19="",I19=""),"TBD",IF(I19&lt;'Executive Summary'!$B$4,"Past Due",IF(H19&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G19="Done","Done",IF(I19="","End TBD",IF(I19&lt;'Executive Summary'!$B$4,"Overdue",IF(H19&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Active window</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="44" customHeight="1">
@@ -2714,7 +2910,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K20" s="61" t="n">
-        <x:f>IF(OR(H20="",I20=""),"",NETWORKDAYS(H20,I20,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L20,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H20,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I20,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H20="",I20=""),"",NETWORKDAYS(H20,I20,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L20,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H20,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I20,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L20" s="13" t="str">
@@ -2736,11 +2932,11 @@
         <x:v>Control Plane 장애와 Rolling Update는 P1이다. 본 P0는 Worker 1대 Drain 시 서비스 지속만 검증한다.</x:v>
       </x:c>
       <x:c r="R20" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #22 snapshot 2026-09-10T04:08:14Z</x:v>
       </x:c>
       <x:c r="S20" s="13" t="str">
-        <x:f>IF(G20="Done","Complete",IF(OR(H20="",I20=""),"TBD",IF(I20&lt;'Executive Summary'!$B$4,"Past Due",IF(H20&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G20="Done","Done",IF(I20="","End TBD",IF(I20&lt;'Executive Summary'!$B$4,"Overdue",IF(H20&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Active window</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="44" customHeight="1">
@@ -2776,7 +2972,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K21" s="61" t="n">
-        <x:f>IF(OR(H21="",I21=""),"",NETWORKDAYS(H21,I21,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L21,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H21,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I21,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H21="",I21=""),"",NETWORKDAYS(H21,I21,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L21,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H21,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I21,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L21" s="13" t="str">
@@ -2798,11 +2994,11 @@
         <x:v>D-SEC-01/D17과 DEC-P1-ENTRY-01/D18을 G2 선행조건으로 판정한다. Scope·Approver·Exit Criteria 승인과 External Exposure 결정을 P1-SEC-01 및 P1-APP-01 Evidence에 연결한다.</x:v>
       </x:c>
       <x:c r="R21" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #23 snapshot 2026-09-09T12:03:10Z</x:v>
       </x:c>
       <x:c r="S21" s="13" t="str">
-        <x:f>IF(G21="Done","Complete",IF(OR(H21="",I21=""),"TBD",IF(I21&lt;'Executive Summary'!$B$4,"Past Due",IF(H21&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G21="Done","Done",IF(I21="","End TBD",IF(I21&lt;'Executive Summary'!$B$4,"Overdue",IF(H21&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="44" customHeight="1">
@@ -2838,7 +3034,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K22" s="61" t="n">
-        <x:f>IF(OR(H22="",I22=""),"",NETWORKDAYS(H22,I22,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L22,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H22,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I22,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H22="",I22=""),"",NETWORKDAYS(H22,I22,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L22,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H22,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I22,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L22" s="13" t="str">
@@ -2860,11 +3056,11 @@
         <x:v>이재환 부재 전 09-13까지 HA/DR Evidence 초안을 인계하고 09-18 최종 검토한다.</x:v>
       </x:c>
       <x:c r="R22" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #24 snapshot 2026-09-10T02:09:36Z</x:v>
       </x:c>
       <x:c r="S22" s="13" t="str">
-        <x:f>IF(G22="Done","Complete",IF(OR(H22="",I22=""),"TBD",IF(I22&lt;'Executive Summary'!$B$4,"Past Due",IF(H22&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G22="Done","Done",IF(I22="","End TBD",IF(I22&lt;'Executive Summary'!$B$4,"Overdue",IF(H22&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="44" customHeight="1">
@@ -2872,7 +3068,7 @@
         <x:v>P1-MON-02</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
-        <x:v>Dashboard / Alert Enhancement</x:v>
+        <x:v>Dashboard / Alert / HA / Retention Enhancement</x:v>
       </x:c>
       <x:c r="C23" s="13" t="str">
         <x:v>Phase 1</x:v>
@@ -2900,7 +3096,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K23" s="61" t="n">
-        <x:f>IF(OR(H23="",I23=""),"",NETWORKDAYS(H23,I23,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L23,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H23,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I23,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H23="",I23=""),"",NETWORKDAYS(H23,I23,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L23,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H23,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I23,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L23" s="13" t="str">
@@ -2910,23 +3106,23 @@
         <x:v>이권욱, 이하영</x:v>
       </x:c>
       <x:c r="N23" s="13" t="str">
-        <x:v>D25</x:v>
+        <x:v>D25; D33</x:v>
       </x:c>
       <x:c r="O23" s="13" t="str">
         <x:v>RISK-05; RISK-07; RISK-09; RISK-14</x:v>
       </x:c>
       <x:c r="P23" s="13" t="str">
-        <x:v>거래·FDS·Node·Pod 상태 Dashboard와 최소 Alert Rule을 구성하고 정상·장애 시나리오 Evidence 확보</x:v>
+        <x:v>Prometheus 2 Replica·Alertmanager 3 Replica, PDB/TopologySpread, Dashboard/Alert·장기보존 고도화와 장애·복구·P0 회귀 Evidence 및 Review</x:v>
       </x:c>
       <x:c r="Q23" s="13" t="str">
-        <x:v>P1-MON-01의 Metric 수집 완료 후 수행한다. Grafana 또는 Prometheus UI 중 승인된 최소 구현을 사용하며 Loki/SIEM은 Scope Out이다.</x:v>
+        <x:v>P1-MON-01의 P0 기본 3 View·Alert·15일 Retention·Watchdog 인수 후 HA·Dashboard/Alert·장기보존을 고도화한다. P1 Non-blocking. 이재환 09-14~17 부재를 반영한 가용일 1일이며 범위/일정 재평가는 별도 Lead 결정이다.</x:v>
       </x:c>
       <x:c r="R23" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #25 snapshot 2026-09-10T04:08:35Z</x:v>
       </x:c>
       <x:c r="S23" s="13" t="str">
-        <x:f>IF(G23="Done","Complete",IF(OR(H23="",I23=""),"TBD",IF(I23&lt;'Executive Summary'!$B$4,"Past Due",IF(H23&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G23="Done","Done",IF(I23="","End TBD",IF(I23&lt;'Executive Summary'!$B$4,"Overdue",IF(H23&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
@@ -2962,7 +3158,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K24" s="61" t="n">
-        <x:f>IF(OR(H24="",I24=""),"",NETWORKDAYS(H24,I24,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L24,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H24,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I24,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H24="",I24=""),"",NETWORKDAYS(H24,I24,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L24,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H24,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I24,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L24" s="13" t="str">
@@ -2984,11 +3180,11 @@
         <x:v>기존 P1-DR-02와 기준선의 etcd Snapshot/Restore P1 범위를 통합한다. Harbor HA는 Scope Out이며 미완료 시 Known Issue로 이관한다.</x:v>
       </x:c>
       <x:c r="R24" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #26 snapshot 2026-09-10T02:09:39Z</x:v>
       </x:c>
       <x:c r="S24" s="13" t="str">
-        <x:f>IF(G24="Done","Complete",IF(OR(H24="",I24=""),"TBD",IF(I24&lt;'Executive Summary'!$B$4,"Past Due",IF(H24&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G24="Done","Done",IF(I24="","End TBD",IF(I24&lt;'Executive Summary'!$B$4,"Overdue",IF(H24&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="44" customHeight="1">
@@ -3024,7 +3220,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K25" s="61" t="n">
-        <x:f>IF(OR(H25="",I25=""),"",NETWORKDAYS(H25,I25,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L25,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H25,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I25,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H25="",I25=""),"",NETWORKDAYS(H25,I25,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L25,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H25,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I25,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L25" s="13" t="str">
@@ -3046,11 +3242,11 @@
         <x:v>기존 P1-HA-02와 P1-HA-03 및 기준선의 PDB/TopologySpreadConstraint P1 범위를 통합한다. 미완료 시 Phase 1 Close의 Known Issue에 Owner 이하영과 Due를 기록한다.</x:v>
       </x:c>
       <x:c r="R25" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #27 snapshot 2026-09-10T02:09:41Z</x:v>
       </x:c>
       <x:c r="S25" s="13" t="str">
-        <x:f>IF(G25="Done","Complete",IF(OR(H25="",I25=""),"TBD",IF(I25&lt;'Executive Summary'!$B$4,"Past Due",IF(H25&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G25="Done","Done",IF(I25="","End TBD",IF(I25&lt;'Executive Summary'!$B$4,"Overdue",IF(H25&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="44" customHeight="1">
@@ -3086,7 +3282,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K26" s="61" t="n">
-        <x:f>IF(OR(H26="",I26=""),"",NETWORKDAYS(H26,I26,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L26,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H26,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I26,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H26="",I26=""),"",NETWORKDAYS(H26,I26,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L26,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H26,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I26,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L26" s="13" t="str">
@@ -3108,11 +3304,11 @@
         <x:v>09-20은 일요일이며 Working Days 0이다. 결정 전 해당 일정을 확정된 근무일로 간주하지 않는다.</x:v>
       </x:c>
       <x:c r="R26" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; 2026 Calendar</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #28 snapshot 2026-09-09T12:04:41Z</x:v>
       </x:c>
       <x:c r="S26" s="13" t="str">
-        <x:f>IF(G26="Done","Complete",IF(OR(H26="",I26=""),"TBD",IF(I26&lt;'Executive Summary'!$B$4,"Past Due",IF(H26&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G26="Done","Done",IF(I26="","End TBD",IF(I26&lt;'Executive Summary'!$B$4,"Overdue",IF(H26&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="44" customHeight="1">
@@ -3148,7 +3344,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K27" s="61" t="n">
-        <x:f>IF(OR(H27="",I27=""),"",NETWORKDAYS(H27,I27,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L27,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H27,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I27,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H27="",I27=""),"",NETWORKDAYS(H27,I27,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L27,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H27,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I27,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L27" s="13" t="str">
@@ -3170,11 +3366,11 @@
         <x:v>같은 날 DEC-CAL-P1-01을 종결해 Review 일정을 확정한다.</x:v>
       </x:c>
       <x:c r="R27" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #29 snapshot 2026-09-09T12:04:58Z</x:v>
       </x:c>
       <x:c r="S27" s="13" t="str">
-        <x:f>IF(G27="Done","Complete",IF(OR(H27="",I27=""),"TBD",IF(I27&lt;'Executive Summary'!$B$4,"Past Due",IF(H27&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G27="Done","Done",IF(I27="","End TBD",IF(I27&lt;'Executive Summary'!$B$4,"Overdue",IF(H27&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="44" customHeight="1">
@@ -3210,7 +3406,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K28" s="61" t="n">
-        <x:f>IF(OR(H28="",I28=""),"",NETWORKDAYS(H28,I28,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L28,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H28,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I28,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H28="",I28=""),"",NETWORKDAYS(H28,I28,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L28,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H28,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I28,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="L28" s="13" t="str">
@@ -3232,11 +3428,11 @@
         <x:v>Review 실행일은 D20 결과를 따른다. 09-24~09-25 비근무 전에 09-23 Close를 완료한다.</x:v>
       </x:c>
       <x:c r="R28" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #30 snapshot 2026-09-10T04:08:08Z</x:v>
       </x:c>
       <x:c r="S28" s="13" t="str">
-        <x:f>IF(G28="Done","Complete",IF(OR(H28="",I28=""),"TBD",IF(I28&lt;'Executive Summary'!$B$4,"Past Due",IF(H28&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G28="Done","Done",IF(I28="","End TBD",IF(I28&lt;'Executive Summary'!$B$4,"Overdue",IF(H28&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="44" customHeight="1">
@@ -3272,7 +3468,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K29" s="61" t="n">
-        <x:f>IF(OR(H29="",I29=""),"",NETWORKDAYS(H29,I29,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L29,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H29,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I29,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H29="",I29=""),"",NETWORKDAYS(H29,I29,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L29,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H29,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I29,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="13" t="str">
@@ -3294,11 +3490,11 @@
         <x:v>2026-09-20은 일요일이며 Working Days 0이다. D20이 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
       </x:c>
       <x:c r="R29" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #31 snapshot 2026-09-09T12:05:57Z</x:v>
       </x:c>
       <x:c r="S29" s="13" t="str">
-        <x:f>IF(G29="Done","Complete",IF(OR(H29="",I29=""),"TBD",IF(I29&lt;'Executive Summary'!$B$4,"Past Due",IF(H29&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G29="Done","Done",IF(I29="","End TBD",IF(I29&lt;'Executive Summary'!$B$4,"Overdue",IF(H29&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="44" customHeight="1">
@@ -3334,7 +3530,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K30" s="61" t="n">
-        <x:f>IF(OR(H30="",I30=""),"",NETWORKDAYS(H30,I30,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L30,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H30,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I30,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H30="",I30=""),"",NETWORKDAYS(H30,I30,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L30,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H30,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I30,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L30" s="13" t="str">
@@ -3356,11 +3552,11 @@
         <x:v>09-24~09-25 비근무 전에 종결한다.</x:v>
       </x:c>
       <x:c r="R30" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #32 snapshot 2026-09-09T12:06:14Z</x:v>
       </x:c>
       <x:c r="S30" s="13" t="str">
-        <x:f>IF(G30="Done","Complete",IF(OR(H30="",I30=""),"TBD",IF(I30&lt;'Executive Summary'!$B$4,"Past Due",IF(H30&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G30="Done","Done",IF(I30="","End TBD",IF(I30&lt;'Executive Summary'!$B$4,"Overdue",IF(H30&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="44" customHeight="1">
@@ -3396,7 +3592,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K31" s="61" t="n">
-        <x:f>IF(OR(H31="",I31=""),"",NETWORKDAYS(H31,I31,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L31,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H31,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I31,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H31="",I31=""),"",NETWORKDAYS(H31,I31,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L31,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H31,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I31,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L31" s="13" t="str">
@@ -3418,11 +3614,11 @@
         <x:v>09-24~09-25 비근무 후 첫 작업일에 착수한다.</x:v>
       </x:c>
       <x:c r="R31" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #33 snapshot 2026-09-09T12:06:31Z</x:v>
       </x:c>
       <x:c r="S31" s="13" t="str">
-        <x:f>IF(G31="Done","Complete",IF(OR(H31="",I31=""),"TBD",IF(I31&lt;'Executive Summary'!$B$4,"Past Due",IF(H31&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G31="Done","Done",IF(I31="","End TBD",IF(I31&lt;'Executive Summary'!$B$4,"Overdue",IF(H31&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="44" customHeight="1">
@@ -3458,7 +3654,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K32" s="61" t="n">
-        <x:f>IF(OR(H32="",I32=""),"",NETWORKDAYS(H32,I32,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L32,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H32,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I32,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H32="",I32=""),"",NETWORKDAYS(H32,I32,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L32,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H32,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I32,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L32" s="13" t="str">
@@ -3480,11 +3676,11 @@
         <x:v>MS-P2-START-01 직후 완료하며 Phase 2 모든 구현 티켓이 참조하는 Phase 2 OCI/AWS/ROSA Design의 권위 Source를 생성한다.</x:v>
       </x:c>
       <x:c r="R32" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #34 snapshot 2026-09-10T02:09:45Z</x:v>
       </x:c>
       <x:c r="S32" s="13" t="str">
-        <x:f>IF(G32="Done","Complete",IF(OR(H32="",I32=""),"TBD",IF(I32&lt;'Executive Summary'!$B$4,"Past Due",IF(H32&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G32="Done","Done",IF(I32="","End TBD",IF(I32&lt;'Executive Summary'!$B$4,"Overdue",IF(H32&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="44" customHeight="1">
@@ -3520,7 +3716,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K33" s="61" t="n">
-        <x:f>IF(OR(H33="",I33=""),"",NETWORKDAYS(H33,I33,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L33,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H33,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I33,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H33="",I33=""),"",NETWORKDAYS(H33,I33,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L33,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H33,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I33,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="L33" s="13" t="str">
@@ -3542,11 +3738,11 @@
         <x:v>10-05는 비근무일이다. OCI Go/No-Go 결과에 따라 VPN 입력과 경로를 갱신한다.</x:v>
       </x:c>
       <x:c r="R33" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #35 snapshot 2026-09-10T02:09:47Z</x:v>
       </x:c>
       <x:c r="S33" s="13" t="str">
-        <x:f>IF(G33="Done","Complete",IF(OR(H33="",I33=""),"TBD",IF(I33&lt;'Executive Summary'!$B$4,"Past Due",IF(H33&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G33="Done","Done",IF(I33="","End TBD",IF(I33&lt;'Executive Summary'!$B$4,"Overdue",IF(H33&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="44" customHeight="1">
@@ -3582,7 +3778,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K34" s="61" t="n">
-        <x:f>IF(OR(H34="",I34=""),"",NETWORKDAYS(H34,I34,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L34,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H34,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I34,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H34="",I34=""),"",NETWORKDAYS(H34,I34,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L34,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H34,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I34,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L34" s="13" t="str">
@@ -3604,11 +3800,11 @@
         <x:v>10-02 Go/No-Go를 넘기지 않는다. No-Go 시 Vendor Endpoint→AWS EC2+EIP Relay→Overlay 순으로 승인된 Fallback을 선택한다.</x:v>
       </x:c>
       <x:c r="R34" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #36 snapshot 2026-09-09T12:07:26Z</x:v>
       </x:c>
       <x:c r="S34" s="13" t="str">
-        <x:f>IF(G34="Done","Complete",IF(OR(H34="",I34=""),"TBD",IF(I34&lt;'Executive Summary'!$B$4,"Past Due",IF(H34&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G34="Done","Done",IF(I34="","End TBD",IF(I34&lt;'Executive Summary'!$B$4,"Overdue",IF(H34&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="44" customHeight="1">
@@ -3644,7 +3840,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K35" s="61" t="n">
-        <x:f>IF(OR(H35="",I35=""),"",NETWORKDAYS(H35,I35,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L35,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H35,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I35,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H35="",I35=""),"",NETWORKDAYS(H35,I35,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L35,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H35,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I35,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L35" s="13" t="str">
@@ -3666,11 +3862,11 @@
         <x:v>10-05는 비근무일이다. OCI No-Go 시 D21에서 승인된 Fallback만 사용한다.</x:v>
       </x:c>
       <x:c r="R35" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #37 snapshot 2026-09-10T02:09:49Z</x:v>
       </x:c>
       <x:c r="S35" s="13" t="str">
-        <x:f>IF(G35="Done","Complete",IF(OR(H35="",I35=""),"TBD",IF(I35&lt;'Executive Summary'!$B$4,"Past Due",IF(H35&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G35="Done","Done",IF(I35="","End TBD",IF(I35&lt;'Executive Summary'!$B$4,"Overdue",IF(H35&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="44" customHeight="1">
@@ -3706,7 +3902,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K36" s="61" t="n">
-        <x:f>IF(OR(H36="",I36=""),"",NETWORKDAYS(H36,I36,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L36,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H36,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I36,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H36="",I36=""),"",NETWORKDAYS(H36,I36,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L36,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H36,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I36,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="L36" s="13" t="str">
@@ -3728,11 +3924,11 @@
         <x:v>10-09는 비근무일이다. 계정·Quota·리전 전제는 G4 이전에 확인하고 Cluster 범위를 최소화한다.</x:v>
       </x:c>
       <x:c r="R36" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #38 snapshot 2026-09-10T02:09:51Z</x:v>
       </x:c>
       <x:c r="S36" s="13" t="str">
-        <x:f>IF(G36="Done","Complete",IF(OR(H36="",I36=""),"TBD",IF(I36&lt;'Executive Summary'!$B$4,"Past Due",IF(H36&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G36="Done","Done",IF(I36="","End TBD",IF(I36&lt;'Executive Summary'!$B$4,"Overdue",IF(H36&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="44" customHeight="1">
@@ -3768,7 +3964,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K37" s="61" t="n">
-        <x:f>IF(OR(H37="",I37=""),"",NETWORKDAYS(H37,I37,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L37,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H37,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I37,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H37="",I37=""),"",NETWORKDAYS(H37,I37,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L37,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H37,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I37,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L37" s="13" t="str">
@@ -3790,11 +3986,11 @@
         <x:v>10-05 비근무를 반영한다. OCI No-Go 시 승인 Fallback 기준으로 판정한다.</x:v>
       </x:c>
       <x:c r="R37" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #39 snapshot 2026-09-09T12:08:10Z</x:v>
       </x:c>
       <x:c r="S37" s="13" t="str">
-        <x:f>IF(G37="Done","Complete",IF(OR(H37="",I37=""),"TBD",IF(I37&lt;'Executive Summary'!$B$4,"Past Due",IF(H37&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G37="Done","Done",IF(I37="","End TBD",IF(I37&lt;'Executive Summary'!$B$4,"Overdue",IF(H37&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="44" customHeight="1">
@@ -3830,7 +4026,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K38" s="61" t="n">
-        <x:f>IF(OR(H38="",I38=""),"",NETWORKDAYS(H38,I38,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L38,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H38,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I38,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H38="",I38=""),"",NETWORKDAYS(H38,I38,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L38,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H38,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I38,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L38" s="13" t="str">
@@ -3846,17 +4042,17 @@
         <x:v>RISK-10; RISK-12</x:v>
       </x:c>
       <x:c r="P38" s="13" t="str">
-        <x:v>P0 IP Endpoint 유지 또는 Hybrid DNS P1 적용을 확정하고 Resolver/Forwarding/Zone/Route/테스트·N/A 근거를 승인</x:v>
+        <x:v>P0 IP Endpoint 유지 또는 Hybrid DNS P1 적용을 확정하고 Resolver/Forwarding/Zone/Route/테스트·Cancelled 결정 근거를 승인</x:v>
       </x:c>
       <x:c r="Q38" s="13" t="str">
         <x:v>Hybrid P0 E2E는 IP Endpoint를 허용하므로 본 P1 결정 미완료가 G5/G6를 자동 차단하지 않는다.</x:v>
       </x:c>
       <x:c r="R38" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #40 snapshot 2026-09-09T12:08:24Z</x:v>
       </x:c>
       <x:c r="S38" s="13" t="str">
-        <x:f>IF(G38="Done","Complete",IF(OR(H38="",I38=""),"TBD",IF(I38&lt;'Executive Summary'!$B$4,"Past Due",IF(H38&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G38="Done","Done",IF(I38="","End TBD",IF(I38&lt;'Executive Summary'!$B$4,"Overdue",IF(H38&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="44" customHeight="1">
@@ -3892,7 +4088,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K39" s="61" t="n">
-        <x:f>IF(OR(H39="",I39=""),"",NETWORKDAYS(H39,I39,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L39,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H39,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I39,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H39="",I39=""),"",NETWORKDAYS(H39,I39,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L39,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H39,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I39,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L39" s="13" t="str">
@@ -3914,11 +4110,11 @@
         <x:v>D26에서 Direct Catalog 선택 시 P2-OP-01은 Cancelled 처리하고, Mirror 선택 시 P2-OP-01을 활성화한다.</x:v>
       </x:c>
       <x:c r="R39" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #41 snapshot 2026-09-09T12:08:39Z</x:v>
       </x:c>
       <x:c r="S39" s="13" t="str">
-        <x:f>IF(G39="Done","Complete",IF(OR(H39="",I39=""),"TBD",IF(I39&lt;'Executive Summary'!$B$4,"Past Due",IF(H39&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G39="Done","Done",IF(I39="","End TBD",IF(I39&lt;'Executive Summary'!$B$4,"Overdue",IF(H39&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="44" customHeight="1">
@@ -3954,7 +4150,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K40" s="61" t="n">
-        <x:f>IF(OR(H40="",I40=""),"",NETWORKDAYS(H40,I40,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L40,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H40,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I40,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H40="",I40=""),"",NETWORKDAYS(H40,I40,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L40,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H40,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I40,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L40" s="13" t="str">
@@ -3976,11 +4172,11 @@
         <x:v>기준선의 ROSA→Harbor는 Optional이다. P2-APP-01 최종 Image 경로 전 10-16까지 확정한다.</x:v>
       </x:c>
       <x:c r="R40" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #42 snapshot 2026-09-09T12:08:53Z</x:v>
       </x:c>
       <x:c r="S40" s="13" t="str">
-        <x:f>IF(G40="Done","Complete",IF(OR(H40="",I40=""),"TBD",IF(I40&lt;'Executive Summary'!$B$4,"Past Due",IF(H40&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G40="Done","Done",IF(I40="","End TBD",IF(I40&lt;'Executive Summary'!$B$4,"Overdue",IF(H40&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="44" customHeight="1">
@@ -4016,7 +4212,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K41" s="61" t="n">
-        <x:f>IF(OR(H41="",I41=""),"",NETWORKDAYS(H41,I41,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L41,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H41,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I41,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H41="",I41=""),"",NETWORKDAYS(H41,I41,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L41,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H41,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I41,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L41" s="13" t="str">
@@ -4038,11 +4234,11 @@
         <x:v>Image Source는 D22 결정에 따르며 Harbor 사용을 사전 가정하지 않는다. Manifest/Image 계약은 P2-CICD-01의 Runner 기반 ROSA Delivery에 연결한다.</x:v>
       </x:c>
       <x:c r="R41" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #43 snapshot 2026-09-10T02:09:53Z</x:v>
       </x:c>
       <x:c r="S41" s="13" t="str">
-        <x:f>IF(G41="Done","Complete",IF(OR(H41="",I41=""),"TBD",IF(I41&lt;'Executive Summary'!$B$4,"Past Due",IF(H41&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G41="Done","Done",IF(I41="","End TBD",IF(I41&lt;'Executive Summary'!$B$4,"Overdue",IF(H41&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="44" customHeight="1">
@@ -4078,7 +4274,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K42" s="61" t="n">
-        <x:f>IF(OR(H42="",I42=""),"",NETWORKDAYS(H42,I42,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L42,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H42,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I42,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H42="",I42=""),"",NETWORKDAYS(H42,I42,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L42,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H42,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I42,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="L42" s="13" t="str">
@@ -4100,11 +4296,11 @@
         <x:v>Backup 생성만으로 DONE 처리하지 않고 Restore 또는 승인된 복구 검증이 필요하다.</x:v>
       </x:c>
       <x:c r="R42" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #44 snapshot 2026-09-10T02:09:55Z</x:v>
       </x:c>
       <x:c r="S42" s="13" t="str">
-        <x:f>IF(G42="Done","Complete",IF(OR(H42="",I42=""),"TBD",IF(I42&lt;'Executive Summary'!$B$4,"Past Due",IF(H42&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G42="Done","Done",IF(I42="","End TBD",IF(I42&lt;'Executive Summary'!$B$4,"Overdue",IF(H42&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="44" customHeight="1">
@@ -4140,7 +4336,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K43" s="61" t="n">
-        <x:f>IF(OR(H43="",I43=""),"",NETWORKDAYS(H43,I43,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L43,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H43,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I43,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H43="",I43=""),"",NETWORKDAYS(H43,I43,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L43,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H43,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I43,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L43" s="13" t="str">
@@ -4162,11 +4358,11 @@
         <x:v>Registry는 D22, Hybrid DNS는 D23을 따른다. D23 미적용은 P0 IP Endpoint 사용 시 Non-blocker다.</x:v>
       </x:c>
       <x:c r="R43" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #45 snapshot 2026-09-09T12:09:48Z</x:v>
       </x:c>
       <x:c r="S43" s="13" t="str">
-        <x:f>IF(G43="Done","Complete",IF(OR(H43="",I43=""),"TBD",IF(I43&lt;'Executive Summary'!$B$4,"Past Due",IF(H43&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G43="Done","Done",IF(I43="","End TBD",IF(I43&lt;'Executive Summary'!$B$4,"Overdue",IF(H43&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="44" customHeight="1">
@@ -4202,7 +4398,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K44" s="61" t="n">
-        <x:f>IF(OR(H44="",I44=""),"",NETWORKDAYS(H44,I44,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L44,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H44,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I44,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H44="",I44=""),"",NETWORKDAYS(H44,I44,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L44,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H44,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I44,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L44" s="13" t="str">
@@ -4224,11 +4420,11 @@
         <x:v>P2-ROSA-01과 P2-APP-01의 Manifest/Image 계약을 사용하고 Registry는 D22 결과를 따른다. G5 ROSA Application Ready에 연결한다.</x:v>
       </x:c>
       <x:c r="R44" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #46 snapshot 2026-09-10T02:09:57Z</x:v>
       </x:c>
       <x:c r="S44" s="13" t="str">
-        <x:f>IF(G44="Done","Complete",IF(OR(H44="",I44=""),"TBD",IF(I44&lt;'Executive Summary'!$B$4,"Past Due",IF(H44&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G44="Done","Done",IF(I44="","End TBD",IF(I44&lt;'Executive Summary'!$B$4,"Overdue",IF(H44&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="44" customHeight="1">
@@ -4264,7 +4460,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K45" s="61" t="n">
-        <x:f>IF(OR(H45="",I45=""),"",NETWORKDAYS(H45,I45,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L45,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H45,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I45,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H45="",I45=""),"",NETWORKDAYS(H45,I45,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L45,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H45,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I45,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L45" s="13" t="str">
@@ -4286,11 +4482,11 @@
         <x:v>Harbor는 D22에 따라 사용 또는 Cancelled 처리한다. Hybrid DNS는 D23에 따라 적용 또는 IP Endpoint로 검증한다.</x:v>
       </x:c>
       <x:c r="R45" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #47 snapshot 2026-09-10T02:09:59Z</x:v>
       </x:c>
       <x:c r="S45" s="13" t="str">
-        <x:f>IF(G45="Done","Complete",IF(OR(H45="",I45=""),"TBD",IF(I45&lt;'Executive Summary'!$B$4,"Past Due",IF(H45&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G45="Done","Done",IF(I45="","End TBD",IF(I45&lt;'Executive Summary'!$B$4,"Overdue",IF(H45&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="44" customHeight="1">
@@ -4326,7 +4522,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K46" s="61" t="n">
-        <x:f>IF(OR(H46="",I46=""),"",NETWORKDAYS(H46,I46,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L46,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H46,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I46,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H46="",I46=""),"",NETWORKDAYS(H46,I46,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L46,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H46,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I46,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L46" s="13" t="str">
@@ -4342,17 +4538,17 @@
         <x:v>RISK-10; RISK-12; RISK-15</x:v>
       </x:c>
       <x:c r="P46" s="13" t="str">
-        <x:v>D23이 Hybrid DNS를 선택한 경우 Resolver/Conditional Forwarding/Route/Query Test PASS; IP Endpoint 유지 시 N/A 근거 승인</x:v>
+        <x:v>D23이 Hybrid DNS를 선택한 경우 Resolver/Conditional Forwarding/Route/Query Test PASS; IP Endpoint 유지 시 Cancelled 결정 근거 승인</x:v>
       </x:c>
       <x:c r="Q46" s="13" t="str">
         <x:v>DEC-P2-DNS-01 / D23 결정 결과가 미구현이면 Status=Cancelled와 결정 근거를 기록한다. 구현 시 Hybrid E2E IP Endpoint에 대한 영향을 검증한다.</x:v>
       </x:c>
       <x:c r="R46" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #48 snapshot 2026-09-10T02:10:01Z</x:v>
       </x:c>
       <x:c r="S46" s="13" t="str">
-        <x:f>IF(G46="Done","Complete",IF(OR(H46="",I46=""),"TBD",IF(I46&lt;'Executive Summary'!$B$4,"Past Due",IF(H46&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G46="Done","Done",IF(I46="","End TBD",IF(I46&lt;'Executive Summary'!$B$4,"Overdue",IF(H46&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="44" customHeight="1">
@@ -4388,7 +4584,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K47" s="61" t="n">
-        <x:f>IF(OR(H47="",I47=""),"",NETWORKDAYS(H47,I47,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L47,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H47,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I47,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H47="",I47=""),"",NETWORKDAYS(H47,I47,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L47,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H47,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I47,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L47" s="13" t="str">
@@ -4410,11 +4606,11 @@
         <x:v>10-23 Deliverable Freeze와 DEC-CAL-P2-01을 함께 완료한다.</x:v>
       </x:c>
       <x:c r="R47" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #49 snapshot 2026-09-10T02:10:03Z</x:v>
       </x:c>
       <x:c r="S47" s="13" t="str">
-        <x:f>IF(G47="Done","Complete",IF(OR(H47="",I47=""),"TBD",IF(I47&lt;'Executive Summary'!$B$4,"Past Due",IF(H47&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G47="Done","Done",IF(I47="","End TBD",IF(I47&lt;'Executive Summary'!$B$4,"Overdue",IF(H47&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="44" customHeight="1">
@@ -4450,7 +4646,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K48" s="61" t="n">
-        <x:f>IF(OR(H48="",I48=""),"",NETWORKDAYS(H48,I48,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L48,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H48,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I48,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H48="",I48=""),"",NETWORKDAYS(H48,I48,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L48,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H48,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I48,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="L48" s="13" t="str">
@@ -4472,11 +4668,11 @@
         <x:v>IP Endpoint와 Registry N/A 여부는 승인 Decision 결과를 Expected에 반영한다.</x:v>
       </x:c>
       <x:c r="R48" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #50 snapshot 2026-09-10T02:10:05Z</x:v>
       </x:c>
       <x:c r="S48" s="13" t="str">
-        <x:f>IF(G48="Done","Complete",IF(OR(H48="",I48=""),"TBD",IF(I48&lt;'Executive Summary'!$B$4,"Past Due",IF(H48&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G48="Done","Done",IF(I48="","End TBD",IF(I48&lt;'Executive Summary'!$B$4,"Overdue",IF(H48&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="44" customHeight="1">
@@ -4512,7 +4708,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K49" s="61" t="n">
-        <x:f>IF(OR(H49="",I49=""),"",NETWORKDAYS(H49,I49,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L49,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H49,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I49,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H49="",I49=""),"",NETWORKDAYS(H49,I49,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L49,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H49,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I49,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L49" s="13" t="str">
@@ -4528,17 +4724,17 @@
         <x:v>RISK-06; RISK-11; RISK-15</x:v>
       </x:c>
       <x:c r="P49" s="13" t="str">
-        <x:v>D26이 Mirror를 선택한 경우 oc-mirror ImageSet·Harbor Push·Custom CatalogSource·Package 조회 PASS; Direct Catalog 선택 시 N/A 근거 승인</x:v>
+        <x:v>D26이 Mirror를 선택한 경우 oc-mirror ImageSet·Harbor Push·Custom CatalogSource·Package 조회 PASS; Direct Catalog 선택 시 Cancelled 결정 근거 승인</x:v>
       </x:c>
       <x:c r="Q49" s="13" t="str">
         <x:v>DEC-P2-OP-01 / D26에서 Direct Catalog를 선택하면 Status=Cancelled와 결정 근거를 기록한다. Mirror 선택 시 구현을 진행한다.</x:v>
       </x:c>
       <x:c r="R49" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Network_Baseline_v2.3; FDS_Phase1_Logical_Architecture_v3.1.2</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #51 snapshot 2026-09-10T02:10:07Z</x:v>
       </x:c>
       <x:c r="S49" s="13" t="str">
-        <x:f>IF(G49="Done","Complete",IF(OR(H49="",I49=""),"TBD",IF(I49&lt;'Executive Summary'!$B$4,"Past Due",IF(H49&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G49="Done","Done",IF(I49="","End TBD",IF(I49&lt;'Executive Summary'!$B$4,"Overdue",IF(H49&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="44" customHeight="1">
@@ -4574,7 +4770,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K50" s="61" t="n">
-        <x:f>IF(OR(H50="",I50=""),"",NETWORKDAYS(H50,I50,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L50,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H50,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I50,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H50="",I50=""),"",NETWORKDAYS(H50,I50,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L50,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H50,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I50,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L50" s="13" t="str">
@@ -4596,11 +4792,11 @@
         <x:v>2026-10-24는 토요일이며 Working Days 0이다. Project Close 10-26 영향을 함께 검토한다.</x:v>
       </x:c>
       <x:c r="R50" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; 2026 Calendar</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #52 snapshot 2026-09-09T12:11:51Z</x:v>
       </x:c>
       <x:c r="S50" s="13" t="str">
-        <x:f>IF(G50="Done","Complete",IF(OR(H50="",I50=""),"TBD",IF(I50&lt;'Executive Summary'!$B$4,"Past Due",IF(H50&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G50="Done","Done",IF(I50="","End TBD",IF(I50&lt;'Executive Summary'!$B$4,"Overdue",IF(H50&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="44" customHeight="1">
@@ -4636,7 +4832,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K51" s="61" t="n">
-        <x:f>IF(OR(H51="",I51=""),"",NETWORKDAYS(H51,I51,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L51,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H51,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I51,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H51="",I51=""),"",NETWORKDAYS(H51,I51,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L51,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H51,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I51,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L51" s="13" t="str">
@@ -4658,11 +4854,11 @@
         <x:v>Hybrid DNS와 Operator 공급망은 D23/D26 결과에 따라 구현 또는 Cancelled 처리한다. 같은 날 DEC-CAL-P2-01 검토를 시작해 Review 일정을 10-23까지 확정한다.</x:v>
       </x:c>
       <x:c r="R51" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #53 snapshot 2026-09-09T12:12:06Z</x:v>
       </x:c>
       <x:c r="S51" s="13" t="str">
-        <x:f>IF(G51="Done","Complete",IF(OR(H51="",I51=""),"TBD",IF(I51&lt;'Executive Summary'!$B$4,"Past Due",IF(H51&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G51="Done","Done",IF(I51="","End TBD",IF(I51&lt;'Executive Summary'!$B$4,"Overdue",IF(H51&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="44" customHeight="1">
@@ -4698,7 +4894,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K52" s="61" t="n">
-        <x:f>IF(OR(H52="",I52=""),"",NETWORKDAYS(H52,I52,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L52,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H52,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I52,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H52="",I52=""),"",NETWORKDAYS(H52,I52,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L52,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H52,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I52,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L52" s="13" t="str">
@@ -4720,11 +4916,11 @@
         <x:v>Freeze 이후 변경은 Review Action 또는 Change Request로만 허용한다.</x:v>
       </x:c>
       <x:c r="R52" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #54 snapshot 2026-09-09T12:12:22Z</x:v>
       </x:c>
       <x:c r="S52" s="13" t="str">
-        <x:f>IF(G52="Done","Complete",IF(OR(H52="",I52=""),"TBD",IF(I52&lt;'Executive Summary'!$B$4,"Past Due",IF(H52&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G52="Done","Done",IF(I52="","End TBD",IF(I52&lt;'Executive Summary'!$B$4,"Overdue",IF(H52&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="44" customHeight="1">
@@ -4760,7 +4956,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K53" s="61" t="n">
-        <x:f>IF(OR(H53="",I53=""),"",NETWORKDAYS(H53,I53,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L53,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H53,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I53,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H53="",I53=""),"",NETWORKDAYS(H53,I53,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L53,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H53,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I53,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L53" s="13" t="str">
@@ -4782,11 +4978,11 @@
         <x:v>Review 실행일은 D24 결과를 따른다. 최종 Close 목표는 10-26이다.</x:v>
       </x:c>
       <x:c r="R53" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #55 snapshot 2026-09-10T02:10:09Z</x:v>
       </x:c>
       <x:c r="S53" s="13" t="str">
-        <x:f>IF(G53="Done","Complete",IF(OR(H53="",I53=""),"TBD",IF(I53&lt;'Executive Summary'!$B$4,"Past Due",IF(H53&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+        <x:f>IF(G53="Done","Done",IF(I53="","End TBD",IF(I53&lt;'Executive Summary'!$B$4,"Overdue",IF(H53&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="44" customHeight="1">
@@ -4822,7 +5018,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K54" s="61" t="n">
-        <x:f>IF(OR(H54="",I54=""),"",NETWORKDAYS(H54,I54,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L54,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H54,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I54,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
+        <x:f>IF(OR(H54="",I54=""),"",NETWORKDAYS(H54,I54,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L54,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H54,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I54,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L54" s="13" t="str">
@@ -4844,73 +5040,259 @@
         <x:v>2026-10-24는 토요일이며 Working Days 0이다. D24가 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
       </x:c>
       <x:c r="R54" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #56 snapshot 2026-09-09T12:12:58Z</x:v>
       </x:c>
       <x:c r="S54" s="13" t="str">
-        <x:f>IF(G54="Done","Complete",IF(OR(H54="",I54=""),"TBD",IF(I54&lt;'Executive Summary'!$B$4,"Past Due",IF(H54&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" t="str">
+        <x:f>IF(G54="Done","Done",IF(I54="","End TBD",IF(I54&lt;'Executive Summary'!$B$4,"Overdue",IF(H54&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="83" t="str">
         <x:v>MS-PROJECT-CLOSE-01</x:v>
       </x:c>
-      <x:c r="B55" t="str">
+      <x:c r="B55" s="83" t="str">
         <x:v>Project Close</x:v>
       </x:c>
-      <x:c r="C55" t="str">
+      <x:c r="C55" s="83" t="str">
         <x:v>Phase 2</x:v>
       </x:c>
-      <x:c r="D55" t="str">
+      <x:c r="D55" s="83" t="str">
         <x:v>Milestone / Close</x:v>
       </x:c>
-      <x:c r="E55" t="str">
+      <x:c r="E55" s="83" t="str">
         <x:v>Milestone</x:v>
       </x:c>
-      <x:c r="F55" t="str">
+      <x:c r="F55" s="83" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G55" t="str">
+      <x:c r="G55" s="83" t="str">
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="H55" t="n">
+      <x:c r="H55" s="84" t="n">
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="I55" t="n">
+      <x:c r="I55" s="84" t="n">
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="J55" t="n">
+      <x:c r="J55" s="85" t="n">
         <x:f>IF(OR(H55="",I55=""),"",I55-H55+1)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K55" t="n">
-        <x:f>IF(OR(H55="",I55=""),"",NETWORKDAYS(H55,I55,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$10,L55,'Team Calendar'!$C$5:$C$10,"&gt;="&amp;H55,'Team Calendar'!$C$5:$C$10,"&lt;="&amp;I55,'Team Calendar'!$F$5:$F$10,"Personal absence"))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L55" t="str">
+      <x:c r="K55" s="85" t="n">
+        <x:f>IF(OR(H55="",I55=""),"",NETWORKDAYS(H55,I55,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L55,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H55,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I55,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L55" s="83" t="str">
         <x:v>이권욱</x:v>
       </x:c>
-      <x:c r="M55" t="str">
+      <x:c r="M55" s="83" t="str">
         <x:v>이하영, 이재환</x:v>
       </x:c>
-      <x:c r="N55" t="str">
+      <x:c r="N55" s="83" t="str">
         <x:v>D24</x:v>
       </x:c>
-      <x:c r="O55" t="str">
+      <x:c r="O55" s="83" t="str">
         <x:v>RISK-05; RISK-11; RISK-13</x:v>
       </x:c>
-      <x:c r="P55" t="str">
+      <x:c r="P55" s="83" t="str">
         <x:v>Review Action, P0 승인, 후속 P1/Known Issue, Cloud Resource/Cost, Source/Deliverable 인계 및 Project Close Sign-off 확보</x:v>
       </x:c>
-      <x:c r="Q55" t="str">
+      <x:c r="Q55" s="83" t="str">
         <x:v>D24가 Review를 10-26 이후로 이동시키면 Project Close도 Change Request 대상이다.</x:v>
       </x:c>
-      <x:c r="R55" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.12; FDS_Phase1_Logical_Architecture_v3.1.2; Phase 2 OCI/AWS/ROSA Design</x:v>
-      </x:c>
-      <x:c r="S55" t="str">
-        <x:f>IF(G55="Done","Complete",IF(OR(H55="",I55=""),"TBD",IF(I55&lt;'Executive Summary'!$B$4,"Past Due",IF(H55&lt;='Executive Summary'!$B$4,"Active Window","Planned"))))</x:f>
-        <x:v>Planned</x:v>
+      <x:c r="R55" s="83" t="str">
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #57 snapshot 2026-09-09T12:13:16Z</x:v>
+      </x:c>
+      <x:c r="S55" s="83" t="str">
+        <x:f>IF(G55="Done","Done",IF(I55="","End TBD",IF(I55&lt;'Executive Summary'!$B$4,"Overdue",IF(H55&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Upcoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="83" t="str">
+        <x:v>DEC-P1-FDS-01</x:v>
+      </x:c>
+      <x:c r="B56" s="83" t="str">
+        <x:v>거래 보류 도입 범위·판정·평가 실패·Gate 편입 결정</x:v>
+      </x:c>
+      <x:c r="C56" s="83" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="D56" s="83" t="str">
+        <x:v>Application / Governance</x:v>
+      </x:c>
+      <x:c r="E56" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="F56" s="83" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G56" s="83" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="H56" s="84" t="n">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="I56" s="84" t="n">
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="J56" s="85" t="n">
+        <x:f>IF(OR(H56="",I56=""),"",I56-H56+1)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K56" s="85" t="n">
+        <x:f>IF(OR(H56="",I56=""),"",NETWORKDAYS(H56,I56,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L56,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H56,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I56,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L56" s="83" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="M56" s="83" t="str">
+        <x:v>이하영, 이권욱</x:v>
+      </x:c>
+      <x:c r="N56" s="83" t="str">
+        <x:v>D03; D12; D17; D28; D34; D36; D37</x:v>
+      </x:c>
+      <x:c r="O56" s="83" t="str">
+        <x:v>현행 정의 연결 대기. v1.0 인용: RISK-05; RISK-07; RISK-09 — 본 종결의 위험 승인 근거로 사용하지 않음</x:v>
+      </x:c>
+      <x:c r="P56" s="83" t="str">
+        <x:v>현행 탐지·기록 유지, 신규 보류·운영 기능 미도입, 실패 정책·계약 소유권, G2 영향 없음 및 후속 검증·재검토 조건 기록</x:v>
+      </x:c>
+      <x:c r="Q56" s="83" t="str">
+        <x:v>현행 유지·신규 기능 확대 유예 결정 Done. 본 v3.1.18 후보에 통합하며 발행 전 운영 정본은 v3.1.17이다. 신규 기능 G2 편입·Runtime 승인은 아니다.</x:v>
+      </x:c>
+      <x:c r="R56" s="83" t="str">
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #4 snapshot 2026-09-10T01:21:55Z</x:v>
+      </x:c>
+      <x:c r="S56" s="83" t="str">
+        <x:f>IF(G56="Done","Done",IF(I56="","End TBD",IF(I56&lt;'Executive Summary'!$B$4,"Overdue",IF(H56&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Done</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="83" t="str">
+        <x:v>DEC-P1-TXN-01</x:v>
+      </x:c>
+      <x:c r="B57" s="83" t="str">
+        <x:v>거래 상태·API 응답·재시도·데이터 정합성 계약 결정</x:v>
+      </x:c>
+      <x:c r="C57" s="83" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="D57" s="83" t="str">
+        <x:v>Application / Data / Interface</x:v>
+      </x:c>
+      <x:c r="E57" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="F57" s="83" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G57" s="83" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="H57" s="84" t="n">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="I57" s="84" t="n">
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="J57" s="85" t="n">
+        <x:f>IF(OR(H57="",I57=""),"",I57-H57+1)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K57" s="85" t="n">
+        <x:f>IF(OR(H57="",I57=""),"",NETWORKDAYS(H57,I57,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L57,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H57,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I57,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L57" s="83" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="M57" s="83" t="str">
+        <x:v>이하영, 이권욱</x:v>
+      </x:c>
+      <x:c r="N57" s="83" t="str">
+        <x:v>D03; D04; D18; D28; D34; D35; DEC-P1-FDS-01</x:v>
+      </x:c>
+      <x:c r="O57" s="83" t="str">
+        <x:v>현행 정의 연결 대기. v1.0 인용: RISK-05; RISK-07; RISK-09 — 본 종결의 위험 승인 근거로 사용하지 않음</x:v>
+      </x:c>
+      <x:c r="P57" s="83" t="str">
+        <x:v>기존 계약 유지 선택, 신규 상태/API·Migration 변경 유예, #4/#6과 정책·표현 소유권 및 기존 구현 정합성 후속 기록</x:v>
+      </x:c>
+      <x:c r="Q57" s="83" t="str">
+        <x:v>현행 유지·신규 기능 확대 유예 결정 Done. 본 v3.1.18 후보에 통합하며 발행 전 운영 정본은 v3.1.17이다. 신규 기능 G2 편입·Runtime 승인은 아니다.</x:v>
+      </x:c>
+      <x:c r="R57" s="83" t="str">
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #5 snapshot 2026-09-10T01:22:10Z</x:v>
+      </x:c>
+      <x:c r="S57" s="83" t="str">
+        <x:f>IF(G57="Done","Done",IF(I57="","End TBD",IF(I57&lt;'Executive Summary'!$B$4,"Overdue",IF(H57&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Done</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="83" t="str">
+        <x:v>DEC-P1-ADMIN-01</x:v>
+      </x:c>
+      <x:c r="B58" s="83" t="str">
+        <x:v>보안 시연 범위·테스트 전제·조건부 운영 통제 결정</x:v>
+      </x:c>
+      <x:c r="C58" s="83" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="D58" s="83" t="str">
+        <x:v>Application Security / Demonstration / Governance</x:v>
+      </x:c>
+      <x:c r="E58" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="F58" s="83" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G58" s="83" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="H58" s="84" t="n">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="I58" s="84" t="n">
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="J58" s="85" t="n">
+        <x:f>IF(OR(H58="",I58=""),"",I58-H58+1)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K58" s="85" t="n">
+        <x:f>IF(OR(H58="",I58=""),"",NETWORKDAYS(H58,I58,'Sources &amp; Change Log'!$J$2:$J$5)-COUNTIFS('Team Calendar'!$A$5:$A$11,L58,'Team Calendar'!$C$5:$C$11,"&gt;="&amp;H58,'Team Calendar'!$C$5:$C$11,"&lt;="&amp;I58,'Team Calendar'!$F$5:$F$11,"Personal absence"))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L58" s="83" t="str">
+        <x:v>이하영</x:v>
+      </x:c>
+      <x:c r="M58" s="83" t="str">
+        <x:v>이권욱, 이재환</x:v>
+      </x:c>
+      <x:c r="N58" s="83" t="str">
+        <x:v>D03; D12; D17; D18; D19; D28; D33; D34; D35; DEC-P1-FDS-01; DEC-P1-TXN-01; OID-01</x:v>
+      </x:c>
+      <x:c r="O58" s="83" t="str">
+        <x:v>현행 정의 연결 대기. v1.0 인용: RISK-05; RISK-06; RISK-07; RISK-08; RISK-09 — 본 종결의 위험 승인 근거로 사용하지 않음</x:v>
+      </x:c>
+      <x:c r="P58" s="83" t="str">
+        <x:v>프론트엔드 배치 제외, 합성 데이터·최소 노출 원칙, 5개 검토 축 적용/유예, 기존 접근 통제 재사용 및 후속 시나리오 인계 기록</x:v>
+      </x:c>
+      <x:c r="Q58" s="83" t="str">
+        <x:v>현행 유지·신규 기능 확대 유예 결정 Done. 본 v3.1.18 후보에 통합하며 발행 전 운영 정본은 v3.1.17이다. 신규 기능 G2 편입·Runtime 승인은 아니다.</x:v>
+      </x:c>
+      <x:c r="R58" s="83" t="str">
+        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #6 snapshot 2026-09-10T01:22:24Z</x:v>
+      </x:c>
+      <x:c r="S58" s="83" t="str">
+        <x:f>IF(G58="Done","Done",IF(I58="","End TBD",IF(I58&lt;'Executive Summary'!$B$4,"Overdue",IF(H58&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4927,17 +5309,33 @@
     <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Overdue"/>
     <x:cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="End TBD"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:conditionalFormatting sqref="G55:G58">
+    <x:cfRule type="containsText" dxfId="23" priority="7" operator="containsText" text="Done"/>
+    <x:cfRule type="containsText" dxfId="24" priority="8" operator="containsText" text="In Progress"/>
+    <x:cfRule type="containsText" dxfId="25" priority="9" operator="containsText" text="In Review"/>
+    <x:cfRule type="containsText" dxfId="26" priority="10" operator="containsText" text="Blocked"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="S55:S58">
+    <x:cfRule type="containsText" dxfId="27" priority="11" operator="containsText" text="Overdue"/>
+    <x:cfRule type="containsText" dxfId="28" priority="12" operator="containsText" text="End TBD"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="G4:G54">
       <x:formula1>"To Do,In Progress,In Review,Blocked,Done"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F4:F54">
       <x:formula1>"P0,P1,P2"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="G55:G58">
+      <x:formula1>"To Do,In Progress,In Review,Blocked,Done"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F55:F58">
+      <x:formula1>"P0,P1,P2"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ac23de9b2b248f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd8a636ecc1340c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4984,115 +5382,47 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · Phase 1 Gantt (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="N1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="O1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="Q1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="S1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="T1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="U1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="V1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="W1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="X1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="Y1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="Z1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AA1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AB1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AC1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AD1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AE1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AF1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AG1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AH1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
-      <x:c r="AI1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 1 Gantt</x:v>
-      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
+      <x:c r="K1" s="79"/>
+      <x:c r="L1" s="79"/>
+      <x:c r="M1" s="79"/>
+      <x:c r="N1" s="79"/>
+      <x:c r="O1" s="79"/>
+      <x:c r="P1" s="79"/>
+      <x:c r="Q1" s="79"/>
+      <x:c r="R1" s="79"/>
+      <x:c r="S1" s="79"/>
+      <x:c r="T1" s="79"/>
+      <x:c r="U1" s="79"/>
+      <x:c r="V1" s="79"/>
+      <x:c r="W1" s="79"/>
+      <x:c r="X1" s="79"/>
+      <x:c r="Y1" s="79"/>
+      <x:c r="Z1" s="79"/>
+      <x:c r="AA1" s="79"/>
+      <x:c r="AB1" s="79"/>
+      <x:c r="AC1" s="79"/>
+      <x:c r="AD1" s="79"/>
+      <x:c r="AE1" s="79"/>
+      <x:c r="AF1" s="79"/>
+      <x:c r="AG1" s="79"/>
+      <x:c r="AH1" s="79"/>
+      <x:c r="AI1" s="79"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="21" t="str">
-        <x:v>Window 2026-08-26 → 2026-09-23 · As of 2026-09-08 · Formula-driven bars · L = owner-specific personal absence</x:v>
+        <x:v>As of 2026-09-10 | 2026-08-26–2026-09-23 | CANDIDATE · plan dates retained</x:v>
       </x:c>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -5238,21 +5568,27 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="13" t="str">
+        <x:f>WBS!A4</x:f>
         <x:v>D-SEC-01</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
+        <x:f>WBS!B4</x:f>
         <x:v>Security Design Scope / Approval Review</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
+        <x:f>WBS!G4</x:f>
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="D5" s="19" t="n">
+      <x:c r="D5" s="86" t="n">
+        <x:f>IF(WBS!H4="","",WBS!H4)</x:f>
         <x:v>46260</x:v>
       </x:c>
-      <x:c r="E5" s="19" t="n">
+      <x:c r="E5" s="86" t="n">
+        <x:f>IF(WBS!I4="","",WBS!I4)</x:f>
         <x:v>46266</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
+        <x:f>WBS!L4</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G5" s="23" t="n">
@@ -5352,21 +5688,27 @@
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="13" t="str">
+        <x:f>WBS!A5</x:f>
         <x:v>MS-G0-01</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
+        <x:f>WBS!B5</x:f>
         <x:v>G0 Design Freeze</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
+        <x:f>WBS!G5</x:f>
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="D6" s="19" t="n">
+      <x:c r="D6" s="86" t="n">
+        <x:f>IF(WBS!H5="","",WBS!H5)</x:f>
         <x:v>46260</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="n">
+      <x:c r="E6" s="86" t="n">
+        <x:f>IF(WBS!I5="","",WBS!I5)</x:f>
         <x:v>46266</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
+        <x:f>WBS!L5</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G6" s="23" t="n">
@@ -5466,21 +5808,27 @@
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="13" t="str">
+        <x:f>WBS!A7</x:f>
         <x:v>P1-K8S-01</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
+        <x:f>WBS!B7</x:f>
         <x:v>kubeadm 3CP + 3Worker / Calico</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
+        <x:f>WBS!G7</x:f>
         <x:v>In Progress</x:v>
       </x:c>
-      <x:c r="D7" s="19" t="n">
+      <x:c r="D7" s="86" t="n">
+        <x:f>IF(WBS!H7="","",WBS!H7)</x:f>
         <x:v>46261</x:v>
       </x:c>
-      <x:c r="E7" s="19" t="n">
+      <x:c r="E7" s="86" t="n">
+        <x:f>IF(WBS!I7="","",WBS!I7)</x:f>
         <x:v>46269</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
+        <x:f>WBS!L7</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G7" s="23" t="str">
@@ -5532,7 +5880,7 @@
         <x:f>IF($D7="","",IF($E7="",IF(S$4=$D7,1,""),IF(AND(S$4&gt;=$D7,S$4&lt;=$E7),1,"")))</x:f>
       </x:c>
       <x:c r="T7" s="75" t="str">
-        <x:v>L</x:v>
+        <x:f>IF($D7="","",IF($E7="",IF(T$4=$D7,1,""),IF(AND(T$4&gt;=$D7,T$4&lt;=$E7),1,"")))</x:f>
       </x:c>
       <x:c r="U7" s="23" t="str">
         <x:f>IF($D7="","",IF($E7="",IF(U$4=$D7,1,""),IF(AND(U$4&gt;=$D7,U$4&lt;=$E7),1,"")))</x:f>
@@ -5582,21 +5930,27 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="13" t="str">
+        <x:f>WBS!A6</x:f>
         <x:v>P1-LB-01</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
+        <x:f>WBS!B6</x:f>
         <x:v>Kubernetes API Load Balancer</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
+        <x:f>WBS!G6</x:f>
         <x:v>In Progress</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="n">
+      <x:c r="D8" s="86" t="n">
+        <x:f>IF(WBS!H6="","",WBS!H6)</x:f>
         <x:v>46261</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="n">
+      <x:c r="E8" s="86" t="n">
+        <x:f>IF(WBS!I6="","",WBS!I6)</x:f>
         <x:v>46272</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
+        <x:f>WBS!L6</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G8" s="23" t="str">
@@ -5701,21 +6055,27 @@
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="13" t="str">
+        <x:f>WBS!A8</x:f>
         <x:v>P1-DB-01</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
+        <x:f>WBS!B8</x:f>
         <x:v>PostgreSQL External VM</x:v>
       </x:c>
       <x:c r="C9" s="13" t="str">
+        <x:f>WBS!G8</x:f>
         <x:v>In Progress</x:v>
       </x:c>
-      <x:c r="D9" s="19" t="n">
+      <x:c r="D9" s="86" t="n">
+        <x:f>IF(WBS!H8="","",WBS!H8)</x:f>
         <x:v>46262</x:v>
       </x:c>
-      <x:c r="E9" s="19" t="n">
+      <x:c r="E9" s="86" t="n">
+        <x:f>IF(WBS!I8="","",WBS!I8)</x:f>
         <x:v>46272</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
+        <x:f>WBS!L8</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G9" s="23" t="str">
@@ -5752,8 +6112,9 @@
         <x:f>IF($D9="","",IF($E9="",IF(O$4=$D9,1,""),IF(AND(O$4&gt;=$D9,O$4&lt;=$E9),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P9" s="66" t="str">
-        <x:v>L</x:v>
+      <x:c r="P9" s="66" t="n">
+        <x:f>IF($D9="","",IF($E9="",IF(P$4=$D9,1,""),IF(AND(P$4&gt;=$D9,P$4&lt;=$E9),1,"")))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q9" s="25" t="n">
         <x:f>IF($D9="","",IF($E9="",IF(Q$4=$D9,1,""),IF(AND(Q$4&gt;=$D9,Q$4&lt;=$E9),1,"")))</x:f>
@@ -5818,21 +6179,27 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="13" t="str">
+        <x:f>WBS!A9</x:f>
         <x:v>P1-DNS-01</x:v>
       </x:c>
       <x:c r="B10" s="13" t="str">
-        <x:v>BIND Primary / Secondary</x:v>
+        <x:f>WBS!B9</x:f>
+        <x:v>Internal DNS Primary/Secondary</x:v>
       </x:c>
       <x:c r="C10" s="13" t="str">
+        <x:f>WBS!G9</x:f>
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="n">
+      <x:c r="D10" s="86" t="n">
+        <x:f>IF(WBS!H9="","",WBS!H9)</x:f>
         <x:v>46262</x:v>
       </x:c>
-      <x:c r="E10" s="19" t="n">
+      <x:c r="E10" s="86" t="n">
+        <x:f>IF(WBS!I9="","",WBS!I9)</x:f>
         <x:v>46268</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
+        <x:f>WBS!L9</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G10" s="23" t="str">
@@ -5932,21 +6299,27 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="13" t="str">
+        <x:f>WBS!A10</x:f>
         <x:v>P1-HBR-01</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
+        <x:f>WBS!B10</x:f>
         <x:v>Harbor / Trivy Registry</x:v>
       </x:c>
       <x:c r="C11" s="13" t="str">
-        <x:v>To Do</x:v>
-      </x:c>
-      <x:c r="D11" s="19" t="n">
+        <x:f>WBS!G10</x:f>
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="D11" s="86" t="n">
+        <x:f>IF(WBS!H10="","",WBS!H10)</x:f>
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="E11" s="19" t="n">
+      <x:c r="E11" s="86" t="n">
+        <x:f>IF(WBS!I10="","",WBS!I10)</x:f>
         <x:v>46269</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
+        <x:f>WBS!L10</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G11" s="23" t="str">
@@ -5994,7 +6367,7 @@
         <x:f>IF($D11="","",IF($E11="",IF(S$4=$D11,1,""),IF(AND(S$4&gt;=$D11,S$4&lt;=$E11),1,"")))</x:f>
       </x:c>
       <x:c r="T11" s="75" t="str">
-        <x:v>L</x:v>
+        <x:f>IF($D11="","",IF($E11="",IF(T$4=$D11,1,""),IF(AND(T$4&gt;=$D11,T$4&lt;=$E11),1,"")))</x:f>
       </x:c>
       <x:c r="U11" s="23" t="str">
         <x:f>IF($D11="","",IF($E11="",IF(U$4=$D11,1,""),IF(AND(U$4&gt;=$D11,U$4&lt;=$E11),1,"")))</x:f>
@@ -6044,19 +6417,26 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="13" t="str">
+        <x:f>WBS!A11</x:f>
         <x:v>ICR-D-NET-01-01</x:v>
       </x:c>
       <x:c r="B12" s="13" t="str">
-        <x:v>Kubernetes Node Host Firewall &amp; Monitoring Route</x:v>
+        <x:f>WBS!B11</x:f>
+        <x:v>Kubernetes Node Host Firewall / Monitoring Route</x:v>
       </x:c>
       <x:c r="C12" s="13" t="str">
+        <x:f>WBS!G11</x:f>
         <x:v>In Progress</x:v>
       </x:c>
-      <x:c r="D12" s="19" t="n">
+      <x:c r="D12" s="86" t="n">
+        <x:f>IF(WBS!H11="","",WBS!H11)</x:f>
         <x:v>46266</x:v>
       </x:c>
-      <x:c r="E12" s="19"/>
+      <x:c r="E12" s="86" t="str">
+        <x:f>IF(WBS!I11="","",WBS!I11)</x:f>
+      </x:c>
       <x:c r="F12" s="13" t="str">
+        <x:f>WBS!L11</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G12" s="23" t="str">
@@ -6150,21 +6530,27 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="13" t="str">
+        <x:f>WBS!A12</x:f>
         <x:v>CR-P1-ANS-01-01</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>Kubernetes Node DNS Resolver Automation</x:v>
+        <x:f>WBS!B12</x:f>
+        <x:v>Ansible Kubernetes Node DNS Resolver 변경</x:v>
       </x:c>
       <x:c r="C13" s="13" t="str">
+        <x:f>WBS!G12</x:f>
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="D13" s="19" t="n">
+      <x:c r="D13" s="86" t="n">
+        <x:f>IF(WBS!H12="","",WBS!H12)</x:f>
         <x:v>46269</x:v>
       </x:c>
-      <x:c r="E13" s="19" t="n">
+      <x:c r="E13" s="86" t="n">
+        <x:f>IF(WBS!I12="","",WBS!I12)</x:f>
         <x:v>46272</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
+        <x:f>WBS!L12</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G13" s="23" t="str">
@@ -6261,21 +6647,27 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="13" t="str">
+        <x:f>WBS!A13</x:f>
         <x:v>P1-APP-01</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
+        <x:f>WBS!B13</x:f>
         <x:v>transaction-api / fds-engine</x:v>
       </x:c>
       <x:c r="C14" s="13" t="str">
+        <x:f>WBS!G13</x:f>
         <x:v>In Progress</x:v>
       </x:c>
-      <x:c r="D14" s="19" t="n">
+      <x:c r="D14" s="86" t="n">
+        <x:f>IF(WBS!H13="","",WBS!H13)</x:f>
         <x:v>46266</x:v>
       </x:c>
-      <x:c r="E14" s="19" t="n">
+      <x:c r="E14" s="86" t="n">
+        <x:f>IF(WBS!I13="","",WBS!I13)</x:f>
         <x:v>46275</x:v>
       </x:c>
       <x:c r="F14" s="13" t="str">
+        <x:f>WBS!L13</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G14" s="23" t="str">
@@ -6309,6 +6701,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P14" s="23" t="n">
+        <x:f>IF($D14="","",IF($E14="",IF(P$4=$D14,1,""),IF(AND(P$4&gt;=$D14,P$4&lt;=$E14),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q14" s="25" t="n">
@@ -6377,21 +6770,27 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="13" t="str">
+        <x:f>WBS!A14</x:f>
         <x:v>P1-CICD-01</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
+        <x:f>WBS!B14</x:f>
         <x:v>GitHub Actions / Self-hosted Runner Delivery</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
-        <x:v>To Do</x:v>
-      </x:c>
-      <x:c r="D15" s="19" t="n">
+        <x:f>WBS!G14</x:f>
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="D15" s="86" t="n">
+        <x:f>IF(WBS!H14="","",WBS!H14)</x:f>
         <x:v>46266</x:v>
       </x:c>
-      <x:c r="E15" s="19" t="n">
+      <x:c r="E15" s="86" t="n">
+        <x:f>IF(WBS!I14="","",WBS!I14)</x:f>
         <x:v>46274</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
+        <x:f>WBS!L14</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G15" s="23" t="str">
@@ -6493,21 +6892,27 @@
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="13" t="str">
+        <x:f>WBS!A16</x:f>
         <x:v>MS-G1-01</x:v>
       </x:c>
       <x:c r="B16" s="13" t="str">
+        <x:f>WBS!B16</x:f>
         <x:v>G1 Infrastructure Ready</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
+        <x:f>WBS!G16</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D16" s="19" t="n">
+      <x:c r="D16" s="86" t="n">
+        <x:f>IF(WBS!H16="","",WBS!H16)</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="E16" s="19" t="n">
+      <x:c r="E16" s="86" t="n">
+        <x:f>IF(WBS!I16="","",WBS!I16)</x:f>
         <x:v>46272</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
+        <x:f>WBS!L16</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G16" s="23" t="str">
@@ -6601,21 +7006,27 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="13" t="str">
+        <x:f>WBS!A15</x:f>
         <x:v>P1-MON-01</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>Prometheus / Node / App Metrics</x:v>
+        <x:f>WBS!B15</x:f>
+        <x:v>Kubernetes-Integrated Hybrid Monitoring 구축 및 검증</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
+        <x:f>WBS!G15</x:f>
         <x:v>In Progress</x:v>
       </x:c>
-      <x:c r="D17" s="19" t="n">
+      <x:c r="D17" s="86" t="n">
+        <x:f>IF(WBS!H15="","",WBS!H15)</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="E17" s="19" t="n">
+      <x:c r="E17" s="86" t="n">
+        <x:f>IF(WBS!I15="","",WBS!I15)</x:f>
         <x:v>46276</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
+        <x:f>WBS!L15</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G17" s="23" t="str">
@@ -6645,7 +7056,9 @@
       <x:c r="O17" s="23" t="str">
         <x:f>IF($D17="","",IF($E17="",IF(O$4=$D17,1,""),IF(AND(O$4&gt;=$D17,O$4&lt;=$E17),1,"")))</x:f>
       </x:c>
-      <x:c r="P17" s="23" t="str"/>
+      <x:c r="P17" s="23" t="str">
+        <x:f>IF($D17="","",IF($E17="",IF(P$4=$D17,1,""),IF(AND(P$4&gt;=$D17,P$4&lt;=$E17),1,"")))</x:f>
+      </x:c>
       <x:c r="Q17" s="25" t="str">
         <x:f>IF($D17="","",IF($E17="",IF(Q$4=$D17,1,""),IF(AND(Q$4&gt;=$D17,Q$4&lt;=$E17),1,"")))</x:f>
       </x:c>
@@ -6711,21 +7124,27 @@
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="13" t="str">
+        <x:f>WBS!A17</x:f>
         <x:v>P1-SEC-01</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
+        <x:f>WBS!B17</x:f>
         <x:v>Kubernetes Security Controls</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
-        <x:v>To Do</x:v>
-      </x:c>
-      <x:c r="D18" s="19" t="n">
+        <x:f>WBS!G17</x:f>
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="D18" s="86" t="n">
+        <x:f>IF(WBS!H17="","",WBS!H17)</x:f>
         <x:v>46269</x:v>
       </x:c>
-      <x:c r="E18" s="19" t="n">
+      <x:c r="E18" s="86" t="n">
+        <x:f>IF(WBS!I17="","",WBS!I17)</x:f>
         <x:v>46276</x:v>
       </x:c>
       <x:c r="F18" s="13" t="str">
+        <x:f>WBS!L17</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G18" s="23" t="str">
@@ -6772,6 +7191,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T18" s="23" t="n">
+        <x:f>IF($D18="","",IF($E18="",IF(T$4=$D18,1,""),IF(AND(T$4&gt;=$D18,T$4&lt;=$E18),1,"")))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="U18" s="23" t="n">
@@ -6825,21 +7245,27 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="13" t="str">
+        <x:f>WBS!A18</x:f>
         <x:v>P1-E2E-01</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
+        <x:f>WBS!B18</x:f>
         <x:v>Initial / Final E2E &amp; Regression</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
+        <x:f>WBS!G18</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D19" s="19" t="n">
+      <x:c r="D19" s="86" t="n">
+        <x:f>IF(WBS!H18="","",WBS!H18)</x:f>
         <x:v>46274</x:v>
       </x:c>
-      <x:c r="E19" s="19" t="n">
+      <x:c r="E19" s="86" t="n">
+        <x:f>IF(WBS!I18="","",WBS!I18)</x:f>
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F19" s="13" t="str">
+        <x:f>WBS!L18</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G19" s="23" t="str">
@@ -6942,21 +7368,27 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="13" t="str">
+        <x:f>WBS!A19</x:f>
         <x:v>P1-DR-01</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
+        <x:f>WBS!B19</x:f>
         <x:v>PostgreSQL Backup / Restore</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
+        <x:f>WBS!G19</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D20" s="19" t="n">
+      <x:c r="D20" s="86" t="n">
+        <x:f>IF(WBS!H19="","",WBS!H19)</x:f>
         <x:v>46275</x:v>
       </x:c>
-      <x:c r="E20" s="19" t="n">
+      <x:c r="E20" s="86" t="n">
+        <x:f>IF(WBS!I19="","",WBS!I19)</x:f>
         <x:v>46278</x:v>
       </x:c>
       <x:c r="F20" s="13" t="str">
+        <x:f>WBS!L19</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G20" s="23" t="str">
@@ -7053,21 +7485,27 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="13" t="str">
+        <x:f>WBS!A20</x:f>
         <x:v>P1-HA-01</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
+        <x:f>WBS!B20</x:f>
         <x:v>Worker Drain Continuity</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
+        <x:f>WBS!G20</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D21" s="19" t="n">
+      <x:c r="D21" s="86" t="n">
+        <x:f>IF(WBS!H20="","",WBS!H20)</x:f>
         <x:v>46275</x:v>
       </x:c>
-      <x:c r="E21" s="19" t="n">
+      <x:c r="E21" s="86" t="n">
+        <x:f>IF(WBS!I20="","",WBS!I20)</x:f>
         <x:v>46278</x:v>
       </x:c>
       <x:c r="F21" s="13" t="str">
+        <x:f>WBS!L20</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G21" s="23" t="str">
@@ -7164,21 +7602,27 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="13" t="str">
+        <x:f>WBS!A21</x:f>
         <x:v>MS-G2-01</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
+        <x:f>WBS!B21</x:f>
         <x:v>G2 Security / Feature Ready</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
+        <x:f>WBS!G21</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D22" s="19" t="n">
+      <x:c r="D22" s="86" t="n">
+        <x:f>IF(WBS!H21="","",WBS!H21)</x:f>
         <x:v>46276</x:v>
       </x:c>
-      <x:c r="E22" s="19" t="n">
+      <x:c r="E22" s="86" t="n">
+        <x:f>IF(WBS!I21="","",WBS!I21)</x:f>
         <x:v>46276</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
+        <x:f>WBS!L21</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G22" s="23" t="str">
@@ -7272,21 +7716,27 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="13" t="str">
+        <x:f>WBS!A22</x:f>
         <x:v>P1-DOC-01</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
+        <x:f>WBS!B22</x:f>
         <x:v>Architecture / Test / Runbook Freeze</x:v>
       </x:c>
       <x:c r="C23" s="13" t="str">
+        <x:f>WBS!G22</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="n">
+      <x:c r="D23" s="86" t="n">
+        <x:f>IF(WBS!H22="","",WBS!H22)</x:f>
         <x:v>46277</x:v>
       </x:c>
-      <x:c r="E23" s="19" t="n">
+      <x:c r="E23" s="86" t="n">
+        <x:f>IF(WBS!I22="","",WBS!I22)</x:f>
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F23" s="13" t="str">
+        <x:f>WBS!L22</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G23" s="23" t="str">
@@ -7386,21 +7836,27 @@
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="13" t="str">
+        <x:f>WBS!A23</x:f>
         <x:v>P1-MON-02</x:v>
       </x:c>
       <x:c r="B24" s="13" t="str">
-        <x:v>Dashboard / Alert Enhancement</x:v>
+        <x:f>WBS!B23</x:f>
+        <x:v>Dashboard / Alert / HA / Retention Enhancement</x:v>
       </x:c>
       <x:c r="C24" s="13" t="str">
+        <x:f>WBS!G23</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D24" s="19" t="n">
+      <x:c r="D24" s="86" t="n">
+        <x:f>IF(WBS!H23="","",WBS!H23)</x:f>
         <x:v>46277</x:v>
       </x:c>
-      <x:c r="E24" s="19" t="n">
+      <x:c r="E24" s="86" t="n">
+        <x:f>IF(WBS!I23="","",WBS!I23)</x:f>
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F24" s="13" t="str">
+        <x:f>WBS!L23</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G24" s="23" t="str">
@@ -7500,21 +7956,27 @@
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="13" t="str">
+        <x:f>WBS!A24</x:f>
         <x:v>P1-DR-02</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
+        <x:f>WBS!B24</x:f>
         <x:v>Harbor / etcd Backup and Restore</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
+        <x:f>WBS!G24</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D25" s="19" t="n">
+      <x:c r="D25" s="86" t="n">
+        <x:f>IF(WBS!H24="","",WBS!H24)</x:f>
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="E25" s="19" t="n">
+      <x:c r="E25" s="86" t="n">
+        <x:f>IF(WBS!I24="","",WBS!I24)</x:f>
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
+        <x:f>WBS!L24</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G25" s="23" t="str">
@@ -7612,21 +8074,27 @@
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="13" t="str">
+        <x:f>WBS!A25</x:f>
         <x:v>P1-HA-02</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
+        <x:f>WBS!B25</x:f>
         <x:v>Platform Resilience P1 Validation</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
+        <x:f>WBS!G25</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D26" s="19" t="n">
+      <x:c r="D26" s="86" t="n">
+        <x:f>IF(WBS!H25="","",WBS!H25)</x:f>
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="E26" s="19" t="n">
+      <x:c r="E26" s="86" t="n">
+        <x:f>IF(WBS!I25="","",WBS!I25)</x:f>
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
+        <x:f>WBS!L25</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G26" s="23" t="str">
@@ -7724,21 +8192,27 @@
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="13" t="str">
+        <x:f>WBS!A26</x:f>
         <x:v>DEC-CAL-P1-01</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
+        <x:f>WBS!B26</x:f>
         <x:v>Phase 1 Weekend Review Decision</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
+        <x:f>WBS!G26</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D27" s="19" t="n">
+      <x:c r="D27" s="86" t="n">
+        <x:f>IF(WBS!H26="","",WBS!H26)</x:f>
         <x:v>46282</x:v>
       </x:c>
-      <x:c r="E27" s="19" t="n">
+      <x:c r="E27" s="86" t="n">
+        <x:f>IF(WBS!I26="","",WBS!I26)</x:f>
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
+        <x:f>WBS!L26</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G27" s="23" t="str">
@@ -7833,21 +8307,27 @@
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="13" t="str">
+        <x:f>WBS!A27</x:f>
         <x:v>MS-G3-01</x:v>
       </x:c>
       <x:c r="B28" s="13" t="str">
+        <x:f>WBS!B27</x:f>
         <x:v>G3 Review Ready</x:v>
       </x:c>
       <x:c r="C28" s="13" t="str">
+        <x:f>WBS!G27</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D28" s="19" t="n">
+      <x:c r="D28" s="86" t="n">
+        <x:f>IF(WBS!H27="","",WBS!H27)</x:f>
         <x:v>46283</x:v>
       </x:c>
-      <x:c r="E28" s="19" t="n">
+      <x:c r="E28" s="86" t="n">
+        <x:f>IF(WBS!I27="","",WBS!I27)</x:f>
         <x:v>46283</x:v>
       </x:c>
       <x:c r="F28" s="13" t="str">
+        <x:f>WBS!L27</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G28" s="23" t="str">
@@ -7941,21 +8421,27 @@
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="13" t="str">
+        <x:f>WBS!A28</x:f>
         <x:v>P1-REV-01</x:v>
       </x:c>
       <x:c r="B29" s="13" t="str">
+        <x:f>WBS!B28</x:f>
         <x:v>Phase 1 Review / Close Execution</x:v>
       </x:c>
       <x:c r="C29" s="13" t="str">
+        <x:f>WBS!G28</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D29" s="19" t="n">
+      <x:c r="D29" s="86" t="n">
+        <x:f>IF(WBS!H28="","",WBS!H28)</x:f>
         <x:v>46283</x:v>
       </x:c>
-      <x:c r="E29" s="19" t="n">
+      <x:c r="E29" s="86" t="n">
+        <x:f>IF(WBS!I28="","",WBS!I28)</x:f>
         <x:v>46288</x:v>
       </x:c>
       <x:c r="F29" s="13" t="str">
+        <x:f>WBS!L28</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G29" s="23" t="str">
@@ -8054,21 +8540,27 @@
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="13" t="str">
+        <x:f>WBS!A29</x:f>
         <x:v>MS-P1-REVIEW-01</x:v>
       </x:c>
       <x:c r="B30" s="13" t="str">
+        <x:f>WBS!B29</x:f>
         <x:v>Phase 1 Review</x:v>
       </x:c>
       <x:c r="C30" s="13" t="str">
+        <x:f>WBS!G29</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D30" s="19" t="n">
+      <x:c r="D30" s="86" t="n">
+        <x:f>IF(WBS!H29="","",WBS!H29)</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="E30" s="19" t="n">
+      <x:c r="E30" s="86" t="n">
+        <x:f>IF(WBS!I29="","",WBS!I29)</x:f>
         <x:v>46285</x:v>
       </x:c>
       <x:c r="F30" s="13" t="str">
+        <x:f>WBS!L29</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G30" s="23" t="str">
@@ -8160,112 +8652,463 @@
         <x:f>IF($D30="","",IF($E30="",IF(AI$4=$D30,1,""),IF(AND(AI$4&gt;=$D30,AI$4&lt;=$E30),1,"")))</x:f>
       </x:c>
     </x:row>
-    <x:row r="31">
+    <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" t="str">
+        <x:f>WBS!A30</x:f>
         <x:v>MS-P1-CLOSE-01</x:v>
       </x:c>
       <x:c r="B31" t="str">
+        <x:f>WBS!B30</x:f>
         <x:v>Phase 1 Close</x:v>
       </x:c>
       <x:c r="C31" t="str">
+        <x:f>WBS!G30</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="n">
+      <x:c r="D31" s="87" t="n">
+        <x:f>IF(WBS!H30="","",WBS!H30)</x:f>
         <x:v>46288</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="n">
+      <x:c r="E31" s="87" t="n">
+        <x:f>IF(WBS!I30="","",WBS!I30)</x:f>
         <x:v>46288</x:v>
       </x:c>
       <x:c r="F31" t="str">
+        <x:f>WBS!L30</x:f>
         <x:v>이권욱</x:v>
       </x:c>
-      <x:c r="G31" t="str">
+      <x:c r="G31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(G$4=$D31,1,""),IF(AND(G$4&gt;=$D31,G$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="H31" t="str">
+      <x:c r="H31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(H$4=$D31,1,""),IF(AND(H$4&gt;=$D31,H$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="I31" t="str">
+      <x:c r="I31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(I$4=$D31,1,""),IF(AND(I$4&gt;=$D31,I$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="J31" t="str">
+      <x:c r="J31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(J$4=$D31,1,""),IF(AND(J$4&gt;=$D31,J$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="K31" t="str">
+      <x:c r="K31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(K$4=$D31,1,""),IF(AND(K$4&gt;=$D31,K$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="L31" t="str">
+      <x:c r="L31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(L$4=$D31,1,""),IF(AND(L$4&gt;=$D31,L$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="M31" t="str">
+      <x:c r="M31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(M$4=$D31,1,""),IF(AND(M$4&gt;=$D31,M$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="N31" t="str">
+      <x:c r="N31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(N$4=$D31,1,""),IF(AND(N$4&gt;=$D31,N$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="O31" t="str">
+      <x:c r="O31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(O$4=$D31,1,""),IF(AND(O$4&gt;=$D31,O$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="P31" t="str">
+      <x:c r="P31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(P$4=$D31,1,""),IF(AND(P$4&gt;=$D31,P$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="Q31" t="str">
+      <x:c r="Q31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(Q$4=$D31,1,""),IF(AND(Q$4&gt;=$D31,Q$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="R31" t="str">
+      <x:c r="R31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(R$4=$D31,1,""),IF(AND(R$4&gt;=$D31,R$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="S31" t="str">
+      <x:c r="S31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(S$4=$D31,1,""),IF(AND(S$4&gt;=$D31,S$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="T31" t="str">
+      <x:c r="T31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(T$4=$D31,1,""),IF(AND(T$4&gt;=$D31,T$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="U31" t="str">
+      <x:c r="U31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(U$4=$D31,1,""),IF(AND(U$4&gt;=$D31,U$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="V31" t="str">
+      <x:c r="V31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(V$4=$D31,1,""),IF(AND(V$4&gt;=$D31,V$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="W31" t="str">
+      <x:c r="W31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(W$4=$D31,1,""),IF(AND(W$4&gt;=$D31,W$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="X31" t="str">
+      <x:c r="X31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(X$4=$D31,1,""),IF(AND(X$4&gt;=$D31,X$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="Y31" t="str">
+      <x:c r="Y31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(Y$4=$D31,1,""),IF(AND(Y$4&gt;=$D31,Y$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="Z31" t="str">
+      <x:c r="Z31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(Z$4=$D31,1,""),IF(AND(Z$4&gt;=$D31,Z$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AA31" t="str">
+      <x:c r="AA31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AA$4=$D31,1,""),IF(AND(AA$4&gt;=$D31,AA$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AB31" t="str">
+      <x:c r="AB31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AB$4=$D31,1,""),IF(AND(AB$4&gt;=$D31,AB$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AC31" t="str">
+      <x:c r="AC31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AC$4=$D31,1,""),IF(AND(AC$4&gt;=$D31,AC$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AD31" t="str">
+      <x:c r="AD31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AD$4=$D31,1,""),IF(AND(AD$4&gt;=$D31,AD$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AE31" t="str">
+      <x:c r="AE31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AE$4=$D31,1,""),IF(AND(AE$4&gt;=$D31,AE$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AF31" t="str">
+      <x:c r="AF31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AF$4=$D31,1,""),IF(AND(AF$4&gt;=$D31,AF$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AG31" t="str">
+      <x:c r="AG31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AG$4=$D31,1,""),IF(AND(AG$4&gt;=$D31,AG$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AH31" t="str">
+      <x:c r="AH31" s="88" t="str">
         <x:f>IF($D31="","",IF($E31="",IF(AH$4=$D31,1,""),IF(AND(AH$4&gt;=$D31,AH$4&lt;=$E31),1,"")))</x:f>
       </x:c>
-      <x:c r="AI31" s="77" t="n">
+      <x:c r="AI31" s="89" t="n">
         <x:f>IF($D31="","",IF($E31="",IF(AI$4=$D31,1,""),IF(AND(AI$4&gt;=$D31,AI$4&lt;=$E31),1,"")))</x:f>
         <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:f>WBS!A56</x:f>
+        <x:v>DEC-P1-FDS-01</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:f>WBS!B56</x:f>
+        <x:v>거래 보류 도입 범위·판정·평가 실패·Gate 편입 결정</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:f>WBS!G56</x:f>
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D32" s="87" t="n">
+        <x:f>IF(WBS!H56="","",WBS!H56)</x:f>
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="E32" s="87" t="n">
+        <x:f>IF(WBS!I56="","",WBS!I56)</x:f>
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:f>WBS!L56</x:f>
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="G32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(G$4=$D32,1,""),IF(AND(G$4&gt;=$D32,G$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="H32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(H$4=$D32,1,""),IF(AND(H$4&gt;=$D32,H$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="I32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(I$4=$D32,1,""),IF(AND(I$4&gt;=$D32,I$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="J32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(J$4=$D32,1,""),IF(AND(J$4&gt;=$D32,J$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="K32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(K$4=$D32,1,""),IF(AND(K$4&gt;=$D32,K$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="L32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(L$4=$D32,1,""),IF(AND(L$4&gt;=$D32,L$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="M32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(M$4=$D32,1,""),IF(AND(M$4&gt;=$D32,M$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="N32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(N$4=$D32,1,""),IF(AND(N$4&gt;=$D32,N$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="O32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(O$4=$D32,1,""),IF(AND(O$4&gt;=$D32,O$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="P32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(P$4=$D32,1,""),IF(AND(P$4&gt;=$D32,P$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="Q32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(Q$4=$D32,1,""),IF(AND(Q$4&gt;=$D32,Q$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="R32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(R$4=$D32,1,""),IF(AND(R$4&gt;=$D32,R$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="S32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(S$4=$D32,1,""),IF(AND(S$4&gt;=$D32,S$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="T32" s="88" t="n">
+        <x:f>IF($D32="","",IF($E32="",IF(T$4=$D32,1,""),IF(AND(T$4&gt;=$D32,T$4&lt;=$E32),1,"")))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U32" s="88" t="n">
+        <x:f>IF($D32="","",IF($E32="",IF(U$4=$D32,1,""),IF(AND(U$4&gt;=$D32,U$4&lt;=$E32),1,"")))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(V$4=$D32,1,""),IF(AND(V$4&gt;=$D32,V$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="W32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(W$4=$D32,1,""),IF(AND(W$4&gt;=$D32,W$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="X32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(X$4=$D32,1,""),IF(AND(X$4&gt;=$D32,X$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="Y32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(Y$4=$D32,1,""),IF(AND(Y$4&gt;=$D32,Y$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="Z32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(Z$4=$D32,1,""),IF(AND(Z$4&gt;=$D32,Z$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AA32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AA$4=$D32,1,""),IF(AND(AA$4&gt;=$D32,AA$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AB32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AB$4=$D32,1,""),IF(AND(AB$4&gt;=$D32,AB$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AC32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AC$4=$D32,1,""),IF(AND(AC$4&gt;=$D32,AC$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AD32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AD$4=$D32,1,""),IF(AND(AD$4&gt;=$D32,AD$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AE32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AE$4=$D32,1,""),IF(AND(AE$4&gt;=$D32,AE$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AF32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AF$4=$D32,1,""),IF(AND(AF$4&gt;=$D32,AF$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AG32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AG$4=$D32,1,""),IF(AND(AG$4&gt;=$D32,AG$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AH32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AH$4=$D32,1,""),IF(AND(AH$4&gt;=$D32,AH$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+      <x:c r="AI32" s="88" t="str">
+        <x:f>IF($D32="","",IF($E32="",IF(AI$4=$D32,1,""),IF(AND(AI$4&gt;=$D32,AI$4&lt;=$E32),1,"")))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:f>WBS!A57</x:f>
+        <x:v>DEC-P1-TXN-01</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:f>WBS!B57</x:f>
+        <x:v>거래 상태·API 응답·재시도·데이터 정합성 계약 결정</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:f>WBS!G57</x:f>
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D33" s="87" t="n">
+        <x:f>IF(WBS!H57="","",WBS!H57)</x:f>
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="E33" s="87" t="n">
+        <x:f>IF(WBS!I57="","",WBS!I57)</x:f>
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:f>WBS!L57</x:f>
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="G33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(G$4=$D33,1,""),IF(AND(G$4&gt;=$D33,G$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="H33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(H$4=$D33,1,""),IF(AND(H$4&gt;=$D33,H$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="I33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(I$4=$D33,1,""),IF(AND(I$4&gt;=$D33,I$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="J33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(J$4=$D33,1,""),IF(AND(J$4&gt;=$D33,J$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="K33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(K$4=$D33,1,""),IF(AND(K$4&gt;=$D33,K$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="L33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(L$4=$D33,1,""),IF(AND(L$4&gt;=$D33,L$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="M33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(M$4=$D33,1,""),IF(AND(M$4&gt;=$D33,M$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="N33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(N$4=$D33,1,""),IF(AND(N$4&gt;=$D33,N$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="O33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(O$4=$D33,1,""),IF(AND(O$4&gt;=$D33,O$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="P33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(P$4=$D33,1,""),IF(AND(P$4&gt;=$D33,P$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="Q33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(Q$4=$D33,1,""),IF(AND(Q$4&gt;=$D33,Q$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="R33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(R$4=$D33,1,""),IF(AND(R$4&gt;=$D33,R$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="S33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(S$4=$D33,1,""),IF(AND(S$4&gt;=$D33,S$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="T33" s="88" t="n">
+        <x:f>IF($D33="","",IF($E33="",IF(T$4=$D33,1,""),IF(AND(T$4&gt;=$D33,T$4&lt;=$E33),1,"")))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U33" s="88" t="n">
+        <x:f>IF($D33="","",IF($E33="",IF(U$4=$D33,1,""),IF(AND(U$4&gt;=$D33,U$4&lt;=$E33),1,"")))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(V$4=$D33,1,""),IF(AND(V$4&gt;=$D33,V$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="W33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(W$4=$D33,1,""),IF(AND(W$4&gt;=$D33,W$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="X33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(X$4=$D33,1,""),IF(AND(X$4&gt;=$D33,X$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="Y33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(Y$4=$D33,1,""),IF(AND(Y$4&gt;=$D33,Y$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="Z33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(Z$4=$D33,1,""),IF(AND(Z$4&gt;=$D33,Z$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AA33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AA$4=$D33,1,""),IF(AND(AA$4&gt;=$D33,AA$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AB33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AB$4=$D33,1,""),IF(AND(AB$4&gt;=$D33,AB$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AC33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AC$4=$D33,1,""),IF(AND(AC$4&gt;=$D33,AC$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AD33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AD$4=$D33,1,""),IF(AND(AD$4&gt;=$D33,AD$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AE33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AE$4=$D33,1,""),IF(AND(AE$4&gt;=$D33,AE$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AF33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AF$4=$D33,1,""),IF(AND(AF$4&gt;=$D33,AF$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AG33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AG$4=$D33,1,""),IF(AND(AG$4&gt;=$D33,AG$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AH33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AH$4=$D33,1,""),IF(AND(AH$4&gt;=$D33,AH$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+      <x:c r="AI33" s="88" t="str">
+        <x:f>IF($D33="","",IF($E33="",IF(AI$4=$D33,1,""),IF(AND(AI$4&gt;=$D33,AI$4&lt;=$E33),1,"")))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="28" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:f>WBS!A58</x:f>
+        <x:v>DEC-P1-ADMIN-01</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:f>WBS!B58</x:f>
+        <x:v>보안 시연 범위·테스트 전제·조건부 운영 통제 결정</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:f>WBS!G58</x:f>
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D34" s="87" t="n">
+        <x:f>IF(WBS!H58="","",WBS!H58)</x:f>
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="E34" s="87" t="n">
+        <x:f>IF(WBS!I58="","",WBS!I58)</x:f>
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:f>WBS!L58</x:f>
+        <x:v>이하영</x:v>
+      </x:c>
+      <x:c r="G34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(G$4=$D34,1,""),IF(AND(G$4&gt;=$D34,G$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="H34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(H$4=$D34,1,""),IF(AND(H$4&gt;=$D34,H$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="I34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(I$4=$D34,1,""),IF(AND(I$4&gt;=$D34,I$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="J34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(J$4=$D34,1,""),IF(AND(J$4&gt;=$D34,J$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="K34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(K$4=$D34,1,""),IF(AND(K$4&gt;=$D34,K$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="L34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(L$4=$D34,1,""),IF(AND(L$4&gt;=$D34,L$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="M34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(M$4=$D34,1,""),IF(AND(M$4&gt;=$D34,M$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="N34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(N$4=$D34,1,""),IF(AND(N$4&gt;=$D34,N$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="O34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(O$4=$D34,1,""),IF(AND(O$4&gt;=$D34,O$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="P34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(P$4=$D34,1,""),IF(AND(P$4&gt;=$D34,P$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="Q34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(Q$4=$D34,1,""),IF(AND(Q$4&gt;=$D34,Q$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="R34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(R$4=$D34,1,""),IF(AND(R$4&gt;=$D34,R$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="S34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(S$4=$D34,1,""),IF(AND(S$4&gt;=$D34,S$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="T34" s="88" t="n">
+        <x:f>IF($D34="","",IF($E34="",IF(T$4=$D34,1,""),IF(AND(T$4&gt;=$D34,T$4&lt;=$E34),1,"")))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U34" s="88" t="n">
+        <x:f>IF($D34="","",IF($E34="",IF(U$4=$D34,1,""),IF(AND(U$4&gt;=$D34,U$4&lt;=$E34),1,"")))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(V$4=$D34,1,""),IF(AND(V$4&gt;=$D34,V$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="W34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(W$4=$D34,1,""),IF(AND(W$4&gt;=$D34,W$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="X34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(X$4=$D34,1,""),IF(AND(X$4&gt;=$D34,X$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="Y34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(Y$4=$D34,1,""),IF(AND(Y$4&gt;=$D34,Y$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="Z34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(Z$4=$D34,1,""),IF(AND(Z$4&gt;=$D34,Z$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AA34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AA$4=$D34,1,""),IF(AND(AA$4&gt;=$D34,AA$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AB34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AB$4=$D34,1,""),IF(AND(AB$4&gt;=$D34,AB$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AC34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AC$4=$D34,1,""),IF(AND(AC$4&gt;=$D34,AC$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AD34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AD$4=$D34,1,""),IF(AND(AD$4&gt;=$D34,AD$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AE34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AE$4=$D34,1,""),IF(AND(AE$4&gt;=$D34,AE$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AF34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AF$4=$D34,1,""),IF(AND(AF$4&gt;=$D34,AF$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AG34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AG$4=$D34,1,""),IF(AND(AG$4&gt;=$D34,AG$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AH34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AH$4=$D34,1,""),IF(AND(AH$4&gt;=$D34,AH$4&lt;=$E34),1,"")))</x:f>
+      </x:c>
+      <x:c r="AI34" s="88" t="str">
+        <x:f>IF($D34="","",IF($E34="",IF(AI$4=$D34,1,""),IF(AND(AI$4&gt;=$D34,AI$4&lt;=$E34),1,"")))</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8294,6 +9137,28 @@
     <x:cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="Done"/>
     <x:cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="In Progress"/>
     <x:cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="In Review"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G31:AI34">
+    <x:cfRule type="expression" dxfId="29" priority="9">
+      <x:formula>AND(G31=1,$C31="Done")</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="31" priority="11">
+      <x:formula>AND(G31=1,$C31="In Progress")</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="33" priority="13">
+      <x:formula>AND(G31=1,$C31="In Review")</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="35" priority="15">
+      <x:formula>AND(G31=1,$C31="Blocked")</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="36" priority="16">
+      <x:formula>AND(G31=1,$C31="To Do")</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="C31:C34">
+    <x:cfRule type="containsText" dxfId="30" priority="10" operator="containsText" text="Done"/>
+    <x:cfRule type="containsText" dxfId="32" priority="12" operator="containsText" text="In Progress"/>
+    <x:cfRule type="containsText" dxfId="34" priority="14" operator="containsText" text="In Review"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8341,115 +9206,47 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · Phase 2 Gantt (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="N1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="O1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="Q1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="S1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="T1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="U1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="V1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="W1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="X1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="Y1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="Z1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AA1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AB1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AC1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AD1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AE1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AF1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AG1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AH1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
-      <x:c r="AI1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Phase 2 Gantt</x:v>
-      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
+      <x:c r="K1" s="79"/>
+      <x:c r="L1" s="79"/>
+      <x:c r="M1" s="79"/>
+      <x:c r="N1" s="79"/>
+      <x:c r="O1" s="79"/>
+      <x:c r="P1" s="79"/>
+      <x:c r="Q1" s="79"/>
+      <x:c r="R1" s="79"/>
+      <x:c r="S1" s="79"/>
+      <x:c r="T1" s="79"/>
+      <x:c r="U1" s="79"/>
+      <x:c r="V1" s="79"/>
+      <x:c r="W1" s="79"/>
+      <x:c r="X1" s="79"/>
+      <x:c r="Y1" s="79"/>
+      <x:c r="Z1" s="79"/>
+      <x:c r="AA1" s="79"/>
+      <x:c r="AB1" s="79"/>
+      <x:c r="AC1" s="79"/>
+      <x:c r="AD1" s="79"/>
+      <x:c r="AE1" s="79"/>
+      <x:c r="AF1" s="79"/>
+      <x:c r="AG1" s="79"/>
+      <x:c r="AH1" s="79"/>
+      <x:c r="AI1" s="79"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="21" t="str">
-        <x:v>Window 2026-09-21 → 2026-10-23 · As of 2026-09-08 · Formula-driven bars · No approved Phase 2 schedule impact</x:v>
+        <x:v>As of 2026-09-10 | 2026-09-28–2026-10-26 | CANDIDATE · plan dates retained</x:v>
       </x:c>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -8595,21 +9392,27 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="13" t="str">
+        <x:f>WBS!A31</x:f>
         <x:v>MS-P2-START-01</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
+        <x:f>WBS!B31</x:f>
         <x:v>Phase 2 Start</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
+        <x:f>WBS!G31</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D5" s="19" t="n">
+      <x:c r="D5" s="86" t="n">
+        <x:f>IF(WBS!H31="","",WBS!H31)</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="E5" s="19" t="n">
+      <x:c r="E5" s="86" t="n">
+        <x:f>IF(WBS!I31="","",WBS!I31)</x:f>
         <x:v>46293</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
+        <x:f>WBS!L31</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G5" s="23" t="n">
@@ -8703,21 +9506,27 @@
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="13" t="str">
+        <x:f>WBS!A32</x:f>
         <x:v>P2-ARC-01</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
+        <x:f>WBS!B32</x:f>
         <x:v>Hybrid / OCI / AWS / ROSA Architecture Freeze</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
+        <x:f>WBS!G32</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D6" s="19" t="n">
+      <x:c r="D6" s="86" t="n">
+        <x:f>IF(WBS!H32="","",WBS!H32)</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="n">
+      <x:c r="E6" s="86" t="n">
+        <x:f>IF(WBS!I32="","",WBS!I32)</x:f>
         <x:v>46293</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
+        <x:f>WBS!L32</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G6" s="23" t="n">
@@ -8811,21 +9620,27 @@
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="13" t="str">
+        <x:f>WBS!A33</x:f>
         <x:v>P2-IAC-01</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
+        <x:f>WBS!B33</x:f>
         <x:v>AWS / ROSA Terraform IaC</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
+        <x:f>WBS!G33</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D7" s="19" t="n">
+      <x:c r="D7" s="86" t="n">
+        <x:f>IF(WBS!H33="","",WBS!H33)</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="E7" s="19" t="n">
+      <x:c r="E7" s="86" t="n">
+        <x:f>IF(WBS!I33="","",WBS!I33)</x:f>
         <x:v>46303</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
+        <x:f>WBS!L33</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G7" s="23" t="n">
@@ -8929,21 +9744,27 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="13" t="str">
+        <x:f>WBS!A34</x:f>
         <x:v>P2-OCI-01</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
+        <x:f>WBS!B34</x:f>
         <x:v>OCI Relay Go / No-Go</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
+        <x:f>WBS!G34</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="n">
+      <x:c r="D8" s="86" t="n">
+        <x:f>IF(WBS!H34="","",WBS!H34)</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="n">
+      <x:c r="E8" s="86" t="n">
+        <x:f>IF(WBS!I34="","",WBS!I34)</x:f>
         <x:v>46297</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
+        <x:f>WBS!L34</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G8" s="23" t="n">
@@ -9041,21 +9862,27 @@
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="13" t="str">
+        <x:f>WBS!A35</x:f>
         <x:v>P2-VPN-01</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
+        <x:f>WBS!B35</x:f>
         <x:v>OCI Relay / AWS Site-to-Site VPN</x:v>
       </x:c>
       <x:c r="C9" s="13" t="str">
+        <x:f>WBS!G35</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D9" s="19" t="n">
+      <x:c r="D9" s="86" t="n">
+        <x:f>IF(WBS!H35="","",WBS!H35)</x:f>
         <x:v>46296</x:v>
       </x:c>
-      <x:c r="E9" s="19" t="n">
+      <x:c r="E9" s="86" t="n">
+        <x:f>IF(WBS!I35="","",WBS!I35)</x:f>
         <x:v>46303</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
+        <x:f>WBS!L35</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G9" s="23" t="str">
@@ -9156,21 +9983,27 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="13" t="str">
+        <x:f>WBS!A36</x:f>
         <x:v>P2-ROSA-01</x:v>
       </x:c>
       <x:c r="B10" s="13" t="str">
+        <x:f>WBS!B36</x:f>
         <x:v>ROSA Platform / Security</x:v>
       </x:c>
       <x:c r="C10" s="13" t="str">
+        <x:f>WBS!G36</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="n">
+      <x:c r="D10" s="86" t="n">
+        <x:f>IF(WBS!H36="","",WBS!H36)</x:f>
         <x:v>46301</x:v>
       </x:c>
-      <x:c r="E10" s="19" t="n">
+      <x:c r="E10" s="86" t="n">
+        <x:f>IF(WBS!I36="","",WBS!I36)</x:f>
         <x:v>46311</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
+        <x:f>WBS!L36</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G10" s="23" t="str">
@@ -9274,21 +10107,27 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="13" t="str">
+        <x:f>WBS!A37</x:f>
         <x:v>MS-G4-01</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
+        <x:f>WBS!B37</x:f>
         <x:v>G4 Cloud / VPN Ready</x:v>
       </x:c>
       <x:c r="C11" s="13" t="str">
+        <x:f>WBS!G37</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D11" s="19" t="n">
+      <x:c r="D11" s="86" t="n">
+        <x:f>IF(WBS!H37="","",WBS!H37)</x:f>
         <x:v>46303</x:v>
       </x:c>
-      <x:c r="E11" s="19" t="n">
+      <x:c r="E11" s="86" t="n">
+        <x:f>IF(WBS!I37="","",WBS!I37)</x:f>
         <x:v>46303</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
+        <x:f>WBS!L37</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G11" s="23" t="str">
@@ -9382,21 +10221,27 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="13" t="str">
+        <x:f>WBS!A38</x:f>
         <x:v>DEC-P2-DNS-01</x:v>
       </x:c>
       <x:c r="B12" s="13" t="str">
+        <x:f>WBS!B38</x:f>
         <x:v>Hybrid DNS Scope Decision</x:v>
       </x:c>
       <x:c r="C12" s="13" t="str">
+        <x:f>WBS!G38</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D12" s="19" t="n">
+      <x:c r="D12" s="86" t="n">
+        <x:f>IF(WBS!H38="","",WBS!H38)</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="E12" s="19" t="n">
+      <x:c r="E12" s="86" t="n">
+        <x:f>IF(WBS!I38="","",WBS!I38)</x:f>
         <x:v>46311</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
+        <x:f>WBS!L38</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G12" s="23" t="str">
@@ -9494,21 +10339,27 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="13" t="str">
+        <x:f>WBS!A39</x:f>
         <x:v>DEC-P2-OP-01</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
+        <x:f>WBS!B39</x:f>
         <x:v>Operator Supply Chain Scope Decision</x:v>
       </x:c>
       <x:c r="C13" s="13" t="str">
+        <x:f>WBS!G39</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D13" s="19" t="n">
+      <x:c r="D13" s="86" t="n">
+        <x:f>IF(WBS!H39="","",WBS!H39)</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="E13" s="19" t="n">
+      <x:c r="E13" s="86" t="n">
+        <x:f>IF(WBS!I39="","",WBS!I39)</x:f>
         <x:v>46311</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
+        <x:f>WBS!L39</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G13" s="23" t="str">
@@ -9606,21 +10457,27 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="13" t="str">
+        <x:f>WBS!A40</x:f>
         <x:v>DEC-P2-REG-01</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
+        <x:f>WBS!B40</x:f>
         <x:v>ROSA Image Registry Source Decision</x:v>
       </x:c>
       <x:c r="C14" s="13" t="str">
+        <x:f>WBS!G40</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D14" s="19" t="n">
+      <x:c r="D14" s="86" t="n">
+        <x:f>IF(WBS!H40="","",WBS!H40)</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="E14" s="19" t="n">
+      <x:c r="E14" s="86" t="n">
+        <x:f>IF(WBS!I40="","",WBS!I40)</x:f>
         <x:v>46311</x:v>
       </x:c>
       <x:c r="F14" s="13" t="str">
+        <x:f>WBS!L40</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G14" s="23" t="str">
@@ -9718,21 +10575,27 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="13" t="str">
+        <x:f>WBS!A41</x:f>
         <x:v>P2-APP-01</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
+        <x:f>WBS!B41</x:f>
         <x:v>ROSA Application Deployment</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
+        <x:f>WBS!G41</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D15" s="19" t="n">
+      <x:c r="D15" s="86" t="n">
+        <x:f>IF(WBS!H41="","",WBS!H41)</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="E15" s="19" t="n">
+      <x:c r="E15" s="86" t="n">
+        <x:f>IF(WBS!I41="","",WBS!I41)</x:f>
         <x:v>46311</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
+        <x:f>WBS!L41</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G15" s="23" t="str">
@@ -9830,21 +10693,27 @@
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="13" t="str">
+        <x:f>WBS!A42</x:f>
         <x:v>P2-OADP-01</x:v>
       </x:c>
       <x:c r="B16" s="13" t="str">
+        <x:f>WBS!B42</x:f>
         <x:v>OADP / S3 Backup</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
+        <x:f>WBS!G42</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D16" s="19" t="n">
+      <x:c r="D16" s="86" t="n">
+        <x:f>IF(WBS!H42="","",WBS!H42)</x:f>
         <x:v>46310</x:v>
       </x:c>
-      <x:c r="E16" s="19" t="n">
+      <x:c r="E16" s="86" t="n">
+        <x:f>IF(WBS!I42="","",WBS!I42)</x:f>
         <x:v>46317</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
+        <x:f>WBS!L42</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G16" s="23" t="str">
@@ -9945,21 +10814,27 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="13" t="str">
+        <x:f>WBS!A43</x:f>
         <x:v>MS-G5-01</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
+        <x:f>WBS!B43</x:f>
         <x:v>G5 ROSA Application Ready</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
+        <x:f>WBS!G43</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D17" s="19" t="n">
+      <x:c r="D17" s="86" t="n">
+        <x:f>IF(WBS!H43="","",WBS!H43)</x:f>
         <x:v>46311</x:v>
       </x:c>
-      <x:c r="E17" s="19" t="n">
+      <x:c r="E17" s="86" t="n">
+        <x:f>IF(WBS!I43="","",WBS!I43)</x:f>
         <x:v>46311</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
+        <x:f>WBS!L43</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G17" s="23" t="str">
@@ -10053,21 +10928,27 @@
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="13" t="str">
+        <x:f>WBS!A44</x:f>
         <x:v>P2-CICD-01</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
+        <x:f>WBS!B44</x:f>
         <x:v>Runner to ROSA Delivery</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
+        <x:f>WBS!G44</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D18" s="19" t="n">
+      <x:c r="D18" s="86" t="n">
+        <x:f>IF(WBS!H44="","",WBS!H44)</x:f>
         <x:v>46311</x:v>
       </x:c>
-      <x:c r="E18" s="19" t="n">
+      <x:c r="E18" s="86" t="n">
+        <x:f>IF(WBS!I44="","",WBS!I44)</x:f>
         <x:v>46314</x:v>
       </x:c>
       <x:c r="F18" s="13" t="str">
+        <x:f>WBS!L44</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G18" s="23" t="str">
@@ -10164,21 +11045,27 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="13" t="str">
+        <x:f>WBS!A45</x:f>
         <x:v>P2-HYB-01</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
+        <x:f>WBS!B45</x:f>
         <x:v>Hybrid DB / Registry Integration</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
+        <x:f>WBS!G45</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D19" s="19" t="n">
+      <x:c r="D19" s="86" t="n">
+        <x:f>IF(WBS!H45="","",WBS!H45)</x:f>
         <x:v>46311</x:v>
       </x:c>
-      <x:c r="E19" s="19" t="n">
+      <x:c r="E19" s="86" t="n">
+        <x:f>IF(WBS!I45="","",WBS!I45)</x:f>
         <x:v>46317</x:v>
       </x:c>
       <x:c r="F19" s="13" t="str">
+        <x:f>WBS!L45</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G19" s="23" t="str">
@@ -10278,21 +11165,27 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="13" t="str">
+        <x:f>WBS!A46</x:f>
         <x:v>P2-DNS-01</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
+        <x:f>WBS!B46</x:f>
         <x:v>Hybrid DNS Implementation Conditional</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
+        <x:f>WBS!G46</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D20" s="19" t="n">
+      <x:c r="D20" s="86" t="n">
+        <x:f>IF(WBS!H46="","",WBS!H46)</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="E20" s="19" t="n">
+      <x:c r="E20" s="86" t="n">
+        <x:f>IF(WBS!I46="","",WBS!I46)</x:f>
         <x:v>46315</x:v>
       </x:c>
       <x:c r="F20" s="13" t="str">
+        <x:f>WBS!L46</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G20" s="23" t="str">
@@ -10387,21 +11280,27 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="13" t="str">
+        <x:f>WBS!A47</x:f>
         <x:v>P2-DOC-01</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
+        <x:f>WBS!B47</x:f>
         <x:v>Cloud / Hybrid Deliverable Freeze</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
+        <x:f>WBS!G47</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D21" s="19" t="n">
+      <x:c r="D21" s="86" t="n">
+        <x:f>IF(WBS!H47="","",WBS!H47)</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="E21" s="19" t="n">
+      <x:c r="E21" s="86" t="n">
+        <x:f>IF(WBS!I47="","",WBS!I47)</x:f>
         <x:v>46318</x:v>
       </x:c>
       <x:c r="F21" s="13" t="str">
+        <x:f>WBS!L47</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G21" s="23" t="str">
@@ -10499,21 +11398,27 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="13" t="str">
+        <x:f>WBS!A48</x:f>
         <x:v>P2-E2E-01</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
+        <x:f>WBS!B48</x:f>
         <x:v>Hybrid E2E / Regression</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
+        <x:f>WBS!G48</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D22" s="19" t="n">
+      <x:c r="D22" s="86" t="n">
+        <x:f>IF(WBS!H48="","",WBS!H48)</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="E22" s="19" t="n">
+      <x:c r="E22" s="86" t="n">
+        <x:f>IF(WBS!I48="","",WBS!I48)</x:f>
         <x:v>46317</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
+        <x:f>WBS!L48</x:f>
         <x:v>이재환</x:v>
       </x:c>
       <x:c r="G22" s="23" t="str">
@@ -10610,21 +11515,27 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="13" t="str">
+        <x:f>WBS!A49</x:f>
         <x:v>P2-OP-01</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
+        <x:f>WBS!B49</x:f>
         <x:v>Operator Supply Chain Implementation Conditional</x:v>
       </x:c>
       <x:c r="C23" s="13" t="str">
+        <x:f>WBS!G49</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="n">
+      <x:c r="D23" s="86" t="n">
+        <x:f>IF(WBS!H49="","",WBS!H49)</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="E23" s="19" t="n">
+      <x:c r="E23" s="86" t="n">
+        <x:f>IF(WBS!I49="","",WBS!I49)</x:f>
         <x:v>46315</x:v>
       </x:c>
       <x:c r="F23" s="13" t="str">
+        <x:f>WBS!L49</x:f>
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="G23" s="23" t="str">
@@ -10719,21 +11630,27 @@
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="13" t="str">
+        <x:f>WBS!A50</x:f>
         <x:v>DEC-CAL-P2-01</x:v>
       </x:c>
       <x:c r="B24" s="13" t="str">
+        <x:f>WBS!B50</x:f>
         <x:v>Phase 2 Weekend Review Decision</x:v>
       </x:c>
       <x:c r="C24" s="13" t="str">
+        <x:f>WBS!G50</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D24" s="19" t="n">
+      <x:c r="D24" s="86" t="n">
+        <x:f>IF(WBS!H50="","",WBS!H50)</x:f>
         <x:v>46317</x:v>
       </x:c>
-      <x:c r="E24" s="19" t="n">
+      <x:c r="E24" s="86" t="n">
+        <x:f>IF(WBS!I50="","",WBS!I50)</x:f>
         <x:v>46318</x:v>
       </x:c>
       <x:c r="F24" s="13" t="str">
+        <x:f>WBS!L50</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G24" s="23" t="str">
@@ -10828,21 +11745,27 @@
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="13" t="str">
+        <x:f>WBS!A51</x:f>
         <x:v>MS-G6-01</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
+        <x:f>WBS!B51</x:f>
         <x:v>G6 Hybrid Integration Ready</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
+        <x:f>WBS!G51</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D25" s="19" t="n">
+      <x:c r="D25" s="86" t="n">
+        <x:f>IF(WBS!H51="","",WBS!H51)</x:f>
         <x:v>46317</x:v>
       </x:c>
-      <x:c r="E25" s="19" t="n">
+      <x:c r="E25" s="86" t="n">
+        <x:f>IF(WBS!I51="","",WBS!I51)</x:f>
         <x:v>46317</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
+        <x:f>WBS!L51</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G25" s="23" t="str">
@@ -10936,21 +11859,27 @@
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="13" t="str">
+        <x:f>WBS!A52</x:f>
         <x:v>MS-DELIVERABLE-FREEZE-01</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
+        <x:f>WBS!B52</x:f>
         <x:v>Deliverable Freeze</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
+        <x:f>WBS!G52</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D26" s="19" t="n">
+      <x:c r="D26" s="86" t="n">
+        <x:f>IF(WBS!H52="","",WBS!H52)</x:f>
         <x:v>46318</x:v>
       </x:c>
-      <x:c r="E26" s="19" t="n">
+      <x:c r="E26" s="86" t="n">
+        <x:f>IF(WBS!I52="","",WBS!I52)</x:f>
         <x:v>46318</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
+        <x:f>WBS!L52</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G26" s="23" t="str">
@@ -11044,21 +11973,27 @@
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="13" t="str">
+        <x:f>WBS!A53</x:f>
         <x:v>P2-REV-01</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
+        <x:f>WBS!B53</x:f>
         <x:v>Phase 2 Review / Project Close Execution</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
+        <x:f>WBS!G53</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D27" s="19" t="n">
+      <x:c r="D27" s="86" t="n">
+        <x:f>IF(WBS!H53="","",WBS!H53)</x:f>
         <x:v>46318</x:v>
       </x:c>
-      <x:c r="E27" s="19" t="n">
+      <x:c r="E27" s="86" t="n">
+        <x:f>IF(WBS!I53="","",WBS!I53)</x:f>
         <x:v>46321</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
+        <x:f>WBS!L53</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G27" s="23" t="str">
@@ -11155,21 +12090,27 @@
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="13" t="str">
+        <x:f>WBS!A54</x:f>
         <x:v>MS-P2-REVIEW-01</x:v>
       </x:c>
       <x:c r="B28" s="13" t="str">
+        <x:f>WBS!B54</x:f>
         <x:v>Phase 2 Review</x:v>
       </x:c>
       <x:c r="C28" s="13" t="str">
+        <x:f>WBS!G54</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D28" s="19" t="n">
+      <x:c r="D28" s="86" t="n">
+        <x:f>IF(WBS!H54="","",WBS!H54)</x:f>
         <x:v>46319</x:v>
       </x:c>
-      <x:c r="E28" s="19" t="n">
+      <x:c r="E28" s="86" t="n">
+        <x:f>IF(WBS!I54="","",WBS!I54)</x:f>
         <x:v>46319</x:v>
       </x:c>
       <x:c r="F28" s="13" t="str">
+        <x:f>WBS!L54</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G28" s="23" t="str">
@@ -11263,21 +12204,27 @@
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="13" t="str">
+        <x:f>WBS!A55</x:f>
         <x:v>MS-PROJECT-CLOSE-01</x:v>
       </x:c>
       <x:c r="B29" s="13" t="str">
+        <x:f>WBS!B55</x:f>
         <x:v>Project Close</x:v>
       </x:c>
       <x:c r="C29" s="13" t="str">
+        <x:f>WBS!G55</x:f>
         <x:v>To Do</x:v>
       </x:c>
-      <x:c r="D29" s="19" t="n">
+      <x:c r="D29" s="86" t="n">
+        <x:f>IF(WBS!H55="","",WBS!H55)</x:f>
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="E29" s="19" t="n">
+      <x:c r="E29" s="86" t="n">
+        <x:f>IF(WBS!I55="","",WBS!I55)</x:f>
         <x:v>46321</x:v>
       </x:c>
       <x:c r="F29" s="13" t="str">
+        <x:f>WBS!L55</x:f>
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="G29" s="23" t="str">
@@ -11404,7 +12351,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
@@ -11417,36 +12364,18 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · Milestones &amp; Decision Calendar (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Milestones &amp; Decision Calendar</x:v>
-      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="9" t="str">
@@ -11503,13 +12432,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
-        <x:v>D17; D28; D32</x:v>
+        <x:v>D-ARC-01·D-NET-01·D-WBS-01·D-SEC-01 승인과 정본 Evidence를 확인하고 G0 FULL PASS 기록 확보</x:v>
       </x:c>
       <x:c r="I4" s="13" t="str">
         <x:v>G0 Design Freeze FULL PASS (2026-09-01).</x:v>
       </x:c>
       <x:c r="J4" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Recorded; runtime scope remains separate</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -11535,13 +12464,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
-        <x:v>D19; D25; D27</x:v>
+        <x:v>CentOS/containerd, Ansible Inventory/SSH/멱등성, 3CP+3Worker, API LB/Calico, Harbor/Runner/PostgreSQL, Node Connectivity와 Push/Pull 준비도 승인</x:v>
       </x:c>
       <x:c r="I5" s="13" t="str">
-        <x:v>D36에 따라 이재환 09-04 개인 휴가 및 P1-DB-01 완료일과 정렬해 09-07로 이동. G2/G3/Phase 1 Close는 유지.</x:v>
+        <x:v>이재환 09-04 개인 휴가와 P1-DB-01 완료일 조정에 연동해 G1을 09-07로 이동한다. P1-DNS-01 Done, P1-LB-01 Stage A PASS를 반영하며 G2/G3/Phase 1 Close는 유지한다.</x:v>
       </x:c>
       <x:c r="J5" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -11567,13 +12496,13 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="H6" s="13" t="str">
-        <x:v>D17; D18; D19; D27</x:v>
+        <x:v>2-Service MSA, DB 저장, Security P0, CI/CD, Monitoring, Initial E2E/Negative Test/Worker Drain 준비도를 승인</x:v>
       </x:c>
       <x:c r="I6" s="13" t="str">
         <x:v>D-SEC-01/D17과 DEC-P1-ENTRY-01/D18을 G2 선행조건으로 판정한다. Scope·Approver·Exit Criteria 승인과 External Exposure 결정을 P1-SEC-01 및 P1-APP-01 Evidence에 연결한다.</x:v>
       </x:c>
       <x:c r="J6" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -11599,13 +12528,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H7" s="13" t="str">
-        <x:v>D20</x:v>
+        <x:v>Final E2E/Regression, Worker Drain, PostgreSQL Restore, Critical Issue 0, Architecture/Test/Runbook 준비도를 승인</x:v>
       </x:c>
       <x:c r="I7" s="13" t="str">
         <x:v>같은 날 DEC-CAL-P1-01을 종결해 Review 일정을 확정한다.</x:v>
       </x:c>
       <x:c r="J7" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -11631,13 +12560,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H8" s="13" t="str">
-        <x:v>D20</x:v>
+        <x:v>승인된 일정에 Demo/산출물/G3/Known Issue Review를 수행하고 Action 및 승인결과를 기록</x:v>
       </x:c>
       <x:c r="I8" s="13" t="str">
         <x:v>2026-09-20은 일요일이며 Working Days 0이다. D20이 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
       </x:c>
       <x:c r="J8" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -11663,13 +12592,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H9" s="13" t="str">
-        <x:v>D20</x:v>
+        <x:v>Review Action 처리, P0 승인, P1/Known Issue Owner·Due 이관 및 Phase 1 Close Sign-off 확보</x:v>
       </x:c>
       <x:c r="I9" s="13" t="str">
         <x:v>09-24~09-25 비근무 전에 종결한다.</x:v>
       </x:c>
       <x:c r="J9" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -11695,13 +12624,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H10" s="13" t="str">
-        <x:v>D10; D21</x:v>
+        <x:v>Phase 1 Close, Phase 2 계정·권한·일정·P0 범위·OCI Go/No-Go 계획을 확인하고 착수 승인</x:v>
       </x:c>
       <x:c r="I10" s="13" t="str">
         <x:v>09-24~09-25 비근무 후 첫 작업일에 착수한다.</x:v>
       </x:c>
       <x:c r="J10" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -11727,13 +12656,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H11" s="13" t="str">
-        <x:v>D21</x:v>
+        <x:v>Terraform 인프라, 승인 Transit/VPN, Route/Security, ROSA 선행조건 및 승인 TCP 경로 준비도 승인</x:v>
       </x:c>
       <x:c r="I11" s="13" t="str">
         <x:v>10-05 비근무를 반영한다. OCI No-Go 시 승인 Fallback 기준으로 판정한다.</x:v>
       </x:c>
       <x:c r="J11" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -11759,13 +12688,13 @@
         <x:v>이하영</x:v>
       </x:c>
       <x:c r="H12" s="13" t="str">
-        <x:v>D22; D23; D25; D26</x:v>
+        <x:v>ROSA Platform/Security, P2-CICD-01 Runner 기반 Delivery, transaction-api/fds-engine Health·Rule Smoke Test와 Registry/DNS/Operator Decision 상태 승인</x:v>
       </x:c>
       <x:c r="I12" s="13" t="str">
         <x:v>Registry는 D22, Hybrid DNS는 D23을 따른다. D23 미적용은 P0 IP Endpoint 사용 시 Non-blocker다.</x:v>
       </x:c>
       <x:c r="J12" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -11791,13 +12720,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H13" s="13" t="str">
-        <x:v>D21; D22; D23; D26</x:v>
+        <x:v>Hybrid DB/Registry Integration, OADP 복구검증, Hybrid E2E/Regression, Critical Issue 0을 승인</x:v>
       </x:c>
       <x:c r="I13" s="13" t="str">
         <x:v>Hybrid DNS와 Operator 공급망은 D23/D26 결과에 따라 구현 또는 Cancelled 처리한다. 같은 날 DEC-CAL-P2-01 검토를 시작해 Review 일정을 10-23까지 확정한다.</x:v>
       </x:c>
       <x:c r="J13" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -11823,13 +12752,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H14" s="13" t="str">
-        <x:v>D24</x:v>
+        <x:v>승인된 일정에 Hybrid Demo/산출물/G6/Known Issue/Cloud Resource Review를 수행하고 Action·승인결과를 기록</x:v>
       </x:c>
       <x:c r="I14" s="13" t="str">
         <x:v>2026-10-24는 토요일이며 Working Days 0이다. D24가 변경을 승인하면 Start/End를 동일하게 수정한다.</x:v>
       </x:c>
       <x:c r="J14" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -11855,13 +12784,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H15" s="13" t="str">
-        <x:v>D24</x:v>
+        <x:v>Review Action, P0 승인, 후속 P1/Known Issue, Cloud Resource/Cost, Source/Deliverable 인계 및 Project Close Sign-off 확보</x:v>
       </x:c>
       <x:c r="I15" s="13" t="str">
         <x:v>D24가 Review를 10-26 이후로 이동시키면 Project Close도 Change Request 대상이다.</x:v>
       </x:c>
       <x:c r="J15" s="13" t="str">
-        <x:v>Approve gate evidence</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -11887,13 +12816,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H16" s="13" t="str">
-        <x:v>D20</x:v>
+        <x:v>09-20 일요일 Review 유지 또는 영업일 재배치, 참석자·승인권자·시간·대체일을 확정하고 WBS/Calendar 동기화</x:v>
       </x:c>
       <x:c r="I16" s="13" t="str">
         <x:v>09-20은 일요일이며 Working Days 0이다. 결정 전 해당 일정을 확정된 근무일로 간주하지 않는다.</x:v>
       </x:c>
       <x:c r="J16" s="13" t="str">
-        <x:v>Confirm weekend date</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -11919,13 +12848,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H17" s="13" t="str">
-        <x:v>D24</x:v>
+        <x:v>10-24 토요일 Review 유지 또는 영업일 재배치, 참석자·승인권자·시간·Project Close 영향도를 확정하고 WBS 동기화</x:v>
       </x:c>
       <x:c r="I17" s="13" t="str">
         <x:v>2026-10-24는 토요일이며 Working Days 0이다. Project Close 10-26 영향을 함께 검토한다.</x:v>
       </x:c>
       <x:c r="J17" s="13" t="str">
-        <x:v>Confirm weekend date</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -11933,7 +12862,7 @@
         <x:v>ICR-D-NET-01-01</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>Kubernetes Node Host Firewall &amp; Monitoring Route</x:v>
+        <x:v>Kubernetes Node Host Firewall / Monitoring Route</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>Change Request</x:v>
@@ -11949,13 +12878,13 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H18" s="13" t="str">
-        <x:v>D-NET-01 §15.2; P1-LB Stage A; P1-MON-01</x:v>
+        <x:v>Kubernetes 6개 Node의 보호 공백 없는 firewalld→Calico named HEP/GNP 전환, 30080/9100/10250 최소 허용, 관리망 반환 경로와 IF-06B 정합화, Positive/Negative/Regression/Reboot/Rollback 및 무결성 Evidence 완료</x:v>
       </x:c>
       <x:c r="I18" s="13" t="str">
-        <x:v>종료일은 Lead 승인 후 확정(TBD). mgmt-gw01 경유 Return Route와 9100/10250 최소 허용 Evidence가 필요.</x:v>
+        <x:v>CP1 사전 진단 완료, 최소 CP 통신 canary 적용·독립 리뷰·운영 인수 대기. 6대 HEP/GNP·IF-06B·IF-16 및 NTP 목적지/Worker 검증은 잔여. End/기간 TBD 유지.</x:v>
       </x:c>
       <x:c r="J18" s="13" t="str">
-        <x:v>End date / G2 impact approval</x:v>
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="38" customHeight="1">
@@ -12019,7 +12948,7 @@
         <x:v>v3.1.16 findings corrected in v3.1.17; CR-P1-ANS-01-01 review remains independent</x:v>
       </x:c>
       <x:c r="J20" s="67" t="str">
-        <x:v>Release v3.1.17 after integrity PASS</x:v>
+        <x:v>v3.1.17 RELEASED 2026-09-07</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
@@ -12027,28 +12956,28 @@
         <x:v>CAL-HY-20260908</x:v>
       </x:c>
       <x:c r="B21" s="67" t="str">
+        <x:v>이하영 면접 휴가</x:v>
+      </x:c>
+      <x:c r="C21" s="67" t="str">
         <x:v>Calendar Control</x:v>
       </x:c>
-      <x:c r="C21" s="67" t="str">
+      <x:c r="D21" s="68" t="str">
         <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="D21" s="68" t="n">
-        <x:v>46273</x:v>
       </x:c>
       <x:c r="E21" s="68" t="n">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="F21" s="67" t="str">
-        <x:v>이권욱</x:v>
+      <x:c r="F21" s="68" t="n">
+        <x:v>46273</x:v>
       </x:c>
       <x:c r="G21" s="67" t="str">
-        <x:v>HY LEE interview leave recorded</x:v>
+        <x:v>이하영</x:v>
       </x:c>
       <x:c r="H21" s="67" t="str">
-        <x:v>No automatic rebaseline</x:v>
+        <x:v>개인 휴가를 작업일에서 제외</x:v>
       </x:c>
       <x:c r="I21" s="67" t="str">
-        <x:v>Update WBS/Gantt and reassess actual delay</x:v>
+        <x:v>기존 일정 / Gate 날짜 유지</x:v>
       </x:c>
       <x:c r="J21" s="67" t="str">
         <x:v>User instruction 2026-09-08</x:v>
@@ -12059,7 +12988,7 @@
         <x:v>CR-P1-ANS-01-01</x:v>
       </x:c>
       <x:c r="B22" s="67" t="str">
-        <x:v>Kubernetes Node DNS Resolver Automation</x:v>
+        <x:v>Ansible Kubernetes Node DNS Resolver 변경</x:v>
       </x:c>
       <x:c r="C22" s="67" t="str">
         <x:v>Change Request</x:v>
@@ -12077,13 +13006,301 @@
         <x:v>이권욱</x:v>
       </x:c>
       <x:c r="H22" s="67" t="str">
-        <x:v>11개 Acceptance Criteria PASS; 이하영 Support Review; 승인 HEAD·Merge Commit 고정</x:v>
+        <x:v>Kubernetes 6개 Node의 DNS 전환, 검색 도메인·API FQDN/Short Name·외부 DNS·직접 질의·서비스 회귀·멱등성·Rollback·Evidence 무결성 및 Support Review 완료</x:v>
       </x:c>
       <x:c r="I22" s="67" t="str">
-        <x:v>GitHub Actions NOT RUN; K8s API·LB Stage B·kubeadm·ICR Runtime 완료를 의미하지 않음</x:v>
+        <x:v>2026-09-07 Runtime·멱등성·회귀·Rollback·무결성 증적과 이하영 승인 리뷰를 완료하고 이권욱 수동 승인으로 PR #1을 병합했다. GitHub Actions 실행은 0건이므로 CI PASS로 기록하지 않는다. v3.1.17의 `In Review` 표시는 발행 시점 스냅샷이며 다음 정본에서 `Done`으로 동기화한다.</x:v>
       </x:c>
       <x:c r="J22" s="67" t="str">
-        <x:v>v3.1.18 정본 묶음에 Baseline·WBS/Gantt·Ticket Pack·완료 기록·증적 참조 동기화</x:v>
+        <x:v>Recorded; runtime scope remains separate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="58" customHeight="1">
+      <x:c r="A23" s="83" t="str">
+        <x:v>DEC-P1-FDS-01</x:v>
+      </x:c>
+      <x:c r="B23" s="83" t="str">
+        <x:v>거래 보류 도입 범위·판정·평가 실패·Gate 편입 결정</x:v>
+      </x:c>
+      <x:c r="C23" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D23" s="83" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E23" s="84" t="n">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="F23" s="84" t="n">
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="G23" s="83" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="H23" s="83" t="str">
+        <x:v>현행 탐지·기록 유지, 신규 보류·운영 기능 미도입, 실패 정책·계약 소유권, G2 영향 없음 및 후속 검증·재검토 조건 기록</x:v>
+      </x:c>
+      <x:c r="I23" s="83" t="str">
+        <x:v>현행 유지·신규 기능 확대 유예 결정 Done. 본 v3.1.18 후보에 통합하며 발행 전 운영 정본은 v3.1.17이다. 신규 기능 G2 편입·Runtime 승인은 아니다.</x:v>
+      </x:c>
+      <x:c r="J23" s="83" t="str">
+        <x:v>Recorded; runtime scope remains separate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="58" customHeight="1">
+      <x:c r="A24" s="83" t="str">
+        <x:v>DEC-P1-TXN-01</x:v>
+      </x:c>
+      <x:c r="B24" s="83" t="str">
+        <x:v>거래 상태·API 응답·재시도·데이터 정합성 계약 결정</x:v>
+      </x:c>
+      <x:c r="C24" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D24" s="83" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E24" s="84" t="n">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="F24" s="84" t="n">
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="G24" s="83" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="H24" s="83" t="str">
+        <x:v>기존 계약 유지 선택, 신규 상태/API·Migration 변경 유예, #4/#6과 정책·표현 소유권 및 기존 구현 정합성 후속 기록</x:v>
+      </x:c>
+      <x:c r="I24" s="83" t="str">
+        <x:v>현행 유지·신규 기능 확대 유예 결정 Done. 본 v3.1.18 후보에 통합하며 발행 전 운영 정본은 v3.1.17이다. 신규 기능 G2 편입·Runtime 승인은 아니다.</x:v>
+      </x:c>
+      <x:c r="J24" s="83" t="str">
+        <x:v>Recorded; runtime scope remains separate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="58" customHeight="1">
+      <x:c r="A25" s="83" t="str">
+        <x:v>DEC-P1-ADMIN-01</x:v>
+      </x:c>
+      <x:c r="B25" s="83" t="str">
+        <x:v>보안 시연 범위·테스트 전제·조건부 운영 통제 결정</x:v>
+      </x:c>
+      <x:c r="C25" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D25" s="83" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E25" s="84" t="n">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="F25" s="84" t="n">
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="G25" s="83" t="str">
+        <x:v>이하영</x:v>
+      </x:c>
+      <x:c r="H25" s="83" t="str">
+        <x:v>프론트엔드 배치 제외, 합성 데이터·최소 노출 원칙, 5개 검토 축 적용/유예, 기존 접근 통제 재사용 및 후속 시나리오 인계 기록</x:v>
+      </x:c>
+      <x:c r="I25" s="83" t="str">
+        <x:v>현행 유지·신규 기능 확대 유예 결정 Done. 본 v3.1.18 후보에 통합하며 발행 전 운영 정본은 v3.1.17이다. 신규 기능 G2 편입·Runtime 승인은 아니다.</x:v>
+      </x:c>
+      <x:c r="J25" s="83" t="str">
+        <x:v>Recorded; runtime scope remains separate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="58" customHeight="1">
+      <x:c r="A26" s="83" t="str">
+        <x:v>D-SEC-01</x:v>
+      </x:c>
+      <x:c r="B26" s="83" t="str">
+        <x:v>Security Design Scope / Approval Review</x:v>
+      </x:c>
+      <x:c r="C26" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D26" s="83" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E26" s="84" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="F26" s="84" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="G26" s="83" t="str">
+        <x:v>이하영</x:v>
+      </x:c>
+      <x:c r="H26" s="83" t="str">
+        <x:v>승인권자 지정, D-SEC-01 검토 범위·산출물·Exit Criteria 승인, P1-SEC-01과의 경계 승인, 요구사항과 검증 증적 연결 후 Done 판정</x:v>
+      </x:c>
+      <x:c r="I26" s="83" t="str">
+        <x:v>v3.1.14 최종 승인·정본 반영 완료. 구현은 P1-SEC-01로 이관.</x:v>
+      </x:c>
+      <x:c r="J26" s="83" t="str">
+        <x:v>Recorded; runtime scope remains separate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="58" customHeight="1">
+      <x:c r="A27" s="83" t="str">
+        <x:v>P2-OCI-01</x:v>
+      </x:c>
+      <x:c r="B27" s="83" t="str">
+        <x:v>OCI Relay Go / No-Go</x:v>
+      </x:c>
+      <x:c r="C27" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D27" s="83" t="str">
+        <x:v>To Do</x:v>
+      </x:c>
+      <x:c r="E27" s="84" t="n">
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="F27" s="84" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G27" s="83" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="H27" s="83" t="str">
+        <x:v>OCI Relay 가능성·권한·Public Endpoint·IPsec/NAT-T·Route를 검증하고 Primary 또는 승인 Fallback 경로를 선택</x:v>
+      </x:c>
+      <x:c r="I27" s="83" t="str">
+        <x:v>10-02 Go/No-Go를 넘기지 않는다. No-Go 시 Vendor Endpoint→AWS EC2+EIP Relay→Overlay 순으로 승인된 Fallback을 선택한다.</x:v>
+      </x:c>
+      <x:c r="J27" s="83" t="str">
+        <x:v>Review / evidence pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="58" customHeight="1">
+      <x:c r="A28" s="83" t="str">
+        <x:v>DEC-P2-DNS-01</x:v>
+      </x:c>
+      <x:c r="B28" s="83" t="str">
+        <x:v>Hybrid DNS Scope Decision</x:v>
+      </x:c>
+      <x:c r="C28" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D28" s="83" t="str">
+        <x:v>To Do</x:v>
+      </x:c>
+      <x:c r="E28" s="84" t="n">
+        <x:v>46307</x:v>
+      </x:c>
+      <x:c r="F28" s="84" t="n">
+        <x:v>46311</x:v>
+      </x:c>
+      <x:c r="G28" s="83" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="H28" s="83" t="str">
+        <x:v>P0 IP Endpoint 유지 또는 Hybrid DNS P1 적용을 확정하고 Resolver/Forwarding/Zone/Route/테스트·Cancelled 결정 근거를 승인</x:v>
+      </x:c>
+      <x:c r="I28" s="83" t="str">
+        <x:v>Hybrid P0 E2E는 IP Endpoint를 허용하므로 본 P1 결정 미완료가 G5/G6를 자동 차단하지 않는다.</x:v>
+      </x:c>
+      <x:c r="J28" s="83" t="str">
+        <x:v>Review / evidence pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="58" customHeight="1">
+      <x:c r="A29" s="83" t="str">
+        <x:v>DEC-P2-OP-01</x:v>
+      </x:c>
+      <x:c r="B29" s="83" t="str">
+        <x:v>Operator Supply Chain Scope Decision</x:v>
+      </x:c>
+      <x:c r="C29" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D29" s="83" t="str">
+        <x:v>To Do</x:v>
+      </x:c>
+      <x:c r="E29" s="84" t="n">
+        <x:v>46307</x:v>
+      </x:c>
+      <x:c r="F29" s="84" t="n">
+        <x:v>46311</x:v>
+      </x:c>
+      <x:c r="G29" s="83" t="str">
+        <x:v>이하영</x:v>
+      </x:c>
+      <x:c r="H29" s="83" t="str">
+        <x:v>ROSA Operator 공급망을 Direct Catalog 또는 oc-mirror/Harbor/Custom CatalogSource 중 하나로 결정하고 구현·N/A 기준 승인</x:v>
+      </x:c>
+      <x:c r="I29" s="83" t="str">
+        <x:v>D26에서 Direct Catalog 선택 시 P2-OP-01은 Cancelled 처리하고, Mirror 선택 시 P2-OP-01을 활성화한다.</x:v>
+      </x:c>
+      <x:c r="J29" s="83" t="str">
+        <x:v>Review / evidence pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="58" customHeight="1">
+      <x:c r="A30" s="83" t="str">
+        <x:v>DEC-P2-REG-01</x:v>
+      </x:c>
+      <x:c r="B30" s="83" t="str">
+        <x:v>ROSA Image Registry Source Decision</x:v>
+      </x:c>
+      <x:c r="C30" s="83" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="D30" s="83" t="str">
+        <x:v>To Do</x:v>
+      </x:c>
+      <x:c r="E30" s="84" t="n">
+        <x:v>46307</x:v>
+      </x:c>
+      <x:c r="F30" s="84" t="n">
+        <x:v>46311</x:v>
+      </x:c>
+      <x:c r="G30" s="83" t="str">
+        <x:v>이하영</x:v>
+      </x:c>
+      <x:c r="H30" s="83" t="str">
+        <x:v>ROSA Image Source를 On-Prem Harbor 또는 승인 Cloud Registry로 확정하고 Route·TLS·Credential·비용·Fallback을 승인</x:v>
+      </x:c>
+      <x:c r="I30" s="83" t="str">
+        <x:v>기준선의 ROSA→Harbor는 Optional이다. P2-APP-01 최종 Image 경로 전 10-16까지 확정한다.</x:v>
+      </x:c>
+      <x:c r="J30" s="83" t="str">
+        <x:v>Review / evidence pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="58" customHeight="1">
+      <x:c r="A31" s="83" t="str">
+        <x:v>MS-DELIVERABLE-FREEZE-01</x:v>
+      </x:c>
+      <x:c r="B31" s="83" t="str">
+        <x:v>Deliverable Freeze</x:v>
+      </x:c>
+      <x:c r="C31" s="83" t="str">
+        <x:v>Milestone</x:v>
+      </x:c>
+      <x:c r="D31" s="83" t="str">
+        <x:v>To Do</x:v>
+      </x:c>
+      <x:c r="E31" s="84" t="n">
+        <x:v>46318</x:v>
+      </x:c>
+      <x:c r="F31" s="84" t="n">
+        <x:v>46318</x:v>
+      </x:c>
+      <x:c r="G31" s="83" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="H31" s="83" t="str">
+        <x:v>Architecture/IaC/Test/Runbook/Evidence/Decision/Known Issue의 최종 Version과 변경금지를 승인</x:v>
+      </x:c>
+      <x:c r="I31" s="83" t="str">
+        <x:v>Freeze 이후 변경은 Review Action 또는 Change Request로만 허용한다.</x:v>
+      </x:c>
+      <x:c r="J31" s="83" t="str">
+        <x:v>Review / evidence pending</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12109,30 +13326,16 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · Risks, Assumptions &amp; Lead Decisions (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Risks, Assumptions &amp; Lead Decisions</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Risks, Assumptions &amp; Lead Decisions</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Risks, Assumptions &amp; Lead Decisions</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Risks, Assumptions &amp; Lead Decisions</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Risks, Assumptions &amp; Lead Decisions</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Risks, Assumptions &amp; Lead Decisions</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Risks, Assumptions &amp; Lead Decisions</x:v>
-      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="9" t="str">
@@ -12472,36 +13675,18 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · Sources &amp; Change Log (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>FDS v3.1.14 · Sources &amp; Change Log</x:v>
-      </x:c>
-      <x:c r="J1" s="14" t="str">
-        <x:v>Non-working dates</x:v>
-      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
     </x:row>
     <x:row r="2">
       <x:c r="J2" s="15" t="n">
@@ -12536,19 +13721,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="13" t="str">
-        <x:v>Canonical</x:v>
+        <x:v>Canonical candidate</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>FDS_Project_Implementation_Baseline_v3.1.17.md</x:v>
+        <x:v>FDS_Project_Implementation_Baseline_v3.1.18.md</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>v3.1.17 / 2026-09-04</x:v>
+        <x:v>v3.1.18</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>Architecture / security / gates / team availability / document governance</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>Primary canonical candidate</x:v>
+        <x:v>Current candidate scope / release review pending</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
         <x:v>D36 / Team availability</x:v>
@@ -12562,19 +13747,19 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
-        <x:v>Canonical</x:v>
+        <x:v>Canonical candidate</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>FDS_v3.1.17_Canonical_Ticket_Update_Pack_v1.0.md</x:v>
+        <x:v>FDS_v3.1.18_Canonical_Ticket_Update_Pack_v1.0.md</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>v1.0 / 2026-09-04</x:v>
+        <x:v>v3.1.18</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Ticket status / owner / acceptance / schedule</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
-        <x:v>Applied as override</x:v>
+        <x:v>64 records; 55 planning + 9 historical closed</x:v>
       </x:c>
       <x:c r="G5" s="13" t="str">
         <x:v>P1-DNS-01</x:v>
@@ -12726,7 +13911,7 @@
         <x:v>Repository governance / integrity correction</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>User-approved decision; release remains candidate until PR approval</x:v>
+        <x:v>v3.1.17 RELEASED 2026-09-07; historical control retained</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
@@ -12785,6 +13970,142 @@
       </x:c>
       <x:c r="J14" s="67" t="str">
         <x:v>NOT RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="58" customHeight="1">
+      <x:c r="A15" s="83" t="str">
+        <x:v>Issue snapshot</x:v>
+      </x:c>
+      <x:c r="B15" s="83" t="str">
+        <x:v>tickets/v3.1.18/source-snapshot.json</x:v>
+      </x:c>
+      <x:c r="C15" s="83" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="D15" s="83" t="str">
+        <x:v>Read-only capture</x:v>
+      </x:c>
+      <x:c r="E15" s="83" t="str">
+        <x:v>Owner reports distinguished from independent evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="58" customHeight="1">
+      <x:c r="A16" s="83" t="str">
+        <x:v>CR merge</x:v>
+      </x:c>
+      <x:c r="B16" s="83" t="str">
+        <x:v>https://github.com/321Team/infra-ansible/pull/1</x:v>
+      </x:c>
+      <x:c r="C16" s="83" t="str">
+        <x:v>4f9bdb7c08704eebb3d1b294751e51b0721b6af4</x:v>
+      </x:c>
+      <x:c r="D16" s="83" t="str">
+        <x:v>Done 2026-09-07</x:v>
+      </x:c>
+      <x:c r="E16" s="83" t="str">
+        <x:v>DNS resolver CR; not Bootstrap approval</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="58" customHeight="1">
+      <x:c r="A17" s="83" t="str">
+        <x:v>Follow-up merge</x:v>
+      </x:c>
+      <x:c r="B17" s="83" t="str">
+        <x:v>https://github.com/321Team/infra-ansible/pull/3</x:v>
+      </x:c>
+      <x:c r="C17" s="83" t="str">
+        <x:v>5cbf3b657014b32a20cb5816d90d3ea5fe4951ab</x:v>
+      </x:c>
+      <x:c r="D17" s="83" t="str">
+        <x:v>Merged</x:v>
+      </x:c>
+      <x:c r="E17" s="83" t="str">
+        <x:v>Gate 0 code; runtime separate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="58" customHeight="1">
+      <x:c r="A18" s="83" t="str">
+        <x:v>Follow-up merge</x:v>
+      </x:c>
+      <x:c r="B18" s="83" t="str">
+        <x:v>https://github.com/321Team/infra-ansible/pull/4</x:v>
+      </x:c>
+      <x:c r="C18" s="83" t="str">
+        <x:v>3a02dc8934adb1f80df48ec6763689c401a1e8d6</x:v>
+      </x:c>
+      <x:c r="D18" s="83" t="str">
+        <x:v>Merged</x:v>
+      </x:c>
+      <x:c r="E18" s="83" t="str">
+        <x:v>SSH count guard + issue #10 operational closure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="58" customHeight="1">
+      <x:c r="A19" s="83" t="str">
+        <x:v>Evidence merge</x:v>
+      </x:c>
+      <x:c r="B19" s="83" t="str">
+        <x:v>https://github.com/321Team/fds-project-evidence/pull/2</x:v>
+      </x:c>
+      <x:c r="C19" s="83" t="str">
+        <x:v>36a65c64763077eabe680b81827b1c4dc6ad3fc5</x:v>
+      </x:c>
+      <x:c r="D19" s="83" t="str">
+        <x:v>Merged</x:v>
+      </x:c>
+      <x:c r="E19" s="83" t="str">
+        <x:v>DB evidence merge; deployed app verification incomplete</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="58" customHeight="1">
+      <x:c r="A20" s="83" t="str">
+        <x:v>Working days</x:v>
+      </x:c>
+      <x:c r="B20" s="83" t="str">
+        <x:v>Team Calendar!A5:F11</x:v>
+      </x:c>
+      <x:c r="C20" s="83" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="D20" s="83" t="str">
+        <x:v>Corrected range</x:v>
+      </x:c>
+      <x:c r="E20" s="83" t="str">
+        <x:v>HY 09-08 included; SEC 5 days / ADMIN 1 day</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="58" customHeight="1">
+      <x:c r="A21" s="83" t="str">
+        <x:v>Candidate delta</x:v>
+      </x:c>
+      <x:c r="B21" s="83" t="str">
+        <x:v>audit/v3.1.18/property-delta.json</x:v>
+      </x:c>
+      <x:c r="C21" s="83" t="str">
+        <x:v>v3.1.18</x:v>
+      </x:c>
+      <x:c r="D21" s="83" t="str">
+        <x:v>No Issue write</x:v>
+      </x:c>
+      <x:c r="E21" s="83" t="str">
+        <x:v>Description refresh must precede fresh metadata map / plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="58" customHeight="1">
+      <x:c r="A22" s="83" t="str">
+        <x:v>Planning count</x:v>
+      </x:c>
+      <x:c r="B22" s="83" t="str">
+        <x:v>WBS!A4:A58</x:v>
+      </x:c>
+      <x:c r="C22" s="83" t="str">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D22" s="83" t="str">
+        <x:v>52 + 3 decisions</x:v>
+      </x:c>
+      <x:c r="E22" s="83" t="str">
+        <x:v>Historic closed 9 retained in Ticket Pack, excluded from backlog</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12812,18 +14133,18 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>FDS v3.1.18 · Team Availability Calendar (CANDIDATE)</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="30"/>
-      <x:c r="D1" s="30"/>
-      <x:c r="E1" s="30"/>
-      <x:c r="F1" s="30"/>
-      <x:c r="G1" s="30"/>
-      <x:c r="H1" s="30"/>
-      <x:c r="I1" s="30"/>
-      <x:c r="J1" s="30"/>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="33" t="str">

--- a/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
+++ b/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R59de15557d2a40d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R02f318c594b54eb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="R133389d2406949a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="Rc6fea7b1f7584016"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="R6a72812e68f84ecf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="Rc9345d8e43814cf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="R007f1f2aae214edc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="R028937b20bd648cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fast Track Plan" sheetId="9" r:id="Ra654dbb8f62d440a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R137a26d119ab4fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R2b78cea4860f46f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="R02176cc0027a4d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="R4b8617fd2af240c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="R3b845c23c57a46c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="R279c4388cc5a4e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="R31006a1b979b4f9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="R09d66d5b4d934e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fast Track Plan" sheetId="9" r:id="R0014c28a50aa4e63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -649,7 +649,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="38">
+  <x:dxfs count="39">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -1000,6 +1000,17 @@
         <x:color rgb="FFB4233D"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFDE3E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB4233D"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFDE3E7"/>
         </x:patternFill>
@@ -1255,7 +1266,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbe51134b881f4031"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae5a8ad124bb46de"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1285,7 +1296,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8d2e98215b35452d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3d52f5ad47624164"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1971,7 +1982,7 @@
     <x:mergeCell ref="A18:V18"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3453ac8c19674810"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a2969211bc44256"/>
 </x:worksheet>
 </file>
 
@@ -2357,7 +2368,7 @@
         <x:v>09-11 CP1, 09-14 CP2/3·Worker, 09-15 NTP·Calico, 09-17 증적 인수를 조건부 목표로 둔다. 실제 상태·완료 판정은 유지한다. 세부 배정: Fast Track Plan 시트.</x:v>
       </x:c>
       <x:c r="R7" s="13" t="str">
-        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #10 snapshot 2026-09-10T05:03:27Z; Issue #10 후속 2026-09-10T06:25:12Z; infra-kubernetes PR #3 @3309866766236bbdbe20b9e2ae1d8fd6f9233bcd; Fast Tracking 일정 권장안 2026-09-10 / 사용자 재편성 요청</x:v>
+        <x:v>Baseline/Ticket Pack v3.1.18; GitHub #10; K8S PR #2 097ddb5, #3 merge 7d44afc, #4 75d476e; audit/v3.1.18/k8s-intake-20260910.json</x:v>
       </x:c>
       <x:c r="S7" s="13" t="str">
         <x:f>IF(G7="Done","Done",IF(I7="",IF(F7="P1","Deferred P1","End TBD"),IF(I7&lt;'Executive Summary'!$B$4,"Overdue",IF(H7&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
@@ -2605,7 +2616,7 @@
         <x:v>09-21은 권장 Plan End이며 실제 종료일 확정이나 AC 완료가 아니다. 기존 End TBD 이력은 보존한다. CP→Worker·NTP·IF-16을 먼저, IF-06B·Negative/Reboot/Rollback·보호 인계를 후속 검증한다. 실제 상태·완료 판정은 유지한다. 세부 배정: Fast Track Plan 시트.</x:v>
       </x:c>
       <x:c r="R11" s="13" t="str">
-        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #14 snapshot 2026-09-10T05:03:39Z; Issue #14 후속 2026-09-10T06:25:25Z; infra-kubernetes PR #3 @3309866766236bbdbe20b9e2ae1d8fd6f9233bcd; Fast Tracking 일정 권장안 2026-09-10 / 사용자 재편성 요청</x:v>
+        <x:v>Baseline/Ticket Pack v3.1.18; GitHub #14; K8S PR #2 097ddb5, #3 merge 7d44afc, #4 75d476e; audit/v3.1.18/k8s-intake-20260910.json</x:v>
       </x:c>
       <x:c r="S11" s="13" t="str">
         <x:f>IF(G11="Done","Done",IF(I11="",IF(F11="P1","Deferred P1","End TBD"),IF(I11&lt;'Executive Summary'!$B$4,"Overdue",IF(H11&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
@@ -2977,7 +2988,7 @@
         <x:v>09-10 휴가 추가 후 기존 09-04~11 가용일은 4일. 권장 종료 09-21로 확장한 전체 계획창의 가용일은 10일이며 잔여 공수를 뜻하지 않는다. Runtime 검증은 플랫폼·앱 인수와 연계한다. 실제 상태·완료 판정은 유지한다. 세부 배정: Fast Track Plan 시트.</x:v>
       </x:c>
       <x:c r="R17" s="13" t="str">
-        <x:v>Baseline v3.1.18; Ticket Pack v3.1.18; GitHub #19 snapshot 2026-09-10T05:05:52Z; 사용자 2026-09-10 면접 휴가 추가 지시; Fast Tracking 일정 권장안 2026-09-10 / 사용자 재편성 요청</x:v>
+        <x:v>Baseline/Ticket Pack v3.1.18; GitHub #19; K8S PR #2 097ddb5, #3 merge 7d44afc, #4 75d476e; audit/v3.1.18/k8s-intake-20260910.json</x:v>
       </x:c>
       <x:c r="S17" s="13" t="str">
         <x:f>IF(G17="Done","Done",IF(I17="",IF(F17="P1","Deferred P1","End TBD"),IF(I17&lt;'Executive Summary'!$B$4,"Overdue",IF(H17&gt;'Executive Summary'!$B$4,"Upcoming","Active window"))))</x:f>
@@ -5548,7 +5559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra65014fa3f164c1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff9569fd6a0f452c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14363,47 +14374,47 @@
         <x:v>https://github.com/321Team/infra-kubernetes/pull/3</x:v>
       </x:c>
       <x:c r="C24" s="67" t="str">
-        <x:v>3309866766236bbdbe20b9e2ae1d8fd6f9233bcd</x:v>
+        <x:v>7d44afc3afff4d322cb4dbeff4433d61e23e111a</x:v>
       </x:c>
       <x:c r="D24" s="67" t="str">
-        <x:v>Evidence PARTIAL</x:v>
+        <x:v>Merged; supplement PASS</x:v>
       </x:c>
       <x:c r="E24" s="67" t="str">
-        <x:v>99 queries / empty time_state; CP→Worker 0/9, Worker→LB 3/3; supplement pending</x:v>
+        <x:v>24/24 queries; time, kubelet cause and Cockpit mask verified. Runtime pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" s="67" t="str">
-        <x:v>Review status</x:v>
+        <x:v>Runtime plans</x:v>
       </x:c>
       <x:c r="B25" s="67" t="str">
-        <x:v>https://github.com/321Team/infra-kubernetes/pull/2</x:v>
+        <x:v>https://github.com/321Team/infra-kubernetes/pull/4</x:v>
       </x:c>
       <x:c r="C25" s="67" t="str">
-        <x:v>068661e076de02669170d3582f3d596d6e1a8eb3</x:v>
+        <x:v>PR #2 097ddb5 / #4 75d476e</x:v>
       </x:c>
       <x:c r="D25" s="67" t="str">
-        <x:v>Ready for review</x:v>
+        <x:v>New HEAD review pending</x:v>
       </x:c>
       <x:c r="E25" s="67" t="str">
-        <x:v>하영님 요청됨; independent approval / runtime pending</x:v>
+        <x:v>PR #2: onsite mock 37/37, inspect 115. PR #4: local mock 74. Runtime not verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" s="67" t="str">
-        <x:v>Follow-up snapshot</x:v>
+        <x:v>K8S intake</x:v>
       </x:c>
       <x:c r="B26" s="67" t="str">
-        <x:v>audit/v3.1.18/followup-20260910.json</x:v>
+        <x:v>audit/v3.1.18/k8s-intake-20260910.json</x:v>
       </x:c>
       <x:c r="C26" s="67" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D26" s="67" t="str">
-        <x:v>Issue #10 / #14</x:v>
+        <x:v>Issues #10 / #14 / #19</x:v>
       </x:c>
       <x:c r="E26" s="67" t="str">
-        <x:v>Original source-snapshot.json preserved</x:v>
+        <x:v>Original snapshots preserved; NTP, CP2 resume, final host protection and storage pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="52" customHeight="1">
@@ -15111,7 +15122,7 @@
         <x:v>수집·정리</x:v>
       </x:c>
       <x:c r="E6" s="130" t="str">
-        <x:v>Worker supplement·ICR 변경범위 정리</x:v>
+        <x:v>CP1 보호·복구·최신 inspect 준비·ICR 범위 정리</x:v>
       </x:c>
       <x:c r="F6" s="130" t="str">
         <x:v>ICR-D-NET-01-01</x:v>
@@ -15151,7 +15162,7 @@
         <x:v>리뷰·결정</x:v>
       </x:c>
       <x:c r="E7" s="131" t="str">
-        <x:v>PR #2 독립 리뷰·NTP 기준·평일 Review 일정 검토</x:v>
+        <x:v>PR #2/#4 재리뷰·NTP 기준·평일 Review 검토</x:v>
       </x:c>
       <x:c r="F7" s="131" t="str">
         <x:v>DEC-CAL-P1-01</x:v>
@@ -17248,7 +17259,7 @@
     <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="K6:K59">
-    <x:cfRule type="containsText" dxfId="37" priority="1" operator="containsText" text="OVERBOOKED"/>
+    <x:cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="OVERBOOKED"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
+++ b/wbs/FDS_v3.1.18_WBS_and_Gantt_v1.0.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R137a26d119ab4fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R2b78cea4860f46f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="R02176cc0027a4d64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="R4b8617fd2af240c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="R3b845c23c57a46c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="R279c4388cc5a4e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="R31006a1b979b4f9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="R09d66d5b4d934e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fast Track Plan" sheetId="9" r:id="R0014c28a50aa4e63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="Rcc79c89ada854c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="Rb87c79f96a824ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Gantt" sheetId="3" r:id="R735bf5c314ac4d2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Gantt" sheetId="4" r:id="Rfca90b01225e4bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones &amp; Decisions" sheetId="5" r:id="R5f9d05df07d445af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Assumptions" sheetId="6" r:id="R4f3e8529c58344a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Change Log" sheetId="7" r:id="Recf9f24bc52a4f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Calendar" sheetId="8" r:id="Rf83e5ff918d348a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fast Track Plan" sheetId="9" r:id="R4b9886d315be4d71"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -649,7 +649,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="39">
+  <x:dxfs count="40">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -1011,6 +1011,17 @@
         <x:color rgb="FFB4233D"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFDE3E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB4233D"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFDE3E7"/>
         </x:patternFill>
@@ -1266,7 +1277,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae5a8ad124bb46de"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb60bf396596841f7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1296,7 +1307,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3d52f5ad47624164"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R812d8636bd3b431c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1554,7 +1565,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · Executive Schedule Summary (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · Executive Schedule Summary (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -1615,7 +1626,7 @@
         <x:v>Canonical version</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>3.1.18 CANDIDATE</x:v>
+        <x:v>3.1.18 RELEASED</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
         <x:v>G1 Target</x:v>
@@ -1982,7 +1993,7 @@
     <x:mergeCell ref="A18:V18"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a2969211bc44256"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4740b4d0a9bc43d4"/>
 </x:worksheet>
 </file>
 
@@ -2013,7 +2024,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · WBS (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · WBS (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -2045,7 +2056,7 @@
         <x:v>Canonical</x:v>
       </x:c>
       <x:c r="D2" s="17" t="str">
-        <x:v>3.1.18 CANDIDATE / Fast Tracking</x:v>
+        <x:v>3.1.18 RELEASED / Fast Tracking</x:v>
       </x:c>
       <x:c r="E2" s="17" t="str">
         <x:v>Records</x:v>
@@ -5559,7 +5570,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff9569fd6a0f452c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7583459ed90c483c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5607,7 +5618,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · Phase 1 Gantt (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · Phase 1 Gantt (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -9427,7 +9438,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · Phase 2 Gantt (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · Phase 2 Gantt (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -12572,7 +12583,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · Milestones &amp; Decision Calendar (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · Milestones &amp; Decision Calendar (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -13568,7 +13579,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · Risks, Assumptions &amp; Lead Decisions (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · Risks, Assumptions &amp; Lead Decisions (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -13917,7 +13928,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · Sources &amp; Change Log (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · Sources &amp; Change Log (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -14511,7 +14522,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="79" t="str">
-        <x:v>FDS v3.1.18 · Team Availability Calendar (CANDIDATE)</x:v>
+        <x:v>FDS v3.1.18 · Team Availability Calendar (RELEASED)</x:v>
       </x:c>
       <x:c r="B1" s="79"/>
       <x:c r="C1" s="79"/>
@@ -17259,7 +17270,7 @@
     <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="K6:K59">
-    <x:cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="OVERBOOKED"/>
+    <x:cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="OVERBOOKED"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
